--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.85</v>
+        <v>3.58</v>
       </c>
       <c r="F14" t="n">
-        <v>11.82</v>
+        <v>12.11</v>
       </c>
       <c r="G14" t="n">
-        <v>218.2</v>
+        <v>227.6</v>
       </c>
       <c r="H14" t="n">
-        <v>88.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-169.54</v>
+        <v>109.31</v>
       </c>
       <c r="K14" t="n">
-        <v>122.27</v>
+        <v>137.89</v>
       </c>
       <c r="L14" t="n">
-        <v>209.03</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:05</t>
+          <t>04:40:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="F15" t="n">
-        <v>12.31</v>
+        <v>11.97</v>
       </c>
       <c r="G15" t="n">
-        <v>239</v>
+        <v>245.3</v>
       </c>
       <c r="H15" t="n">
-        <v>74.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-30.14</v>
+        <v>-14.78</v>
       </c>
       <c r="K15" t="n">
-        <v>63.92</v>
+        <v>143.47</v>
       </c>
       <c r="L15" t="n">
-        <v>70.67</v>
+        <v>144.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:41:49</t>
+          <t>04:42:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="F16" t="n">
-        <v>13.04</v>
+        <v>12.36</v>
       </c>
       <c r="G16" t="n">
-        <v>240.2</v>
+        <v>241.9</v>
       </c>
       <c r="H16" t="n">
-        <v>82.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-72.79000000000001</v>
+        <v>74.83</v>
       </c>
       <c r="K16" t="n">
-        <v>-134.18</v>
+        <v>-107.78</v>
       </c>
       <c r="L16" t="n">
-        <v>152.66</v>
+        <v>131.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:46:45</t>
+          <t>04:46:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="F17" t="n">
-        <v>12.37</v>
+        <v>11.48</v>
       </c>
       <c r="G17" t="n">
-        <v>236.1</v>
+        <v>237.1</v>
       </c>
       <c r="H17" t="n">
-        <v>78.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.17</v>
+        <v>-28.46</v>
       </c>
       <c r="K17" t="n">
-        <v>20.7</v>
+        <v>-197.39</v>
       </c>
       <c r="L17" t="n">
-        <v>21.11</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:48:11</t>
+          <t>04:48:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="F18" t="n">
-        <v>12.67</v>
+        <v>11.58</v>
       </c>
       <c r="G18" t="n">
-        <v>229.3</v>
+        <v>243.1</v>
       </c>
       <c r="H18" t="n">
-        <v>76.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-112.78</v>
+        <v>-23.64</v>
       </c>
       <c r="K18" t="n">
-        <v>74.51000000000001</v>
+        <v>-238.79</v>
       </c>
       <c r="L18" t="n">
-        <v>135.17</v>
+        <v>239.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:25</t>
+          <t>04:50:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="F19" t="n">
-        <v>12.04</v>
+        <v>12.51</v>
       </c>
       <c r="G19" t="n">
-        <v>233.8</v>
+        <v>224.6</v>
       </c>
       <c r="H19" t="n">
-        <v>74.7</v>
+        <v>81.2</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>469.57</v>
+        <v>-79.06</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.12</v>
+        <v>131.54</v>
       </c>
       <c r="L19" t="n">
-        <v>469.57</v>
+        <v>153.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:55:04</t>
+          <t>04:54:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.9</v>
+        <v>2.13</v>
       </c>
       <c r="F20" t="n">
-        <v>11.78</v>
+        <v>12.45</v>
       </c>
       <c r="G20" t="n">
-        <v>234.5</v>
+        <v>211.2</v>
       </c>
       <c r="H20" t="n">
-        <v>72.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-228.72</v>
+        <v>-111.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-150.53</v>
+        <v>111.11</v>
       </c>
       <c r="L20" t="n">
-        <v>273.81</v>
+        <v>157.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:57:12</t>
+          <t>04:56:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="F21" t="n">
-        <v>12.27</v>
+        <v>12.16</v>
       </c>
       <c r="G21" t="n">
-        <v>233.8</v>
+        <v>240.4</v>
       </c>
       <c r="H21" t="n">
-        <v>83.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-318.31</v>
+        <v>23.83</v>
       </c>
       <c r="K21" t="n">
-        <v>400.09</v>
+        <v>-58.72</v>
       </c>
       <c r="L21" t="n">
-        <v>511.26</v>
+        <v>63.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:58:36</t>
+          <t>04:58:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.38</v>
+        <v>3.53</v>
       </c>
       <c r="F22" t="n">
-        <v>11.99</v>
+        <v>11.44</v>
       </c>
       <c r="G22" t="n">
-        <v>231.6</v>
+        <v>223.1</v>
       </c>
       <c r="H22" t="n">
-        <v>81.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-231.4</v>
+        <v>-224.79</v>
       </c>
       <c r="K22" t="n">
-        <v>116.86</v>
+        <v>-70.70999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>259.24</v>
+        <v>235.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:04:12</t>
+          <t>05:03:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="F23" t="n">
-        <v>12.43</v>
+        <v>12.25</v>
       </c>
       <c r="G23" t="n">
-        <v>239.2</v>
+        <v>242.8</v>
       </c>
       <c r="H23" t="n">
-        <v>82.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-216.85</v>
+        <v>-330.41</v>
       </c>
       <c r="K23" t="n">
-        <v>-400.76</v>
+        <v>471.49</v>
       </c>
       <c r="L23" t="n">
-        <v>455.66</v>
+        <v>575.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:05:58</t>
+          <t>05:05:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.54</v>
+        <v>2.86</v>
       </c>
       <c r="F24" t="n">
-        <v>11.6</v>
+        <v>12.36</v>
       </c>
       <c r="G24" t="n">
-        <v>242.1</v>
+        <v>232</v>
       </c>
       <c r="H24" t="n">
-        <v>71.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>672.83</v>
+        <v>43.53</v>
       </c>
       <c r="K24" t="n">
-        <v>-43.28</v>
+        <v>167.19</v>
       </c>
       <c r="L24" t="n">
-        <v>674.22</v>
+        <v>172.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:07:21</t>
+          <t>05:07:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="F25" t="n">
-        <v>12.6</v>
+        <v>11.73</v>
       </c>
       <c r="G25" t="n">
-        <v>234.6</v>
+        <v>226.8</v>
       </c>
       <c r="H25" t="n">
-        <v>83.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>369.39</v>
+        <v>58.16</v>
       </c>
       <c r="K25" t="n">
-        <v>-174.34</v>
+        <v>282.72</v>
       </c>
       <c r="L25" t="n">
-        <v>408.46</v>
+        <v>288.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:12:34</t>
+          <t>05:12:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="F26" t="n">
-        <v>12.3</v>
+        <v>12.07</v>
       </c>
       <c r="G26" t="n">
-        <v>229.7</v>
+        <v>231.6</v>
       </c>
       <c r="H26" t="n">
-        <v>78.7</v>
+        <v>80.7</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>772.42</v>
+        <v>78.14</v>
       </c>
       <c r="K26" t="n">
-        <v>-170.81</v>
+        <v>216.36</v>
       </c>
       <c r="L26" t="n">
-        <v>791.08</v>
+        <v>230.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:13:47</t>
+          <t>05:13:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.07</v>
+        <v>3.31</v>
       </c>
       <c r="F27" t="n">
-        <v>12.43</v>
+        <v>11.77</v>
       </c>
       <c r="G27" t="n">
-        <v>232.3</v>
+        <v>233.5</v>
       </c>
       <c r="H27" t="n">
-        <v>73.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>60.96</v>
+        <v>122.23</v>
       </c>
       <c r="K27" t="n">
-        <v>611.34</v>
+        <v>-90.94</v>
       </c>
       <c r="L27" t="n">
-        <v>614.37</v>
+        <v>152.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:15:29</t>
+          <t>05:15:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="F28" t="n">
-        <v>12.73</v>
+        <v>13.34</v>
       </c>
       <c r="G28" t="n">
-        <v>231.2</v>
+        <v>236.1</v>
       </c>
       <c r="H28" t="n">
-        <v>77.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-27.4</v>
+        <v>-393.12</v>
       </c>
       <c r="K28" t="n">
-        <v>72.73999999999999</v>
+        <v>-68.37</v>
       </c>
       <c r="L28" t="n">
-        <v>77.73</v>
+        <v>399.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:25:48</t>
+          <t>05:28:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="F29" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="G29" t="n">
-        <v>231.3</v>
+        <v>235.9</v>
       </c>
       <c r="H29" t="n">
-        <v>86.3</v>
+        <v>84.8</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>118.94</v>
+        <v>-61.58</v>
       </c>
       <c r="K29" t="n">
-        <v>-149.62</v>
+        <v>6.94</v>
       </c>
       <c r="L29" t="n">
-        <v>191.14</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:27:12</t>
+          <t>05:30:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="F30" t="n">
-        <v>11.49</v>
+        <v>11.35</v>
       </c>
       <c r="G30" t="n">
-        <v>212.8</v>
+        <v>237</v>
       </c>
       <c r="H30" t="n">
-        <v>80.3</v>
+        <v>84.3</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-47.87</v>
+        <v>-36.9</v>
       </c>
       <c r="K30" t="n">
-        <v>-110.27</v>
+        <v>111.71</v>
       </c>
       <c r="L30" t="n">
-        <v>120.21</v>
+        <v>117.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:29:28</t>
+          <t>05:32:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.68</v>
+        <v>3.21</v>
       </c>
       <c r="F31" t="n">
-        <v>12.29</v>
+        <v>12.65</v>
       </c>
       <c r="G31" t="n">
-        <v>226.3</v>
+        <v>221.8</v>
       </c>
       <c r="H31" t="n">
-        <v>77.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>15.73</v>
+        <v>177.45</v>
       </c>
       <c r="K31" t="n">
-        <v>53.45</v>
+        <v>-49.35</v>
       </c>
       <c r="L31" t="n">
-        <v>55.72</v>
+        <v>184.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:33:54</t>
+          <t>05:37:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="F32" t="n">
-        <v>11.73</v>
+        <v>12.51</v>
       </c>
       <c r="G32" t="n">
-        <v>237.2</v>
+        <v>229.1</v>
       </c>
       <c r="H32" t="n">
-        <v>81.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-91.02</v>
+        <v>-66.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-13.95</v>
+        <v>-183.22</v>
       </c>
       <c r="L32" t="n">
-        <v>92.08</v>
+        <v>194.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:35:29</t>
+          <t>05:38:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.36</v>
+        <v>3.56</v>
       </c>
       <c r="F33" t="n">
-        <v>12.17</v>
+        <v>12.21</v>
       </c>
       <c r="G33" t="n">
-        <v>232</v>
+        <v>240.3</v>
       </c>
       <c r="H33" t="n">
-        <v>80.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>46.21</v>
+        <v>-181.01</v>
       </c>
       <c r="K33" t="n">
-        <v>224.03</v>
+        <v>-89.12</v>
       </c>
       <c r="L33" t="n">
-        <v>228.74</v>
+        <v>201.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:36:40</t>
+          <t>05:40:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="F34" t="n">
-        <v>12.72</v>
+        <v>12.12</v>
       </c>
       <c r="G34" t="n">
-        <v>215.6</v>
+        <v>243.3</v>
       </c>
       <c r="H34" t="n">
-        <v>83.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>86.88</v>
+        <v>-67.18000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.13</v>
+        <v>-215.13</v>
       </c>
       <c r="L34" t="n">
-        <v>116.18</v>
+        <v>225.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:40:58</t>
+          <t>05:45:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.33</v>
+        <v>3.74</v>
       </c>
       <c r="F35" t="n">
-        <v>12.91</v>
+        <v>12.7</v>
       </c>
       <c r="G35" t="n">
-        <v>232.2</v>
+        <v>222.1</v>
       </c>
       <c r="H35" t="n">
-        <v>75.2</v>
+        <v>77</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-224.63</v>
+        <v>-375.34</v>
       </c>
       <c r="K35" t="n">
-        <v>41.55</v>
+        <v>235.21</v>
       </c>
       <c r="L35" t="n">
-        <v>228.44</v>
+        <v>442.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:42:03</t>
+          <t>05:48:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="F36" t="n">
-        <v>12.19</v>
+        <v>12.14</v>
       </c>
       <c r="G36" t="n">
-        <v>221</v>
+        <v>233.4</v>
       </c>
       <c r="H36" t="n">
-        <v>82.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-109.15</v>
+        <v>-0.73</v>
       </c>
       <c r="K36" t="n">
-        <v>61.35</v>
+        <v>-33.38</v>
       </c>
       <c r="L36" t="n">
-        <v>125.21</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:43:46</t>
+          <t>05:49:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.62</v>
+        <v>3.18</v>
       </c>
       <c r="F37" t="n">
-        <v>11.86</v>
+        <v>12.66</v>
       </c>
       <c r="G37" t="n">
-        <v>237.5</v>
+        <v>236.6</v>
       </c>
       <c r="H37" t="n">
-        <v>76.5</v>
+        <v>82.7</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>-361.1</v>
+        <v>150.14</v>
       </c>
       <c r="K37" t="n">
-        <v>159.03</v>
+        <v>68.72</v>
       </c>
       <c r="L37" t="n">
-        <v>394.57</v>
+        <v>165.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:49:26</t>
+          <t>05:55:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="F38" t="n">
-        <v>12.16</v>
+        <v>12.15</v>
       </c>
       <c r="G38" t="n">
-        <v>233.8</v>
+        <v>228.5</v>
       </c>
       <c r="H38" t="n">
-        <v>73.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-54.53</v>
+        <v>-173.68</v>
       </c>
       <c r="K38" t="n">
-        <v>225.01</v>
+        <v>20.44</v>
       </c>
       <c r="L38" t="n">
-        <v>231.52</v>
+        <v>174.88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:51:35</t>
+          <t>05:57:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.98</v>
+        <v>3.07</v>
       </c>
       <c r="F39" t="n">
-        <v>12.71</v>
+        <v>12.21</v>
       </c>
       <c r="G39" t="n">
-        <v>232.2</v>
+        <v>232</v>
       </c>
       <c r="H39" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>318.86</v>
+        <v>-351.79</v>
       </c>
       <c r="K39" t="n">
-        <v>197.97</v>
+        <v>385.42</v>
       </c>
       <c r="L39" t="n">
-        <v>375.32</v>
+        <v>521.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:53:16</t>
+          <t>06:00:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="F40" t="n">
-        <v>12.19</v>
+        <v>12.13</v>
       </c>
       <c r="G40" t="n">
-        <v>235.2</v>
+        <v>227.4</v>
       </c>
       <c r="H40" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>434.67</v>
+        <v>130.1</v>
       </c>
       <c r="K40" t="n">
-        <v>14.14</v>
+        <v>-256.07</v>
       </c>
       <c r="L40" t="n">
-        <v>434.9</v>
+        <v>287.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:58:49</t>
+          <t>06:04:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="F41" t="n">
-        <v>12.11</v>
+        <v>12.34</v>
       </c>
       <c r="G41" t="n">
-        <v>227.5</v>
+        <v>232.6</v>
       </c>
       <c r="H41" t="n">
-        <v>79.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>423.41</v>
+        <v>-19.21</v>
       </c>
       <c r="K41" t="n">
-        <v>276.69</v>
+        <v>-305.8</v>
       </c>
       <c r="L41" t="n">
-        <v>505.8</v>
+        <v>306.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:00:09</t>
+          <t>06:05:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.71</v>
+        <v>5.02</v>
       </c>
       <c r="F42" t="n">
-        <v>12.7</v>
+        <v>12.54</v>
       </c>
       <c r="G42" t="n">
-        <v>233.7</v>
+        <v>234.2</v>
       </c>
       <c r="H42" t="n">
-        <v>80</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>349.9</v>
+        <v>-366.82</v>
       </c>
       <c r="K42" t="n">
-        <v>-211.14</v>
+        <v>-148.08</v>
       </c>
       <c r="L42" t="n">
-        <v>408.67</v>
+        <v>395.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:01:17</t>
+          <t>06:07:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.98</v>
+        <v>3.57</v>
       </c>
       <c r="F43" t="n">
-        <v>11.8</v>
+        <v>12.21</v>
       </c>
       <c r="G43" t="n">
-        <v>220</v>
+        <v>229.5</v>
       </c>
       <c r="H43" t="n">
-        <v>78.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-171.91</v>
+        <v>648.11</v>
       </c>
       <c r="K43" t="n">
-        <v>291.23</v>
+        <v>99.39</v>
       </c>
       <c r="L43" t="n">
-        <v>338.19</v>
+        <v>655.6799999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:53</t>
+          <t>06:17:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.42</v>
+        <v>2.93</v>
       </c>
       <c r="F44" t="n">
-        <v>11.89</v>
+        <v>11.84</v>
       </c>
       <c r="G44" t="n">
-        <v>244.4</v>
+        <v>216.5</v>
       </c>
       <c r="H44" t="n">
-        <v>80.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-45.21</v>
+        <v>129.23</v>
       </c>
       <c r="K44" t="n">
-        <v>-84.2</v>
+        <v>100.26</v>
       </c>
       <c r="L44" t="n">
-        <v>95.56999999999999</v>
+        <v>163.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:10:29</t>
+          <t>06:19:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="F45" t="n">
-        <v>11.94</v>
+        <v>12.62</v>
       </c>
       <c r="G45" t="n">
-        <v>226.1</v>
+        <v>230.3</v>
       </c>
       <c r="H45" t="n">
-        <v>77.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>80.92</v>
+        <v>-146.06</v>
       </c>
       <c r="K45" t="n">
-        <v>1.97</v>
+        <v>-97.67</v>
       </c>
       <c r="L45" t="n">
-        <v>80.94</v>
+        <v>175.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:11:28</t>
+          <t>06:20:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="F46" t="n">
-        <v>12.31</v>
+        <v>12.27</v>
       </c>
       <c r="G46" t="n">
-        <v>234.4</v>
+        <v>236.7</v>
       </c>
       <c r="H46" t="n">
-        <v>81.5</v>
+        <v>78.5</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>244.64</v>
+        <v>-121.47</v>
       </c>
       <c r="K46" t="n">
-        <v>119.76</v>
+        <v>-88.43000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>272.38</v>
+        <v>150.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:16:21</t>
+          <t>06:24:02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="F47" t="n">
-        <v>11.91</v>
+        <v>12.69</v>
       </c>
       <c r="G47" t="n">
-        <v>227.9</v>
+        <v>235.4</v>
       </c>
       <c r="H47" t="n">
-        <v>74.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-28.49</v>
+        <v>62.15</v>
       </c>
       <c r="K47" t="n">
-        <v>-113.83</v>
+        <v>-31.58</v>
       </c>
       <c r="L47" t="n">
-        <v>117.34</v>
+        <v>69.70999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:17:33</t>
+          <t>06:26:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.78</v>
+        <v>2.49</v>
       </c>
       <c r="F48" t="n">
-        <v>11.71</v>
+        <v>12.05</v>
       </c>
       <c r="G48" t="n">
-        <v>224.5</v>
+        <v>233.2</v>
       </c>
       <c r="H48" t="n">
-        <v>77</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-88.63</v>
+        <v>17.52</v>
       </c>
       <c r="K48" t="n">
-        <v>234.51</v>
+        <v>-135.55</v>
       </c>
       <c r="L48" t="n">
-        <v>250.7</v>
+        <v>136.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:19:23</t>
+          <t>06:28:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>12.2</v>
+        <v>12.71</v>
       </c>
       <c r="G49" t="n">
-        <v>232.8</v>
+        <v>225.5</v>
       </c>
       <c r="H49" t="n">
-        <v>81.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>244.99</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-123.94</v>
+        <v>-176.14</v>
       </c>
       <c r="L49" t="n">
-        <v>274.55</v>
+        <v>188.95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:25:21</t>
+          <t>06:33:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="F50" t="n">
-        <v>12.24</v>
+        <v>12.7</v>
       </c>
       <c r="G50" t="n">
-        <v>234</v>
+        <v>241.1</v>
       </c>
       <c r="H50" t="n">
-        <v>80.2</v>
+        <v>78.2</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>133.33</v>
+        <v>-27.19</v>
       </c>
       <c r="K50" t="n">
-        <v>205.67</v>
+        <v>-230.14</v>
       </c>
       <c r="L50" t="n">
-        <v>245.11</v>
+        <v>231.74</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:26:58</t>
+          <t>06:34:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.1</v>
+        <v>3.77</v>
       </c>
       <c r="F51" t="n">
-        <v>11.82</v>
+        <v>11.97</v>
       </c>
       <c r="G51" t="n">
-        <v>244.4</v>
+        <v>227.1</v>
       </c>
       <c r="H51" t="n">
-        <v>74.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>29.5</v>
+        <v>132.47</v>
       </c>
       <c r="K51" t="n">
-        <v>-131.01</v>
+        <v>-85.98999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>134.29</v>
+        <v>157.93</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:28:04</t>
+          <t>06:36:02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.23</v>
+        <v>3.84</v>
       </c>
       <c r="F52" t="n">
-        <v>12.04</v>
+        <v>12.29</v>
       </c>
       <c r="G52" t="n">
-        <v>228.4</v>
+        <v>227.1</v>
       </c>
       <c r="H52" t="n">
-        <v>82.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-255.44</v>
+        <v>-203.09</v>
       </c>
       <c r="K52" t="n">
-        <v>-385.17</v>
+        <v>44.15</v>
       </c>
       <c r="L52" t="n">
-        <v>462.17</v>
+        <v>207.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:34:34</t>
+          <t>06:40:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.74</v>
+        <v>3.12</v>
       </c>
       <c r="F53" t="n">
-        <v>12.71</v>
+        <v>12.56</v>
       </c>
       <c r="G53" t="n">
-        <v>238.4</v>
+        <v>236.6</v>
       </c>
       <c r="H53" t="n">
-        <v>85.5</v>
+        <v>72.3</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-93.88</v>
+        <v>-41.91</v>
       </c>
       <c r="K53" t="n">
-        <v>-340.78</v>
+        <v>64.05</v>
       </c>
       <c r="L53" t="n">
-        <v>353.47</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:36:03</t>
+          <t>06:42:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.85</v>
+        <v>3.56</v>
       </c>
       <c r="F54" t="n">
-        <v>12.24</v>
+        <v>12.29</v>
       </c>
       <c r="G54" t="n">
-        <v>225.2</v>
+        <v>234.2</v>
       </c>
       <c r="H54" t="n">
-        <v>74.8</v>
+        <v>83</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-386.48</v>
+        <v>-53.73</v>
       </c>
       <c r="K54" t="n">
-        <v>-161.95</v>
+        <v>-405.04</v>
       </c>
       <c r="L54" t="n">
-        <v>419.04</v>
+        <v>408.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:37:48</t>
+          <t>06:44:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="F55" t="n">
-        <v>12.08</v>
+        <v>12.32</v>
       </c>
       <c r="G55" t="n">
-        <v>237.2</v>
+        <v>230.6</v>
       </c>
       <c r="H55" t="n">
-        <v>79.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-71.61</v>
+        <v>141.04</v>
       </c>
       <c r="K55" t="n">
-        <v>254.24</v>
+        <v>56.23</v>
       </c>
       <c r="L55" t="n">
-        <v>264.14</v>
+        <v>151.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:44:09</t>
+          <t>06:49:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.18</v>
+        <v>3.14</v>
       </c>
       <c r="F56" t="n">
-        <v>12.07</v>
+        <v>12.21</v>
       </c>
       <c r="G56" t="n">
-        <v>228.1</v>
+        <v>224.9</v>
       </c>
       <c r="H56" t="n">
-        <v>79.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-300.73</v>
+        <v>-220.94</v>
       </c>
       <c r="K56" t="n">
-        <v>-1284.81</v>
+        <v>486.9</v>
       </c>
       <c r="L56" t="n">
-        <v>1319.54</v>
+        <v>534.6799999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:46:25</t>
+          <t>06:50:34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.93</v>
+        <v>4.97</v>
       </c>
       <c r="F57" t="n">
-        <v>11.67</v>
+        <v>12.14</v>
       </c>
       <c r="G57" t="n">
-        <v>221.5</v>
+        <v>231.1</v>
       </c>
       <c r="H57" t="n">
-        <v>75.7</v>
+        <v>78.7</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>361.61</v>
+        <v>-91.42</v>
       </c>
       <c r="K57" t="n">
-        <v>177.24</v>
+        <v>-296.54</v>
       </c>
       <c r="L57" t="n">
-        <v>402.71</v>
+        <v>310.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:48:05</t>
+          <t>06:51:49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="F58" t="n">
-        <v>12.62</v>
+        <v>12.14</v>
       </c>
       <c r="G58" t="n">
-        <v>223.7</v>
+        <v>232.2</v>
       </c>
       <c r="H58" t="n">
-        <v>83</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>132.7</v>
+        <v>-332.34</v>
       </c>
       <c r="K58" t="n">
-        <v>348.99</v>
+        <v>-466.41</v>
       </c>
       <c r="L58" t="n">
-        <v>373.37</v>
+        <v>572.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:56:39</t>
+          <t>07:02:48</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2518,31 +2518,31 @@
         <v>3.08</v>
       </c>
       <c r="F59" t="n">
-        <v>12.69</v>
+        <v>12.81</v>
       </c>
       <c r="G59" t="n">
-        <v>230.7</v>
+        <v>235.6</v>
       </c>
       <c r="H59" t="n">
-        <v>78.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-47.16</v>
+        <v>-57.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-42.65</v>
+        <v>-198.94</v>
       </c>
       <c r="L59" t="n">
-        <v>63.59</v>
+        <v>207.15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:58:15</t>
+          <t>07:05:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.68</v>
+        <v>3.51</v>
       </c>
       <c r="F60" t="n">
-        <v>12.2</v>
+        <v>11.39</v>
       </c>
       <c r="G60" t="n">
-        <v>224.1</v>
+        <v>225.2</v>
       </c>
       <c r="H60" t="n">
-        <v>74.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-149.1</v>
+        <v>-161.35</v>
       </c>
       <c r="K60" t="n">
-        <v>-49.75</v>
+        <v>-47.37</v>
       </c>
       <c r="L60" t="n">
-        <v>157.18</v>
+        <v>168.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:59:22</t>
+          <t>07:07:08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.05</v>
+        <v>3.39</v>
       </c>
       <c r="F61" t="n">
-        <v>12.23</v>
+        <v>12.43</v>
       </c>
       <c r="G61" t="n">
-        <v>221.2</v>
+        <v>234.7</v>
       </c>
       <c r="H61" t="n">
-        <v>84.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-90.34999999999999</v>
+        <v>28.55</v>
       </c>
       <c r="K61" t="n">
-        <v>38.48</v>
+        <v>-141.59</v>
       </c>
       <c r="L61" t="n">
-        <v>98.2</v>
+        <v>144.44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:05:10</t>
+          <t>07:11:17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="F62" t="n">
-        <v>12.7</v>
+        <v>12.45</v>
       </c>
       <c r="G62" t="n">
-        <v>237.5</v>
+        <v>228.3</v>
       </c>
       <c r="H62" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>185.7</v>
+        <v>-196.38</v>
       </c>
       <c r="K62" t="n">
-        <v>-98.38</v>
+        <v>96.62</v>
       </c>
       <c r="L62" t="n">
-        <v>210.15</v>
+        <v>218.86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:07:14</t>
+          <t>07:13:23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="F63" t="n">
-        <v>12.74</v>
+        <v>13.15</v>
       </c>
       <c r="G63" t="n">
-        <v>235.6</v>
+        <v>229</v>
       </c>
       <c r="H63" t="n">
-        <v>79.3</v>
+        <v>82.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>92.37</v>
+        <v>19.77</v>
       </c>
       <c r="K63" t="n">
-        <v>60.29</v>
+        <v>-60.72</v>
       </c>
       <c r="L63" t="n">
-        <v>110.31</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:08:35</t>
+          <t>07:14:41</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="F64" t="n">
-        <v>11.79</v>
+        <v>11.76</v>
       </c>
       <c r="G64" t="n">
-        <v>229.2</v>
+        <v>237.1</v>
       </c>
       <c r="H64" t="n">
-        <v>75.7</v>
+        <v>79.7</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>54.98</v>
+        <v>140.64</v>
       </c>
       <c r="K64" t="n">
-        <v>-239.13</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>245.37</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:14:35</t>
+          <t>07:19:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="F65" t="n">
-        <v>12.17</v>
+        <v>13.15</v>
       </c>
       <c r="G65" t="n">
-        <v>228.3</v>
+        <v>231.8</v>
       </c>
       <c r="H65" t="n">
-        <v>84.7</v>
+        <v>79</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-480.47</v>
+        <v>-212.75</v>
       </c>
       <c r="K65" t="n">
-        <v>-72.39</v>
+        <v>162.7</v>
       </c>
       <c r="L65" t="n">
-        <v>485.9</v>
+        <v>267.83</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:16:45</t>
+          <t>07:21:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.98</v>
+        <v>3.63</v>
       </c>
       <c r="F66" t="n">
-        <v>12.84</v>
+        <v>12.28</v>
       </c>
       <c r="G66" t="n">
-        <v>239.3</v>
+        <v>233.5</v>
       </c>
       <c r="H66" t="n">
-        <v>82.8</v>
+        <v>74.8</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>5.28</v>
+        <v>-50</v>
       </c>
       <c r="K66" t="n">
-        <v>-346.55</v>
+        <v>-63.81</v>
       </c>
       <c r="L66" t="n">
-        <v>346.59</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:24</t>
+          <t>07:22:35</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="F67" t="n">
-        <v>12.34</v>
+        <v>12.83</v>
       </c>
       <c r="G67" t="n">
-        <v>229</v>
+        <v>227.7</v>
       </c>
       <c r="H67" t="n">
-        <v>76.2</v>
+        <v>74.8</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>848.8099999999999</v>
+        <v>-39.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-16.14</v>
+        <v>-7.99</v>
       </c>
       <c r="L67" t="n">
-        <v>848.97</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:24:48</t>
+          <t>07:26:43</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="F68" t="n">
-        <v>12.51</v>
+        <v>11.8</v>
       </c>
       <c r="G68" t="n">
-        <v>220.8</v>
+        <v>233.9</v>
       </c>
       <c r="H68" t="n">
-        <v>75.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-122.64</v>
+        <v>296.33</v>
       </c>
       <c r="K68" t="n">
-        <v>286</v>
+        <v>49.08</v>
       </c>
       <c r="L68" t="n">
-        <v>311.18</v>
+        <v>300.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:26:04</t>
+          <t>07:28:06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.06</v>
+        <v>3.88</v>
       </c>
       <c r="F69" t="n">
-        <v>12.25</v>
+        <v>11.79</v>
       </c>
       <c r="G69" t="n">
-        <v>226.6</v>
+        <v>213.4</v>
       </c>
       <c r="H69" t="n">
-        <v>78.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-89.54000000000001</v>
+        <v>-230.52</v>
       </c>
       <c r="K69" t="n">
-        <v>164.88</v>
+        <v>104.83</v>
       </c>
       <c r="L69" t="n">
-        <v>187.63</v>
+        <v>253.24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:28:25</t>
+          <t>07:30:34</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="F70" t="n">
-        <v>11.98</v>
+        <v>12.32</v>
       </c>
       <c r="G70" t="n">
-        <v>247.1</v>
+        <v>221.4</v>
       </c>
       <c r="H70" t="n">
-        <v>83</v>
+        <v>74.5</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>327.54</v>
+        <v>-27.48</v>
       </c>
       <c r="K70" t="n">
-        <v>416.67</v>
+        <v>157.69</v>
       </c>
       <c r="L70" t="n">
-        <v>530</v>
+        <v>160.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:31:59</t>
+          <t>07:36:06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="F71" t="n">
-        <v>12.28</v>
+        <v>12.72</v>
       </c>
       <c r="G71" t="n">
-        <v>233.3</v>
+        <v>237.1</v>
       </c>
       <c r="H71" t="n">
-        <v>77.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>33.13</v>
+        <v>-400.27</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.33</v>
+        <v>399.51</v>
       </c>
       <c r="L71" t="n">
-        <v>33.73</v>
+        <v>565.53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:34:01</t>
+          <t>07:37:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="F72" t="n">
-        <v>11.4</v>
+        <v>12.46</v>
       </c>
       <c r="G72" t="n">
-        <v>226.8</v>
+        <v>240.8</v>
       </c>
       <c r="H72" t="n">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>344.76</v>
+        <v>714.7</v>
       </c>
       <c r="K72" t="n">
-        <v>-165.23</v>
+        <v>276.8</v>
       </c>
       <c r="L72" t="n">
-        <v>382.31</v>
+        <v>766.4299999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:35:59</t>
+          <t>07:39:31</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="F73" t="n">
-        <v>12.43</v>
+        <v>12.73</v>
       </c>
       <c r="G73" t="n">
-        <v>222.5</v>
+        <v>238</v>
       </c>
       <c r="H73" t="n">
-        <v>81.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-91.72</v>
+        <v>-342.37</v>
       </c>
       <c r="K73" t="n">
-        <v>607.1900000000001</v>
+        <v>-217.23</v>
       </c>
       <c r="L73" t="n">
-        <v>614.08</v>
+        <v>405.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:47:04</t>
+          <t>07:49:41</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.9</v>
+        <v>4.48</v>
       </c>
       <c r="F74" t="n">
-        <v>12.15</v>
+        <v>12.64</v>
       </c>
       <c r="G74" t="n">
-        <v>234</v>
+        <v>224.9</v>
       </c>
       <c r="H74" t="n">
-        <v>79.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-56.89</v>
+        <v>119.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-62.27</v>
+        <v>-221.81</v>
       </c>
       <c r="L74" t="n">
-        <v>84.34</v>
+        <v>252.13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:48:03</t>
+          <t>07:50:43</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.44</v>
+        <v>4.16</v>
       </c>
       <c r="F75" t="n">
-        <v>12.3</v>
+        <v>12.63</v>
       </c>
       <c r="G75" t="n">
-        <v>242.3</v>
+        <v>221.4</v>
       </c>
       <c r="H75" t="n">
-        <v>76.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.39</v>
+        <v>-48.59</v>
       </c>
       <c r="K75" t="n">
-        <v>-53.16</v>
+        <v>-103.2</v>
       </c>
       <c r="L75" t="n">
-        <v>71.20999999999999</v>
+        <v>114.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:49:24</t>
+          <t>07:52:42</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="F76" t="n">
-        <v>12.96</v>
+        <v>12.74</v>
       </c>
       <c r="G76" t="n">
-        <v>227.2</v>
+        <v>226.6</v>
       </c>
       <c r="H76" t="n">
-        <v>79.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.22</v>
+        <v>-103.28</v>
       </c>
       <c r="K76" t="n">
-        <v>73.06</v>
+        <v>18.79</v>
       </c>
       <c r="L76" t="n">
-        <v>73.13</v>
+        <v>104.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:54:16</t>
+          <t>07:57:20</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.16</v>
+        <v>3.41</v>
       </c>
       <c r="F77" t="n">
-        <v>12.37</v>
+        <v>13.2</v>
       </c>
       <c r="G77" t="n">
-        <v>235.6</v>
+        <v>228.4</v>
       </c>
       <c r="H77" t="n">
-        <v>85.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>2.6</v>
+        <v>66.91</v>
       </c>
       <c r="K77" t="n">
-        <v>208.1</v>
+        <v>-7.44</v>
       </c>
       <c r="L77" t="n">
-        <v>208.11</v>
+        <v>67.31999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:56:01</t>
+          <t>07:59:08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="F78" t="n">
-        <v>12.5</v>
+        <v>12.46</v>
       </c>
       <c r="G78" t="n">
-        <v>228.7</v>
+        <v>233.4</v>
       </c>
       <c r="H78" t="n">
-        <v>77.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>194.68</v>
+        <v>-396.9</v>
       </c>
       <c r="K78" t="n">
-        <v>12.84</v>
+        <v>258.07</v>
       </c>
       <c r="L78" t="n">
-        <v>195.1</v>
+        <v>473.42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:57:02</t>
+          <t>08:00:03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.59</v>
+        <v>4.58</v>
       </c>
       <c r="F79" t="n">
-        <v>11.72</v>
+        <v>12.97</v>
       </c>
       <c r="G79" t="n">
-        <v>241.4</v>
+        <v>238.9</v>
       </c>
       <c r="H79" t="n">
-        <v>83.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>42.62</v>
+        <v>-335.4</v>
       </c>
       <c r="K79" t="n">
-        <v>86.92</v>
+        <v>205.57</v>
       </c>
       <c r="L79" t="n">
-        <v>96.81</v>
+        <v>393.38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:01:41</t>
+          <t>08:06:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.29</v>
+        <v>3.83</v>
       </c>
       <c r="F80" t="n">
-        <v>12.2</v>
+        <v>12.31</v>
       </c>
       <c r="G80" t="n">
-        <v>234.1</v>
+        <v>221.9</v>
       </c>
       <c r="H80" t="n">
-        <v>76.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>308.17</v>
+        <v>326.82</v>
       </c>
       <c r="K80" t="n">
-        <v>75.88</v>
+        <v>-167.97</v>
       </c>
       <c r="L80" t="n">
-        <v>317.37</v>
+        <v>367.46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:03:15</t>
+          <t>08:07:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.73</v>
+        <v>3.43</v>
       </c>
       <c r="F81" t="n">
-        <v>12.37</v>
+        <v>12.49</v>
       </c>
       <c r="G81" t="n">
-        <v>234.5</v>
+        <v>228</v>
       </c>
       <c r="H81" t="n">
-        <v>85.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>24</v>
+        <v>-183.27</v>
       </c>
       <c r="K81" t="n">
-        <v>516.61</v>
+        <v>-86.95</v>
       </c>
       <c r="L81" t="n">
-        <v>517.17</v>
+        <v>202.85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:04:29</t>
+          <t>08:08:31</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.23</v>
+        <v>3.37</v>
       </c>
       <c r="F82" t="n">
-        <v>12.44</v>
+        <v>12.06</v>
       </c>
       <c r="G82" t="n">
-        <v>229</v>
+        <v>246.7</v>
       </c>
       <c r="H82" t="n">
-        <v>82.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>408.38</v>
+        <v>-15.5</v>
       </c>
       <c r="K82" t="n">
-        <v>-126.34</v>
+        <v>-205.54</v>
       </c>
       <c r="L82" t="n">
-        <v>427.48</v>
+        <v>206.12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:08:59</t>
+          <t>08:13:23</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.04</v>
+        <v>2.95</v>
       </c>
       <c r="F83" t="n">
-        <v>12.57</v>
+        <v>12.07</v>
       </c>
       <c r="G83" t="n">
-        <v>221.2</v>
+        <v>216.2</v>
       </c>
       <c r="H83" t="n">
-        <v>80.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>631.74</v>
+        <v>-50.1</v>
       </c>
       <c r="K83" t="n">
-        <v>-24.53</v>
+        <v>27.43</v>
       </c>
       <c r="L83" t="n">
-        <v>632.22</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:10:15</t>
+          <t>08:14:53</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="F84" t="n">
-        <v>12.29</v>
+        <v>12.44</v>
       </c>
       <c r="G84" t="n">
-        <v>240.7</v>
+        <v>230.1</v>
       </c>
       <c r="H84" t="n">
         <v>75.8</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>16.09</v>
+        <v>-316.6</v>
       </c>
       <c r="K84" t="n">
-        <v>-264.84</v>
+        <v>-298.46</v>
       </c>
       <c r="L84" t="n">
-        <v>265.33</v>
+        <v>435.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:12:08</t>
+          <t>08:16:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="F85" t="n">
-        <v>12.32</v>
+        <v>12.18</v>
       </c>
       <c r="G85" t="n">
-        <v>240.9</v>
+        <v>241.5</v>
       </c>
       <c r="H85" t="n">
-        <v>84</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>106.96</v>
+        <v>-544.3099999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>312.79</v>
+        <v>408.69</v>
       </c>
       <c r="L85" t="n">
-        <v>330.57</v>
+        <v>680.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:15:51</t>
+          <t>08:21:24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.48</v>
+        <v>5.16</v>
       </c>
       <c r="F86" t="n">
-        <v>12.41</v>
+        <v>11.8</v>
       </c>
       <c r="G86" t="n">
-        <v>243.1</v>
+        <v>231</v>
       </c>
       <c r="H86" t="n">
-        <v>78</v>
+        <v>81.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>435.69</v>
+        <v>-334.07</v>
       </c>
       <c r="K86" t="n">
-        <v>201.09</v>
+        <v>-285.6</v>
       </c>
       <c r="L86" t="n">
-        <v>479.86</v>
+        <v>439.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:18:11</t>
+          <t>08:22:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.1</v>
+        <v>3.63</v>
       </c>
       <c r="F87" t="n">
-        <v>12.63</v>
+        <v>12.31</v>
       </c>
       <c r="G87" t="n">
-        <v>240.7</v>
+        <v>227</v>
       </c>
       <c r="H87" t="n">
-        <v>77.8</v>
+        <v>81</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>267.07</v>
+        <v>-322.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-903.72</v>
+        <v>538.37</v>
       </c>
       <c r="L87" t="n">
-        <v>942.36</v>
+        <v>627.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:19:11</t>
+          <t>08:24:14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,25 +3736,25 @@
         <v>3.61</v>
       </c>
       <c r="F88" t="n">
-        <v>12.15</v>
+        <v>11.94</v>
       </c>
       <c r="G88" t="n">
-        <v>230.7</v>
+        <v>236.8</v>
       </c>
       <c r="H88" t="n">
-        <v>84.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-193.86</v>
+        <v>293.34</v>
       </c>
       <c r="K88" t="n">
-        <v>105.63</v>
+        <v>-126.39</v>
       </c>
       <c r="L88" t="n">
-        <v>220.76</v>
+        <v>319.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>109.31</v>
+        <v>119.5</v>
       </c>
       <c r="K14" t="n">
-        <v>137.89</v>
+        <v>150.75</v>
       </c>
       <c r="L14" t="n">
-        <v>175.96</v>
+        <v>192.37</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.78</v>
+        <v>-11.15</v>
       </c>
       <c r="K15" t="n">
-        <v>143.47</v>
+        <v>108.23</v>
       </c>
       <c r="L15" t="n">
-        <v>144.23</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>74.83</v>
+        <v>76.41</v>
       </c>
       <c r="K16" t="n">
-        <v>-107.78</v>
+        <v>-110.06</v>
       </c>
       <c r="L16" t="n">
-        <v>131.21</v>
+        <v>133.98</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-28.46</v>
+        <v>-26.69</v>
       </c>
       <c r="K17" t="n">
-        <v>-197.39</v>
+        <v>-185.06</v>
       </c>
       <c r="L17" t="n">
-        <v>199.43</v>
+        <v>186.98</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-23.64</v>
+        <v>-18.4</v>
       </c>
       <c r="K18" t="n">
-        <v>-238.79</v>
+        <v>-185.82</v>
       </c>
       <c r="L18" t="n">
-        <v>239.96</v>
+        <v>186.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-79.06</v>
+        <v>-92.33</v>
       </c>
       <c r="K19" t="n">
-        <v>131.54</v>
+        <v>153.63</v>
       </c>
       <c r="L19" t="n">
-        <v>153.47</v>
+        <v>179.24</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-111.85</v>
+        <v>-117.42</v>
       </c>
       <c r="K20" t="n">
-        <v>111.11</v>
+        <v>116.64</v>
       </c>
       <c r="L20" t="n">
-        <v>157.65</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>23.83</v>
+        <v>59.57</v>
       </c>
       <c r="K21" t="n">
-        <v>-58.72</v>
+        <v>-146.78</v>
       </c>
       <c r="L21" t="n">
-        <v>63.37</v>
+        <v>158.41</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-224.79</v>
+        <v>-276.4</v>
       </c>
       <c r="K22" t="n">
-        <v>-70.70999999999999</v>
+        <v>-86.95</v>
       </c>
       <c r="L22" t="n">
-        <v>235.65</v>
+        <v>289.76</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-330.41</v>
+        <v>-354.24</v>
       </c>
       <c r="K23" t="n">
-        <v>471.49</v>
+        <v>505.5</v>
       </c>
       <c r="L23" t="n">
-        <v>575.74</v>
+        <v>617.27</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>43.53</v>
+        <v>63.81</v>
       </c>
       <c r="K24" t="n">
-        <v>167.19</v>
+        <v>245.12</v>
       </c>
       <c r="L24" t="n">
-        <v>172.76</v>
+        <v>253.29</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>58.16</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>282.72</v>
+        <v>329.86</v>
       </c>
       <c r="L25" t="n">
-        <v>288.63</v>
+        <v>336.76</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>78.14</v>
+        <v>115.44</v>
       </c>
       <c r="K26" t="n">
-        <v>216.36</v>
+        <v>319.61</v>
       </c>
       <c r="L26" t="n">
-        <v>230.03</v>
+        <v>339.82</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>122.23</v>
+        <v>251.69</v>
       </c>
       <c r="K27" t="n">
-        <v>-90.94</v>
+        <v>-187.26</v>
       </c>
       <c r="L27" t="n">
-        <v>152.35</v>
+        <v>313.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-393.12</v>
+        <v>-412.91</v>
       </c>
       <c r="K28" t="n">
-        <v>-68.37</v>
+        <v>-71.81</v>
       </c>
       <c r="L28" t="n">
-        <v>399.02</v>
+        <v>419.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-61.58</v>
+        <v>-99.29000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>6.94</v>
+        <v>11.19</v>
       </c>
       <c r="L29" t="n">
-        <v>61.97</v>
+        <v>99.92</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-36.9</v>
+        <v>-34.68</v>
       </c>
       <c r="K30" t="n">
-        <v>111.71</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
-        <v>117.64</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>177.45</v>
+        <v>159.93</v>
       </c>
       <c r="K31" t="n">
-        <v>-49.35</v>
+        <v>-44.47</v>
       </c>
       <c r="L31" t="n">
-        <v>184.18</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-66.19</v>
+        <v>-59.93</v>
       </c>
       <c r="K32" t="n">
-        <v>-183.22</v>
+        <v>-165.92</v>
       </c>
       <c r="L32" t="n">
-        <v>194.81</v>
+        <v>176.41</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-181.01</v>
+        <v>-191.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-89.12</v>
+        <v>-94.23</v>
       </c>
       <c r="L33" t="n">
-        <v>201.76</v>
+        <v>213.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-67.18000000000001</v>
+        <v>-67.11</v>
       </c>
       <c r="K34" t="n">
-        <v>-215.13</v>
+        <v>-214.89</v>
       </c>
       <c r="L34" t="n">
-        <v>225.37</v>
+        <v>225.13</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-375.34</v>
+        <v>-411.23</v>
       </c>
       <c r="K35" t="n">
-        <v>235.21</v>
+        <v>257.7</v>
       </c>
       <c r="L35" t="n">
-        <v>442.95</v>
+        <v>485.3</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.73</v>
+        <v>-2.36</v>
       </c>
       <c r="K36" t="n">
-        <v>-33.38</v>
+        <v>-108.08</v>
       </c>
       <c r="L36" t="n">
-        <v>33.39</v>
+        <v>108.11</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>150.14</v>
+        <v>201.55</v>
       </c>
       <c r="K37" t="n">
-        <v>68.72</v>
+        <v>92.25</v>
       </c>
       <c r="L37" t="n">
-        <v>165.12</v>
+        <v>221.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-173.68</v>
+        <v>-247.42</v>
       </c>
       <c r="K38" t="n">
-        <v>20.44</v>
+        <v>29.12</v>
       </c>
       <c r="L38" t="n">
-        <v>174.88</v>
+        <v>249.12</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-351.79</v>
+        <v>-322.98</v>
       </c>
       <c r="K39" t="n">
-        <v>385.42</v>
+        <v>353.85</v>
       </c>
       <c r="L39" t="n">
-        <v>521.83</v>
+        <v>479.09</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>130.1</v>
+        <v>136.92</v>
       </c>
       <c r="K40" t="n">
-        <v>-256.07</v>
+        <v>-269.47</v>
       </c>
       <c r="L40" t="n">
-        <v>287.23</v>
+        <v>302.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.21</v>
+        <v>-27.88</v>
       </c>
       <c r="K41" t="n">
-        <v>-305.8</v>
+        <v>-443.77</v>
       </c>
       <c r="L41" t="n">
-        <v>306.41</v>
+        <v>444.65</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-366.82</v>
+        <v>-544.46</v>
       </c>
       <c r="K42" t="n">
-        <v>-148.08</v>
+        <v>-219.79</v>
       </c>
       <c r="L42" t="n">
-        <v>395.58</v>
+        <v>587.15</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>648.11</v>
+        <v>817.84</v>
       </c>
       <c r="K43" t="n">
-        <v>99.39</v>
+        <v>125.42</v>
       </c>
       <c r="L43" t="n">
-        <v>655.6799999999999</v>
+        <v>827.4</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>129.23</v>
+        <v>103.66</v>
       </c>
       <c r="K44" t="n">
-        <v>100.26</v>
+        <v>80.42</v>
       </c>
       <c r="L44" t="n">
-        <v>163.56</v>
+        <v>131.19</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-146.06</v>
+        <v>-132.56</v>
       </c>
       <c r="K45" t="n">
-        <v>-97.67</v>
+        <v>-88.64</v>
       </c>
       <c r="L45" t="n">
-        <v>175.71</v>
+        <v>159.47</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-121.47</v>
+        <v>-124.13</v>
       </c>
       <c r="K46" t="n">
-        <v>-88.43000000000001</v>
+        <v>-90.36</v>
       </c>
       <c r="L46" t="n">
-        <v>150.25</v>
+        <v>153.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>62.15</v>
+        <v>73.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-31.58</v>
+        <v>-37.56</v>
       </c>
       <c r="L47" t="n">
-        <v>69.70999999999999</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>17.52</v>
+        <v>17.54</v>
       </c>
       <c r="K48" t="n">
-        <v>-135.55</v>
+        <v>-135.71</v>
       </c>
       <c r="L48" t="n">
-        <v>136.68</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-68.40000000000001</v>
+        <v>-69.04000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-176.14</v>
+        <v>-177.8</v>
       </c>
       <c r="L49" t="n">
-        <v>188.95</v>
+        <v>190.74</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-27.19</v>
+        <v>-29.13</v>
       </c>
       <c r="K50" t="n">
-        <v>-230.14</v>
+        <v>-246.53</v>
       </c>
       <c r="L50" t="n">
-        <v>231.74</v>
+        <v>248.25</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>132.47</v>
+        <v>187.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.98999999999999</v>
+        <v>-121.76</v>
       </c>
       <c r="L51" t="n">
-        <v>157.93</v>
+        <v>223.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-203.09</v>
+        <v>-266.73</v>
       </c>
       <c r="K52" t="n">
-        <v>44.15</v>
+        <v>57.99</v>
       </c>
       <c r="L52" t="n">
-        <v>207.84</v>
+        <v>272.96</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-41.91</v>
+        <v>-113.05</v>
       </c>
       <c r="K53" t="n">
-        <v>64.05</v>
+        <v>172.78</v>
       </c>
       <c r="L53" t="n">
-        <v>76.54000000000001</v>
+        <v>206.48</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-53.73</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-405.04</v>
+        <v>-485.72</v>
       </c>
       <c r="L54" t="n">
-        <v>408.59</v>
+        <v>489.98</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>141.04</v>
+        <v>190.8</v>
       </c>
       <c r="K55" t="n">
-        <v>56.23</v>
+        <v>76.06</v>
       </c>
       <c r="L55" t="n">
-        <v>151.84</v>
+        <v>205.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-220.94</v>
+        <v>-254.07</v>
       </c>
       <c r="K56" t="n">
-        <v>486.9</v>
+        <v>559.92</v>
       </c>
       <c r="L56" t="n">
-        <v>534.6799999999999</v>
+        <v>614.86</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-91.42</v>
+        <v>-178.51</v>
       </c>
       <c r="K57" t="n">
-        <v>-296.54</v>
+        <v>-579.05</v>
       </c>
       <c r="L57" t="n">
-        <v>310.32</v>
+        <v>605.95</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-332.34</v>
+        <v>-409.31</v>
       </c>
       <c r="K58" t="n">
-        <v>-466.41</v>
+        <v>-574.4299999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>572.7</v>
+        <v>705.34</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-57.73</v>
+        <v>-50.19</v>
       </c>
       <c r="K59" t="n">
-        <v>-198.94</v>
+        <v>-172.93</v>
       </c>
       <c r="L59" t="n">
-        <v>207.15</v>
+        <v>180.06</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-161.35</v>
+        <v>-154.18</v>
       </c>
       <c r="K60" t="n">
-        <v>-47.37</v>
+        <v>-45.26</v>
       </c>
       <c r="L60" t="n">
-        <v>168.16</v>
+        <v>160.68</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>28.55</v>
+        <v>30.18</v>
       </c>
       <c r="K61" t="n">
-        <v>-141.59</v>
+        <v>-149.67</v>
       </c>
       <c r="L61" t="n">
-        <v>144.44</v>
+        <v>152.68</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-196.38</v>
+        <v>-184.05</v>
       </c>
       <c r="K62" t="n">
-        <v>96.62</v>
+        <v>90.56</v>
       </c>
       <c r="L62" t="n">
-        <v>218.86</v>
+        <v>205.12</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>19.77</v>
+        <v>39.48</v>
       </c>
       <c r="K63" t="n">
-        <v>-60.72</v>
+        <v>-121.26</v>
       </c>
       <c r="L63" t="n">
-        <v>63.86</v>
+        <v>127.52</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>140.64</v>
+        <v>158.77</v>
       </c>
       <c r="K64" t="n">
-        <v>86.01000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>164.85</v>
+        <v>186.11</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-212.75</v>
+        <v>-209.45</v>
       </c>
       <c r="K65" t="n">
-        <v>162.7</v>
+        <v>160.17</v>
       </c>
       <c r="L65" t="n">
-        <v>267.83</v>
+        <v>263.68</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-50</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-63.81</v>
+        <v>-122.89</v>
       </c>
       <c r="L66" t="n">
-        <v>81.06999999999999</v>
+        <v>156.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-39.91</v>
+        <v>-114.08</v>
       </c>
       <c r="K67" t="n">
-        <v>-7.99</v>
+        <v>-22.85</v>
       </c>
       <c r="L67" t="n">
-        <v>40.71</v>
+        <v>116.34</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>296.33</v>
+        <v>268.86</v>
       </c>
       <c r="K68" t="n">
-        <v>49.08</v>
+        <v>44.53</v>
       </c>
       <c r="L68" t="n">
-        <v>300.37</v>
+        <v>272.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-230.52</v>
+        <v>-314.55</v>
       </c>
       <c r="K69" t="n">
-        <v>104.83</v>
+        <v>143.04</v>
       </c>
       <c r="L69" t="n">
-        <v>253.24</v>
+        <v>345.54</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-27.48</v>
+        <v>-48.21</v>
       </c>
       <c r="K70" t="n">
-        <v>157.69</v>
+        <v>276.65</v>
       </c>
       <c r="L70" t="n">
-        <v>160.06</v>
+        <v>280.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-400.27</v>
+        <v>-477.39</v>
       </c>
       <c r="K71" t="n">
-        <v>399.51</v>
+        <v>476.49</v>
       </c>
       <c r="L71" t="n">
-        <v>565.53</v>
+        <v>674.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>714.7</v>
+        <v>765.91</v>
       </c>
       <c r="K72" t="n">
-        <v>276.8</v>
+        <v>296.63</v>
       </c>
       <c r="L72" t="n">
-        <v>766.4299999999999</v>
+        <v>821.34</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-342.37</v>
+        <v>-445.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-217.23</v>
+        <v>-282.8</v>
       </c>
       <c r="L73" t="n">
-        <v>405.47</v>
+        <v>527.85</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>119.86</v>
+        <v>117.79</v>
       </c>
       <c r="K74" t="n">
-        <v>-221.81</v>
+        <v>-217.96</v>
       </c>
       <c r="L74" t="n">
-        <v>252.13</v>
+        <v>247.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-48.59</v>
+        <v>-58.47</v>
       </c>
       <c r="K75" t="n">
-        <v>-103.2</v>
+        <v>-124.19</v>
       </c>
       <c r="L75" t="n">
-        <v>114.06</v>
+        <v>137.26</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-103.28</v>
+        <v>-135.62</v>
       </c>
       <c r="K76" t="n">
-        <v>18.79</v>
+        <v>24.68</v>
       </c>
       <c r="L76" t="n">
-        <v>104.98</v>
+        <v>137.84</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>66.91</v>
+        <v>116.66</v>
       </c>
       <c r="K77" t="n">
-        <v>-7.44</v>
+        <v>-12.97</v>
       </c>
       <c r="L77" t="n">
-        <v>67.31999999999999</v>
+        <v>117.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-396.9</v>
+        <v>-345.15</v>
       </c>
       <c r="K78" t="n">
-        <v>258.07</v>
+        <v>224.42</v>
       </c>
       <c r="L78" t="n">
-        <v>473.42</v>
+        <v>411.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-335.4</v>
+        <v>-295.44</v>
       </c>
       <c r="K79" t="n">
-        <v>205.57</v>
+        <v>181.08</v>
       </c>
       <c r="L79" t="n">
-        <v>393.38</v>
+        <v>346.51</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>326.82</v>
+        <v>334.35</v>
       </c>
       <c r="K80" t="n">
-        <v>-167.97</v>
+        <v>-171.84</v>
       </c>
       <c r="L80" t="n">
-        <v>367.46</v>
+        <v>375.92</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-183.27</v>
+        <v>-207.53</v>
       </c>
       <c r="K81" t="n">
-        <v>-86.95</v>
+        <v>-98.45999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>202.85</v>
+        <v>229.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-15.5</v>
+        <v>-20.72</v>
       </c>
       <c r="K82" t="n">
-        <v>-205.54</v>
+        <v>-274.69</v>
       </c>
       <c r="L82" t="n">
-        <v>206.12</v>
+        <v>275.47</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-50.1</v>
+        <v>-142.28</v>
       </c>
       <c r="K83" t="n">
-        <v>27.43</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>57.12</v>
+        <v>162.21</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-316.6</v>
+        <v>-400.05</v>
       </c>
       <c r="K84" t="n">
-        <v>-298.46</v>
+        <v>-377.13</v>
       </c>
       <c r="L84" t="n">
-        <v>435.1</v>
+        <v>549.79</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-544.3099999999999</v>
+        <v>-475.3</v>
       </c>
       <c r="K85" t="n">
-        <v>408.69</v>
+        <v>356.87</v>
       </c>
       <c r="L85" t="n">
-        <v>680.66</v>
+        <v>594.37</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-334.07</v>
+        <v>-561.66</v>
       </c>
       <c r="K86" t="n">
-        <v>-285.6</v>
+        <v>-480.16</v>
       </c>
       <c r="L86" t="n">
-        <v>439.51</v>
+        <v>738.9299999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-322.14</v>
+        <v>-412.58</v>
       </c>
       <c r="K87" t="n">
-        <v>538.37</v>
+        <v>689.52</v>
       </c>
       <c r="L87" t="n">
-        <v>627.39</v>
+        <v>803.53</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>293.34</v>
+        <v>403.26</v>
       </c>
       <c r="K88" t="n">
-        <v>-126.39</v>
+        <v>-173.75</v>
       </c>
       <c r="L88" t="n">
-        <v>319.41</v>
+        <v>439.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>119.5</v>
+        <v>87.44</v>
       </c>
       <c r="K14" t="n">
-        <v>150.75</v>
+        <v>110.3</v>
       </c>
       <c r="L14" t="n">
-        <v>192.37</v>
+        <v>140.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.15</v>
+        <v>-9.66</v>
       </c>
       <c r="K15" t="n">
-        <v>108.23</v>
+        <v>93.77</v>
       </c>
       <c r="L15" t="n">
-        <v>108.8</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>76.41</v>
+        <v>59.27</v>
       </c>
       <c r="K16" t="n">
-        <v>-110.06</v>
+        <v>-85.37</v>
       </c>
       <c r="L16" t="n">
-        <v>133.98</v>
+        <v>103.93</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-26.69</v>
+        <v>-21.24</v>
       </c>
       <c r="K17" t="n">
-        <v>-185.06</v>
+        <v>-147.3</v>
       </c>
       <c r="L17" t="n">
-        <v>186.98</v>
+        <v>148.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-18.4</v>
+        <v>-16.7</v>
       </c>
       <c r="K18" t="n">
-        <v>-185.82</v>
+        <v>-168.69</v>
       </c>
       <c r="L18" t="n">
-        <v>186.73</v>
+        <v>169.52</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-92.33</v>
+        <v>-67.27</v>
       </c>
       <c r="K19" t="n">
-        <v>153.63</v>
+        <v>111.93</v>
       </c>
       <c r="L19" t="n">
-        <v>179.24</v>
+        <v>130.59</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-117.42</v>
+        <v>-82.03</v>
       </c>
       <c r="K20" t="n">
-        <v>116.64</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>165.5</v>
+        <v>115.63</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>59.57</v>
+        <v>40.03</v>
       </c>
       <c r="K21" t="n">
-        <v>-146.78</v>
+        <v>-98.64</v>
       </c>
       <c r="L21" t="n">
-        <v>158.41</v>
+        <v>106.45</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-276.4</v>
+        <v>-179.59</v>
       </c>
       <c r="K22" t="n">
-        <v>-86.95</v>
+        <v>-56.49</v>
       </c>
       <c r="L22" t="n">
-        <v>289.76</v>
+        <v>188.26</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-354.24</v>
+        <v>-209.24</v>
       </c>
       <c r="K23" t="n">
-        <v>505.5</v>
+        <v>298.58</v>
       </c>
       <c r="L23" t="n">
-        <v>617.27</v>
+        <v>364.6</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>63.81</v>
+        <v>38.41</v>
       </c>
       <c r="K24" t="n">
-        <v>245.12</v>
+        <v>147.55</v>
       </c>
       <c r="L24" t="n">
-        <v>253.29</v>
+        <v>152.46</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>67.84999999999999</v>
+        <v>41.9</v>
       </c>
       <c r="K25" t="n">
-        <v>329.86</v>
+        <v>203.71</v>
       </c>
       <c r="L25" t="n">
-        <v>336.76</v>
+        <v>207.98</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>115.44</v>
+        <v>66.16</v>
       </c>
       <c r="K26" t="n">
-        <v>319.61</v>
+        <v>183.16</v>
       </c>
       <c r="L26" t="n">
-        <v>339.82</v>
+        <v>194.74</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>251.69</v>
+        <v>144.29</v>
       </c>
       <c r="K27" t="n">
-        <v>-187.26</v>
+        <v>-107.35</v>
       </c>
       <c r="L27" t="n">
-        <v>313.72</v>
+        <v>179.85</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-412.91</v>
+        <v>-251.95</v>
       </c>
       <c r="K28" t="n">
-        <v>-71.81</v>
+        <v>-43.82</v>
       </c>
       <c r="L28" t="n">
-        <v>419.11</v>
+        <v>255.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-99.29000000000001</v>
+        <v>-74.91</v>
       </c>
       <c r="K29" t="n">
-        <v>11.19</v>
+        <v>8.44</v>
       </c>
       <c r="L29" t="n">
-        <v>99.92</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-34.68</v>
+        <v>-31.7</v>
       </c>
       <c r="K30" t="n">
-        <v>105</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>110.58</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>159.93</v>
+        <v>133.12</v>
       </c>
       <c r="K31" t="n">
-        <v>-44.47</v>
+        <v>-37.02</v>
       </c>
       <c r="L31" t="n">
-        <v>166</v>
+        <v>138.17</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-59.93</v>
+        <v>-47.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-165.92</v>
+        <v>-131.01</v>
       </c>
       <c r="L32" t="n">
-        <v>176.41</v>
+        <v>139.29</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-191.4</v>
+        <v>-142.71</v>
       </c>
       <c r="K33" t="n">
-        <v>-94.23</v>
+        <v>-70.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>213.34</v>
+        <v>159.07</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-67.11</v>
+        <v>-49.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-214.89</v>
+        <v>-157.55</v>
       </c>
       <c r="L34" t="n">
-        <v>225.13</v>
+        <v>165.06</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-411.23</v>
+        <v>-247.63</v>
       </c>
       <c r="K35" t="n">
-        <v>257.7</v>
+        <v>155.18</v>
       </c>
       <c r="L35" t="n">
-        <v>485.3</v>
+        <v>292.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.36</v>
+        <v>-1.77</v>
       </c>
       <c r="K36" t="n">
-        <v>-108.08</v>
+        <v>-80.90000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>108.11</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>201.55</v>
+        <v>133.67</v>
       </c>
       <c r="K37" t="n">
-        <v>92.25</v>
+        <v>61.19</v>
       </c>
       <c r="L37" t="n">
-        <v>221.66</v>
+        <v>147.01</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-247.42</v>
+        <v>-150.1</v>
       </c>
       <c r="K38" t="n">
-        <v>29.12</v>
+        <v>17.67</v>
       </c>
       <c r="L38" t="n">
-        <v>249.12</v>
+        <v>151.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-322.98</v>
+        <v>-214.84</v>
       </c>
       <c r="K39" t="n">
-        <v>353.85</v>
+        <v>235.38</v>
       </c>
       <c r="L39" t="n">
-        <v>479.09</v>
+        <v>318.68</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>136.92</v>
+        <v>92.52</v>
       </c>
       <c r="K40" t="n">
-        <v>-269.47</v>
+        <v>-182.09</v>
       </c>
       <c r="L40" t="n">
-        <v>302.26</v>
+        <v>204.24</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-27.88</v>
+        <v>-15.44</v>
       </c>
       <c r="K41" t="n">
-        <v>-443.77</v>
+        <v>-245.78</v>
       </c>
       <c r="L41" t="n">
-        <v>444.65</v>
+        <v>246.27</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-544.46</v>
+        <v>-316.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-219.79</v>
+        <v>-127.9</v>
       </c>
       <c r="L42" t="n">
-        <v>587.15</v>
+        <v>341.65</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>817.84</v>
+        <v>402.94</v>
       </c>
       <c r="K43" t="n">
-        <v>125.42</v>
+        <v>61.79</v>
       </c>
       <c r="L43" t="n">
-        <v>827.4</v>
+        <v>407.65</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>103.66</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>80.42</v>
+        <v>74.59</v>
       </c>
       <c r="L44" t="n">
-        <v>131.19</v>
+        <v>121.69</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-132.56</v>
+        <v>-103.44</v>
       </c>
       <c r="K45" t="n">
-        <v>-88.64</v>
+        <v>-69.17</v>
       </c>
       <c r="L45" t="n">
-        <v>159.47</v>
+        <v>124.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-124.13</v>
+        <v>-96.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-90.36</v>
+        <v>-70.31</v>
       </c>
       <c r="L46" t="n">
-        <v>153.53</v>
+        <v>119.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>73.92</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.56</v>
+        <v>-34.79</v>
       </c>
       <c r="L47" t="n">
-        <v>82.91</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>17.54</v>
+        <v>13.39</v>
       </c>
       <c r="K48" t="n">
-        <v>-135.71</v>
+        <v>-103.59</v>
       </c>
       <c r="L48" t="n">
-        <v>136.84</v>
+        <v>104.45</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-69.04000000000001</v>
+        <v>-58.94</v>
       </c>
       <c r="K49" t="n">
-        <v>-177.8</v>
+        <v>-151.79</v>
       </c>
       <c r="L49" t="n">
-        <v>190.74</v>
+        <v>162.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.13</v>
+        <v>-19.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-246.53</v>
+        <v>-164.28</v>
       </c>
       <c r="L50" t="n">
-        <v>248.25</v>
+        <v>165.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>187.58</v>
+        <v>129.83</v>
       </c>
       <c r="K51" t="n">
-        <v>-121.76</v>
+        <v>-84.28</v>
       </c>
       <c r="L51" t="n">
-        <v>223.63</v>
+        <v>154.79</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-266.73</v>
+        <v>-177.05</v>
       </c>
       <c r="K52" t="n">
-        <v>57.99</v>
+        <v>38.49</v>
       </c>
       <c r="L52" t="n">
-        <v>272.96</v>
+        <v>181.18</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-113.05</v>
+        <v>-64.47</v>
       </c>
       <c r="K53" t="n">
-        <v>172.78</v>
+        <v>98.53</v>
       </c>
       <c r="L53" t="n">
-        <v>206.48</v>
+        <v>117.74</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-64.43000000000001</v>
+        <v>-36.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-485.72</v>
+        <v>-278.76</v>
       </c>
       <c r="L54" t="n">
-        <v>489.98</v>
+        <v>281.2</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>190.8</v>
+        <v>129.82</v>
       </c>
       <c r="K55" t="n">
-        <v>76.06</v>
+        <v>51.75</v>
       </c>
       <c r="L55" t="n">
-        <v>205.41</v>
+        <v>139.76</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-254.07</v>
+        <v>-141.32</v>
       </c>
       <c r="K56" t="n">
-        <v>559.92</v>
+        <v>311.44</v>
       </c>
       <c r="L56" t="n">
-        <v>614.86</v>
+        <v>342.01</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-178.51</v>
+        <v>-88.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-579.05</v>
+        <v>-287.16</v>
       </c>
       <c r="L57" t="n">
-        <v>605.95</v>
+        <v>300.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-409.31</v>
+        <v>-210.55</v>
       </c>
       <c r="K58" t="n">
-        <v>-574.4299999999999</v>
+        <v>-295.49</v>
       </c>
       <c r="L58" t="n">
-        <v>705.34</v>
+        <v>362.83</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-50.19</v>
+        <v>-40.78</v>
       </c>
       <c r="K59" t="n">
-        <v>-172.93</v>
+        <v>-140.52</v>
       </c>
       <c r="L59" t="n">
-        <v>180.06</v>
+        <v>146.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-154.18</v>
+        <v>-130.44</v>
       </c>
       <c r="K60" t="n">
-        <v>-45.26</v>
+        <v>-38.29</v>
       </c>
       <c r="L60" t="n">
-        <v>160.68</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>30.18</v>
+        <v>23.88</v>
       </c>
       <c r="K61" t="n">
-        <v>-149.67</v>
+        <v>-118.47</v>
       </c>
       <c r="L61" t="n">
-        <v>152.68</v>
+        <v>120.85</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-184.05</v>
+        <v>-138.4</v>
       </c>
       <c r="K62" t="n">
-        <v>90.56</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>205.12</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>39.48</v>
+        <v>27.55</v>
       </c>
       <c r="K63" t="n">
-        <v>-121.26</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>127.52</v>
+        <v>88.97</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>158.77</v>
+        <v>115.86</v>
       </c>
       <c r="K64" t="n">
-        <v>97.09999999999999</v>
+        <v>70.86</v>
       </c>
       <c r="L64" t="n">
-        <v>186.11</v>
+        <v>135.81</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-209.45</v>
+        <v>-160.84</v>
       </c>
       <c r="K65" t="n">
-        <v>160.17</v>
+        <v>123</v>
       </c>
       <c r="L65" t="n">
-        <v>263.68</v>
+        <v>202.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-96.29000000000001</v>
+        <v>-69.93000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-122.89</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>156.11</v>
+        <v>113.39</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-114.08</v>
+        <v>-87.45999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-22.85</v>
+        <v>-17.52</v>
       </c>
       <c r="L67" t="n">
-        <v>116.34</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>268.86</v>
+        <v>196.25</v>
       </c>
       <c r="K68" t="n">
-        <v>44.53</v>
+        <v>32.5</v>
       </c>
       <c r="L68" t="n">
-        <v>272.52</v>
+        <v>198.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-314.55</v>
+        <v>-199.58</v>
       </c>
       <c r="K69" t="n">
-        <v>143.04</v>
+        <v>90.75</v>
       </c>
       <c r="L69" t="n">
-        <v>345.54</v>
+        <v>219.24</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-48.21</v>
+        <v>-27.92</v>
       </c>
       <c r="K70" t="n">
-        <v>276.65</v>
+        <v>160.24</v>
       </c>
       <c r="L70" t="n">
-        <v>280.81</v>
+        <v>162.65</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-477.39</v>
+        <v>-276.37</v>
       </c>
       <c r="K71" t="n">
-        <v>476.49</v>
+        <v>275.84</v>
       </c>
       <c r="L71" t="n">
-        <v>674.49</v>
+        <v>390.47</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>765.91</v>
+        <v>421.3</v>
       </c>
       <c r="K72" t="n">
-        <v>296.63</v>
+        <v>163.17</v>
       </c>
       <c r="L72" t="n">
-        <v>821.34</v>
+        <v>451.8</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-445.7</v>
+        <v>-245.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-282.8</v>
+        <v>-156.03</v>
       </c>
       <c r="L73" t="n">
-        <v>527.85</v>
+        <v>291.24</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>117.79</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-217.96</v>
+        <v>-175.66</v>
       </c>
       <c r="L74" t="n">
-        <v>247.75</v>
+        <v>199.67</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-58.47</v>
+        <v>-49.77</v>
       </c>
       <c r="K75" t="n">
-        <v>-124.19</v>
+        <v>-105.72</v>
       </c>
       <c r="L75" t="n">
-        <v>137.26</v>
+        <v>116.85</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-135.62</v>
+        <v>-110.6</v>
       </c>
       <c r="K76" t="n">
-        <v>24.68</v>
+        <v>20.13</v>
       </c>
       <c r="L76" t="n">
-        <v>137.84</v>
+        <v>112.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>116.66</v>
+        <v>85</v>
       </c>
       <c r="K77" t="n">
-        <v>-12.97</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>117.38</v>
+        <v>85.52</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-345.15</v>
+        <v>-248.94</v>
       </c>
       <c r="K78" t="n">
-        <v>224.42</v>
+        <v>161.86</v>
       </c>
       <c r="L78" t="n">
-        <v>411.69</v>
+        <v>296.94</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-295.44</v>
+        <v>-247.08</v>
       </c>
       <c r="K79" t="n">
-        <v>181.08</v>
+        <v>151.44</v>
       </c>
       <c r="L79" t="n">
-        <v>346.51</v>
+        <v>289.8</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>334.35</v>
+        <v>230.8</v>
       </c>
       <c r="K80" t="n">
-        <v>-171.84</v>
+        <v>-118.62</v>
       </c>
       <c r="L80" t="n">
-        <v>375.92</v>
+        <v>259.49</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-207.53</v>
+        <v>-152.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-98.45999999999999</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>229.7</v>
+        <v>168.57</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-20.72</v>
+        <v>-12.71</v>
       </c>
       <c r="K82" t="n">
-        <v>-274.69</v>
+        <v>-168.56</v>
       </c>
       <c r="L82" t="n">
-        <v>275.47</v>
+        <v>169.04</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-142.28</v>
+        <v>-88.15000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>77.90000000000001</v>
+        <v>48.26</v>
       </c>
       <c r="L83" t="n">
-        <v>162.21</v>
+        <v>100.49</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-400.05</v>
+        <v>-213.95</v>
       </c>
       <c r="K84" t="n">
-        <v>-377.13</v>
+        <v>-201.69</v>
       </c>
       <c r="L84" t="n">
-        <v>549.79</v>
+        <v>294.03</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-475.3</v>
+        <v>-324.47</v>
       </c>
       <c r="K85" t="n">
-        <v>356.87</v>
+        <v>243.62</v>
       </c>
       <c r="L85" t="n">
-        <v>594.37</v>
+        <v>405.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-561.66</v>
+        <v>-277.11</v>
       </c>
       <c r="K86" t="n">
-        <v>-480.16</v>
+        <v>-236.9</v>
       </c>
       <c r="L86" t="n">
-        <v>738.9299999999999</v>
+        <v>364.57</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-412.58</v>
+        <v>-202.79</v>
       </c>
       <c r="K87" t="n">
-        <v>689.52</v>
+        <v>338.92</v>
       </c>
       <c r="L87" t="n">
-        <v>803.53</v>
+        <v>394.96</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>403.26</v>
+        <v>238.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-173.75</v>
+        <v>-102.55</v>
       </c>
       <c r="L88" t="n">
-        <v>439.1</v>
+        <v>259.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>87.44</v>
+        <v>90.72</v>
       </c>
       <c r="K14" t="n">
-        <v>110.3</v>
+        <v>114.45</v>
       </c>
       <c r="L14" t="n">
-        <v>140.75</v>
+        <v>146.04</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.66</v>
+        <v>-9.99</v>
       </c>
       <c r="K15" t="n">
-        <v>93.77</v>
+        <v>96.97</v>
       </c>
       <c r="L15" t="n">
-        <v>94.27</v>
+        <v>97.48</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>59.27</v>
+        <v>61.35</v>
       </c>
       <c r="K16" t="n">
-        <v>-85.37</v>
+        <v>-88.36</v>
       </c>
       <c r="L16" t="n">
-        <v>103.93</v>
+        <v>107.56</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-21.24</v>
+        <v>-22.69</v>
       </c>
       <c r="K17" t="n">
-        <v>-147.3</v>
+        <v>-157.34</v>
       </c>
       <c r="L17" t="n">
-        <v>148.83</v>
+        <v>158.97</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-16.7</v>
+        <v>-17.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-168.69</v>
+        <v>-177.23</v>
       </c>
       <c r="L18" t="n">
-        <v>169.52</v>
+        <v>178.1</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-67.27</v>
+        <v>-72.54000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>111.93</v>
+        <v>120.7</v>
       </c>
       <c r="L19" t="n">
-        <v>130.59</v>
+        <v>140.82</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-82.03</v>
+        <v>-91.8</v>
       </c>
       <c r="K20" t="n">
-        <v>81.48999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="L20" t="n">
-        <v>115.63</v>
+        <v>129.39</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>40.03</v>
+        <v>44.17</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.64</v>
+        <v>-108.83</v>
       </c>
       <c r="L21" t="n">
-        <v>106.45</v>
+        <v>117.46</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-179.59</v>
+        <v>-197.31</v>
       </c>
       <c r="K22" t="n">
-        <v>-56.49</v>
+        <v>-62.07</v>
       </c>
       <c r="L22" t="n">
-        <v>188.26</v>
+        <v>206.84</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-209.24</v>
+        <v>-233.41</v>
       </c>
       <c r="K23" t="n">
-        <v>298.58</v>
+        <v>333.07</v>
       </c>
       <c r="L23" t="n">
-        <v>364.6</v>
+        <v>406.71</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>38.41</v>
+        <v>43.25</v>
       </c>
       <c r="K24" t="n">
-        <v>147.55</v>
+        <v>166.14</v>
       </c>
       <c r="L24" t="n">
-        <v>152.46</v>
+        <v>171.68</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>41.9</v>
+        <v>47.33</v>
       </c>
       <c r="K25" t="n">
-        <v>203.71</v>
+        <v>230.11</v>
       </c>
       <c r="L25" t="n">
-        <v>207.98</v>
+        <v>234.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>66.16</v>
+        <v>75.48</v>
       </c>
       <c r="K26" t="n">
-        <v>183.16</v>
+        <v>208.97</v>
       </c>
       <c r="L26" t="n">
-        <v>194.74</v>
+        <v>222.18</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>144.29</v>
+        <v>163.16</v>
       </c>
       <c r="K27" t="n">
-        <v>-107.35</v>
+        <v>-121.39</v>
       </c>
       <c r="L27" t="n">
-        <v>179.85</v>
+        <v>203.36</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-251.95</v>
+        <v>-285.17</v>
       </c>
       <c r="K28" t="n">
-        <v>-43.82</v>
+        <v>-49.59</v>
       </c>
       <c r="L28" t="n">
-        <v>255.73</v>
+        <v>289.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-74.91</v>
+        <v>-78.12</v>
       </c>
       <c r="K29" t="n">
-        <v>8.44</v>
+        <v>8.81</v>
       </c>
       <c r="L29" t="n">
-        <v>75.38</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-31.7</v>
+        <v>-32.2</v>
       </c>
       <c r="K30" t="n">
-        <v>95.95999999999999</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>101.06</v>
+        <v>102.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>133.12</v>
+        <v>135.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.02</v>
+        <v>-37.58</v>
       </c>
       <c r="L31" t="n">
-        <v>138.17</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-47.32</v>
+        <v>-50.24</v>
       </c>
       <c r="K32" t="n">
-        <v>-131.01</v>
+        <v>-139.07</v>
       </c>
       <c r="L32" t="n">
-        <v>139.29</v>
+        <v>147.86</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-142.71</v>
+        <v>-152.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-70.26000000000001</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>159.07</v>
+        <v>170.39</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-49.2</v>
+        <v>-53.05</v>
       </c>
       <c r="K34" t="n">
-        <v>-157.55</v>
+        <v>-169.88</v>
       </c>
       <c r="L34" t="n">
-        <v>165.06</v>
+        <v>177.97</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-247.63</v>
+        <v>-275.1</v>
       </c>
       <c r="K35" t="n">
-        <v>155.18</v>
+        <v>172.39</v>
       </c>
       <c r="L35" t="n">
-        <v>292.23</v>
+        <v>324.66</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.77</v>
+        <v>-1.9</v>
       </c>
       <c r="K36" t="n">
-        <v>-80.90000000000001</v>
+        <v>-87.01000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>80.92</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>133.67</v>
+        <v>148.2</v>
       </c>
       <c r="K37" t="n">
-        <v>61.19</v>
+        <v>67.84</v>
       </c>
       <c r="L37" t="n">
-        <v>147.01</v>
+        <v>162.99</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-150.1</v>
+        <v>-171.64</v>
       </c>
       <c r="K38" t="n">
-        <v>17.67</v>
+        <v>20.2</v>
       </c>
       <c r="L38" t="n">
-        <v>151.14</v>
+        <v>172.82</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-214.84</v>
+        <v>-240.68</v>
       </c>
       <c r="K39" t="n">
-        <v>235.38</v>
+        <v>263.69</v>
       </c>
       <c r="L39" t="n">
-        <v>318.68</v>
+        <v>357.01</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>92.52</v>
+        <v>103.56</v>
       </c>
       <c r="K40" t="n">
-        <v>-182.09</v>
+        <v>-203.82</v>
       </c>
       <c r="L40" t="n">
-        <v>204.24</v>
+        <v>228.62</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.44</v>
+        <v>-17.4</v>
       </c>
       <c r="K41" t="n">
-        <v>-245.78</v>
+        <v>-277.02</v>
       </c>
       <c r="L41" t="n">
-        <v>246.27</v>
+        <v>277.56</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-316.81</v>
+        <v>-358.21</v>
       </c>
       <c r="K42" t="n">
-        <v>-127.9</v>
+        <v>-144.61</v>
       </c>
       <c r="L42" t="n">
-        <v>341.65</v>
+        <v>386.3</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>402.94</v>
+        <v>467.46</v>
       </c>
       <c r="K43" t="n">
-        <v>61.79</v>
+        <v>71.69</v>
       </c>
       <c r="L43" t="n">
-        <v>407.65</v>
+        <v>472.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>96.15000000000001</v>
+        <v>96.42</v>
       </c>
       <c r="K44" t="n">
-        <v>74.59</v>
+        <v>74.81</v>
       </c>
       <c r="L44" t="n">
-        <v>121.69</v>
+        <v>122.04</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-103.44</v>
+        <v>-105.6</v>
       </c>
       <c r="K45" t="n">
-        <v>-69.17</v>
+        <v>-70.61</v>
       </c>
       <c r="L45" t="n">
-        <v>124.44</v>
+        <v>127.03</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-96.59</v>
+        <v>-99.41</v>
       </c>
       <c r="K46" t="n">
-        <v>-70.31</v>
+        <v>-72.37</v>
       </c>
       <c r="L46" t="n">
-        <v>119.47</v>
+        <v>122.96</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>68.45999999999999</v>
+        <v>70.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-34.79</v>
+        <v>-35.62</v>
       </c>
       <c r="L47" t="n">
-        <v>76.79000000000001</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>13.39</v>
+        <v>14.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-103.59</v>
+        <v>-110.84</v>
       </c>
       <c r="L48" t="n">
-        <v>104.45</v>
+        <v>111.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-58.94</v>
+        <v>-61.35</v>
       </c>
       <c r="K49" t="n">
-        <v>-151.79</v>
+        <v>-157.99</v>
       </c>
       <c r="L49" t="n">
-        <v>162.83</v>
+        <v>169.49</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-19.41</v>
+        <v>-21.49</v>
       </c>
       <c r="K50" t="n">
-        <v>-164.28</v>
+        <v>-181.93</v>
       </c>
       <c r="L50" t="n">
-        <v>165.42</v>
+        <v>183.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>129.83</v>
+        <v>142.68</v>
       </c>
       <c r="K51" t="n">
-        <v>-84.28</v>
+        <v>-92.62</v>
       </c>
       <c r="L51" t="n">
-        <v>154.79</v>
+        <v>170.11</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-177.05</v>
+        <v>-194.72</v>
       </c>
       <c r="K52" t="n">
-        <v>38.49</v>
+        <v>42.33</v>
       </c>
       <c r="L52" t="n">
-        <v>181.18</v>
+        <v>199.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-64.47</v>
+        <v>-72.27</v>
       </c>
       <c r="K53" t="n">
-        <v>98.53</v>
+        <v>110.46</v>
       </c>
       <c r="L53" t="n">
-        <v>117.74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-36.98</v>
+        <v>-41.94</v>
       </c>
       <c r="K54" t="n">
-        <v>-278.76</v>
+        <v>-316.14</v>
       </c>
       <c r="L54" t="n">
-        <v>281.2</v>
+        <v>318.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>129.82</v>
+        <v>146.22</v>
       </c>
       <c r="K55" t="n">
-        <v>51.75</v>
+        <v>58.29</v>
       </c>
       <c r="L55" t="n">
-        <v>139.76</v>
+        <v>157.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-141.32</v>
+        <v>-159.93</v>
       </c>
       <c r="K56" t="n">
-        <v>311.44</v>
+        <v>352.45</v>
       </c>
       <c r="L56" t="n">
-        <v>342.01</v>
+        <v>387.04</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-88.52</v>
+        <v>-103.2</v>
       </c>
       <c r="K57" t="n">
-        <v>-287.16</v>
+        <v>-334.77</v>
       </c>
       <c r="L57" t="n">
-        <v>300.49</v>
+        <v>350.32</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-210.55</v>
+        <v>-241.17</v>
       </c>
       <c r="K58" t="n">
-        <v>-295.49</v>
+        <v>-338.46</v>
       </c>
       <c r="L58" t="n">
-        <v>362.83</v>
+        <v>415.6</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-40.78</v>
+        <v>-41.43</v>
       </c>
       <c r="K59" t="n">
-        <v>-140.52</v>
+        <v>-142.75</v>
       </c>
       <c r="L59" t="n">
-        <v>146.32</v>
+        <v>148.64</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-130.44</v>
+        <v>-133.25</v>
       </c>
       <c r="K60" t="n">
-        <v>-38.29</v>
+        <v>-39.12</v>
       </c>
       <c r="L60" t="n">
-        <v>135.94</v>
+        <v>138.87</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>23.88</v>
+        <v>24.49</v>
       </c>
       <c r="K61" t="n">
-        <v>-118.47</v>
+        <v>-121.45</v>
       </c>
       <c r="L61" t="n">
-        <v>120.85</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-138.4</v>
+        <v>-148.56</v>
       </c>
       <c r="K62" t="n">
-        <v>68.09999999999999</v>
+        <v>73.09</v>
       </c>
       <c r="L62" t="n">
-        <v>154.25</v>
+        <v>165.57</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>27.55</v>
+        <v>29.84</v>
       </c>
       <c r="K63" t="n">
-        <v>-84.59999999999999</v>
+        <v>-91.64</v>
       </c>
       <c r="L63" t="n">
-        <v>88.97</v>
+        <v>96.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>115.86</v>
+        <v>124.7</v>
       </c>
       <c r="K64" t="n">
-        <v>70.86</v>
+        <v>76.27</v>
       </c>
       <c r="L64" t="n">
-        <v>135.81</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-160.84</v>
+        <v>-173.66</v>
       </c>
       <c r="K65" t="n">
-        <v>123</v>
+        <v>132.81</v>
       </c>
       <c r="L65" t="n">
-        <v>202.48</v>
+        <v>218.63</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-69.93000000000001</v>
+        <v>-75.52</v>
       </c>
       <c r="K66" t="n">
-        <v>-89.26000000000001</v>
+        <v>-96.38</v>
       </c>
       <c r="L66" t="n">
-        <v>113.39</v>
+        <v>122.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-87.45999999999999</v>
+        <v>-93.90000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-17.52</v>
+        <v>-18.81</v>
       </c>
       <c r="L67" t="n">
-        <v>89.2</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>196.25</v>
+        <v>218.07</v>
       </c>
       <c r="K68" t="n">
-        <v>32.5</v>
+        <v>36.11</v>
       </c>
       <c r="L68" t="n">
-        <v>198.92</v>
+        <v>221.04</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-199.58</v>
+        <v>-220.74</v>
       </c>
       <c r="K69" t="n">
-        <v>90.75</v>
+        <v>100.38</v>
       </c>
       <c r="L69" t="n">
-        <v>219.24</v>
+        <v>242.49</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-27.92</v>
+        <v>-31.26</v>
       </c>
       <c r="K70" t="n">
-        <v>160.24</v>
+        <v>179.38</v>
       </c>
       <c r="L70" t="n">
-        <v>162.65</v>
+        <v>182.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-276.37</v>
+        <v>-316.13</v>
       </c>
       <c r="K71" t="n">
-        <v>275.84</v>
+        <v>315.53</v>
       </c>
       <c r="L71" t="n">
-        <v>390.47</v>
+        <v>446.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>421.3</v>
+        <v>479.04</v>
       </c>
       <c r="K72" t="n">
-        <v>163.17</v>
+        <v>185.53</v>
       </c>
       <c r="L72" t="n">
-        <v>451.8</v>
+        <v>513.71</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-245.91</v>
+        <v>-277.46</v>
       </c>
       <c r="K73" t="n">
-        <v>-156.03</v>
+        <v>-176.05</v>
       </c>
       <c r="L73" t="n">
-        <v>291.24</v>
+        <v>328.6</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>94.93000000000001</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-175.66</v>
+        <v>-183.64</v>
       </c>
       <c r="L74" t="n">
-        <v>199.67</v>
+        <v>208.74</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-49.77</v>
+        <v>-51.47</v>
       </c>
       <c r="K75" t="n">
-        <v>-105.72</v>
+        <v>-109.32</v>
       </c>
       <c r="L75" t="n">
-        <v>116.85</v>
+        <v>120.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-110.6</v>
+        <v>-114.91</v>
       </c>
       <c r="K76" t="n">
-        <v>20.13</v>
+        <v>20.91</v>
       </c>
       <c r="L76" t="n">
-        <v>112.42</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>85</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-9.449999999999999</v>
+        <v>-10.21</v>
       </c>
       <c r="L77" t="n">
-        <v>85.52</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-248.94</v>
+        <v>-267.39</v>
       </c>
       <c r="K78" t="n">
-        <v>161.86</v>
+        <v>173.86</v>
       </c>
       <c r="L78" t="n">
-        <v>296.94</v>
+        <v>318.94</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-247.08</v>
+        <v>-258.28</v>
       </c>
       <c r="K79" t="n">
-        <v>151.44</v>
+        <v>158.3</v>
       </c>
       <c r="L79" t="n">
-        <v>289.8</v>
+        <v>302.93</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>230.8</v>
+        <v>250.01</v>
       </c>
       <c r="K80" t="n">
-        <v>-118.62</v>
+        <v>-128.49</v>
       </c>
       <c r="L80" t="n">
-        <v>259.49</v>
+        <v>281.1</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-152.3</v>
+        <v>-166.02</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.26000000000001</v>
+        <v>-78.77</v>
       </c>
       <c r="L81" t="n">
-        <v>168.57</v>
+        <v>183.76</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-12.71</v>
+        <v>-14.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-168.56</v>
+        <v>-188.34</v>
       </c>
       <c r="L82" t="n">
-        <v>169.04</v>
+        <v>188.88</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-88.15000000000001</v>
+        <v>-98.98</v>
       </c>
       <c r="K83" t="n">
-        <v>48.26</v>
+        <v>54.19</v>
       </c>
       <c r="L83" t="n">
-        <v>100.49</v>
+        <v>112.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-213.95</v>
+        <v>-242.85</v>
       </c>
       <c r="K84" t="n">
-        <v>-201.69</v>
+        <v>-228.93</v>
       </c>
       <c r="L84" t="n">
-        <v>294.03</v>
+        <v>333.75</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-324.47</v>
+        <v>-356.71</v>
       </c>
       <c r="K85" t="n">
-        <v>243.62</v>
+        <v>267.83</v>
       </c>
       <c r="L85" t="n">
-        <v>405.75</v>
+        <v>446.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-277.11</v>
+        <v>-323.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-236.9</v>
+        <v>-276.48</v>
       </c>
       <c r="L86" t="n">
-        <v>364.57</v>
+        <v>425.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-202.79</v>
+        <v>-235.72</v>
       </c>
       <c r="K87" t="n">
-        <v>338.92</v>
+        <v>393.94</v>
       </c>
       <c r="L87" t="n">
-        <v>394.96</v>
+        <v>459.07</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>238.02</v>
+        <v>266.93</v>
       </c>
       <c r="K88" t="n">
-        <v>-102.55</v>
+        <v>-115.01</v>
       </c>
       <c r="L88" t="n">
-        <v>259.17</v>
+        <v>290.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>90.72</v>
+        <v>45.4</v>
       </c>
       <c r="K14" t="n">
-        <v>114.45</v>
+        <v>57.27</v>
       </c>
       <c r="L14" t="n">
-        <v>146.04</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.99</v>
+        <v>-6.6</v>
       </c>
       <c r="K15" t="n">
-        <v>96.97</v>
+        <v>64.09</v>
       </c>
       <c r="L15" t="n">
-        <v>97.48</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>61.35</v>
+        <v>35.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-88.36</v>
+        <v>-50.78</v>
       </c>
       <c r="L16" t="n">
-        <v>107.56</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-22.69</v>
+        <v>-12.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-157.34</v>
+        <v>-86.12</v>
       </c>
       <c r="L17" t="n">
-        <v>158.97</v>
+        <v>87.01000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-17.55</v>
+        <v>-9.76</v>
       </c>
       <c r="K18" t="n">
-        <v>-177.23</v>
+        <v>-98.56</v>
       </c>
       <c r="L18" t="n">
-        <v>178.1</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-72.54000000000001</v>
+        <v>-37.77</v>
       </c>
       <c r="K19" t="n">
-        <v>120.7</v>
+        <v>62.85</v>
       </c>
       <c r="L19" t="n">
-        <v>140.82</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-91.8</v>
+        <v>-62.47</v>
       </c>
       <c r="K20" t="n">
-        <v>91.19</v>
+        <v>62.06</v>
       </c>
       <c r="L20" t="n">
-        <v>129.39</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>44.17</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-108.83</v>
+        <v>-20.6</v>
       </c>
       <c r="L21" t="n">
-        <v>117.46</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-197.31</v>
+        <v>-99.92</v>
       </c>
       <c r="K22" t="n">
-        <v>-62.07</v>
+        <v>-31.43</v>
       </c>
       <c r="L22" t="n">
-        <v>206.84</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-233.41</v>
+        <v>-122.32</v>
       </c>
       <c r="K23" t="n">
-        <v>333.07</v>
+        <v>174.55</v>
       </c>
       <c r="L23" t="n">
-        <v>406.71</v>
+        <v>213.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>43.25</v>
+        <v>26.47</v>
       </c>
       <c r="K24" t="n">
-        <v>166.14</v>
+        <v>101.69</v>
       </c>
       <c r="L24" t="n">
-        <v>171.68</v>
+        <v>105.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>47.33</v>
+        <v>28.4</v>
       </c>
       <c r="K25" t="n">
-        <v>230.11</v>
+        <v>138.08</v>
       </c>
       <c r="L25" t="n">
-        <v>234.93</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>75.48</v>
+        <v>47.49</v>
       </c>
       <c r="K26" t="n">
-        <v>208.97</v>
+        <v>131.5</v>
       </c>
       <c r="L26" t="n">
-        <v>222.18</v>
+        <v>139.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>163.16</v>
+        <v>92.19</v>
       </c>
       <c r="K27" t="n">
-        <v>-121.39</v>
+        <v>-68.59</v>
       </c>
       <c r="L27" t="n">
-        <v>203.36</v>
+        <v>114.91</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-285.17</v>
+        <v>-190.93</v>
       </c>
       <c r="K28" t="n">
-        <v>-49.59</v>
+        <v>-33.2</v>
       </c>
       <c r="L28" t="n">
-        <v>289.45</v>
+        <v>193.8</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-78.12</v>
+        <v>-43.08</v>
       </c>
       <c r="K29" t="n">
-        <v>8.81</v>
+        <v>4.86</v>
       </c>
       <c r="L29" t="n">
-        <v>78.61</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.2</v>
+        <v>-18.02</v>
       </c>
       <c r="K30" t="n">
-        <v>97.48999999999999</v>
+        <v>54.55</v>
       </c>
       <c r="L30" t="n">
-        <v>102.67</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>135.13</v>
+        <v>74.11</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.58</v>
+        <v>-20.61</v>
       </c>
       <c r="L31" t="n">
-        <v>140.25</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-50.24</v>
+        <v>-29.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-139.07</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>147.86</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-152.87</v>
+        <v>-77.11</v>
       </c>
       <c r="K33" t="n">
-        <v>-75.26000000000001</v>
+        <v>-37.96</v>
       </c>
       <c r="L33" t="n">
-        <v>170.39</v>
+        <v>85.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-53.05</v>
+        <v>-28.12</v>
       </c>
       <c r="K34" t="n">
-        <v>-169.88</v>
+        <v>-90.05</v>
       </c>
       <c r="L34" t="n">
-        <v>177.97</v>
+        <v>94.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-275.1</v>
+        <v>-137.63</v>
       </c>
       <c r="K35" t="n">
-        <v>172.39</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>324.66</v>
+        <v>162.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.9</v>
+        <v>-0.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-87.01000000000001</v>
+        <v>-2.35</v>
       </c>
       <c r="L36" t="n">
-        <v>87.03</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>148.2</v>
+        <v>77.47</v>
       </c>
       <c r="K37" t="n">
-        <v>67.84</v>
+        <v>35.46</v>
       </c>
       <c r="L37" t="n">
-        <v>162.99</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-171.64</v>
+        <v>-106.57</v>
       </c>
       <c r="K38" t="n">
-        <v>20.2</v>
+        <v>12.54</v>
       </c>
       <c r="L38" t="n">
-        <v>172.82</v>
+        <v>107.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-240.68</v>
+        <v>-142.75</v>
       </c>
       <c r="K39" t="n">
-        <v>263.69</v>
+        <v>156.4</v>
       </c>
       <c r="L39" t="n">
-        <v>357.01</v>
+        <v>211.75</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>103.56</v>
+        <v>63.28</v>
       </c>
       <c r="K40" t="n">
-        <v>-203.82</v>
+        <v>-124.55</v>
       </c>
       <c r="L40" t="n">
-        <v>228.62</v>
+        <v>139.71</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.4</v>
+        <v>-9.92</v>
       </c>
       <c r="K41" t="n">
-        <v>-277.02</v>
+        <v>-157.86</v>
       </c>
       <c r="L41" t="n">
-        <v>277.56</v>
+        <v>158.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-358.21</v>
+        <v>-190.84</v>
       </c>
       <c r="K42" t="n">
-        <v>-144.61</v>
+        <v>-77.04000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>386.3</v>
+        <v>205.81</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>467.46</v>
+        <v>260.25</v>
       </c>
       <c r="K43" t="n">
-        <v>71.69</v>
+        <v>39.91</v>
       </c>
       <c r="L43" t="n">
-        <v>472.93</v>
+        <v>263.29</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>96.42</v>
+        <v>55.14</v>
       </c>
       <c r="K44" t="n">
-        <v>74.81</v>
+        <v>42.78</v>
       </c>
       <c r="L44" t="n">
-        <v>122.04</v>
+        <v>69.79000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-105.6</v>
+        <v>-61.2</v>
       </c>
       <c r="K45" t="n">
-        <v>-70.61</v>
+        <v>-40.92</v>
       </c>
       <c r="L45" t="n">
-        <v>127.03</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-99.41</v>
+        <v>-54.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-72.37</v>
+        <v>-39.85</v>
       </c>
       <c r="L46" t="n">
-        <v>122.96</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>70.08</v>
+        <v>40.86</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.62</v>
+        <v>-20.76</v>
       </c>
       <c r="L47" t="n">
-        <v>78.61</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>14.33</v>
+        <v>8.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-110.84</v>
+        <v>-69.54000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>111.76</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-61.35</v>
+        <v>-28.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-157.99</v>
+        <v>-73.34999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>169.49</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.49</v>
+        <v>-12.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-181.93</v>
+        <v>-104.88</v>
       </c>
       <c r="L50" t="n">
-        <v>183.2</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>142.68</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-92.62</v>
+        <v>-46.26</v>
       </c>
       <c r="L51" t="n">
-        <v>170.11</v>
+        <v>84.95999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-194.72</v>
+        <v>-96.88</v>
       </c>
       <c r="K52" t="n">
-        <v>42.33</v>
+        <v>21.06</v>
       </c>
       <c r="L52" t="n">
-        <v>199.27</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-72.27</v>
+        <v>-20.52</v>
       </c>
       <c r="K53" t="n">
-        <v>110.46</v>
+        <v>31.37</v>
       </c>
       <c r="L53" t="n">
-        <v>132</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-41.94</v>
+        <v>-22.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-316.14</v>
+        <v>-170.6</v>
       </c>
       <c r="L54" t="n">
-        <v>318.91</v>
+        <v>172.09</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>146.22</v>
+        <v>90.5</v>
       </c>
       <c r="K55" t="n">
-        <v>58.29</v>
+        <v>36.08</v>
       </c>
       <c r="L55" t="n">
-        <v>157.41</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-159.93</v>
+        <v>-92.36</v>
       </c>
       <c r="K56" t="n">
-        <v>352.45</v>
+        <v>203.53</v>
       </c>
       <c r="L56" t="n">
-        <v>387.04</v>
+        <v>223.51</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-103.2</v>
+        <v>-54.89</v>
       </c>
       <c r="K57" t="n">
-        <v>-334.77</v>
+        <v>-178.06</v>
       </c>
       <c r="L57" t="n">
-        <v>350.32</v>
+        <v>186.33</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-241.17</v>
+        <v>-136.35</v>
       </c>
       <c r="K58" t="n">
-        <v>-338.46</v>
+        <v>-191.36</v>
       </c>
       <c r="L58" t="n">
-        <v>415.6</v>
+        <v>234.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-41.43</v>
+        <v>-23.14</v>
       </c>
       <c r="K59" t="n">
-        <v>-142.75</v>
+        <v>-79.75</v>
       </c>
       <c r="L59" t="n">
-        <v>148.64</v>
+        <v>83.04000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-133.25</v>
+        <v>-67.84</v>
       </c>
       <c r="K60" t="n">
-        <v>-39.12</v>
+        <v>-19.92</v>
       </c>
       <c r="L60" t="n">
-        <v>138.87</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>24.49</v>
+        <v>12.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-121.45</v>
+        <v>-63.77</v>
       </c>
       <c r="L61" t="n">
-        <v>123.9</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-148.56</v>
+        <v>-83.98</v>
       </c>
       <c r="K62" t="n">
-        <v>73.09</v>
+        <v>41.32</v>
       </c>
       <c r="L62" t="n">
-        <v>165.57</v>
+        <v>93.59</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>29.84</v>
+        <v>15.02</v>
       </c>
       <c r="K63" t="n">
-        <v>-91.64</v>
+        <v>-46.13</v>
       </c>
       <c r="L63" t="n">
-        <v>96.37</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>124.7</v>
+        <v>65.22</v>
       </c>
       <c r="K64" t="n">
-        <v>76.27</v>
+        <v>39.89</v>
       </c>
       <c r="L64" t="n">
-        <v>146.18</v>
+        <v>76.45</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-173.66</v>
+        <v>-88.55</v>
       </c>
       <c r="K65" t="n">
-        <v>132.81</v>
+        <v>67.72</v>
       </c>
       <c r="L65" t="n">
-        <v>218.63</v>
+        <v>111.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-75.52</v>
+        <v>-38.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-96.38</v>
+        <v>-48.52</v>
       </c>
       <c r="L66" t="n">
-        <v>122.44</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-93.90000000000001</v>
+        <v>-7.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-18.81</v>
+        <v>-1.47</v>
       </c>
       <c r="L67" t="n">
-        <v>95.77</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>218.07</v>
+        <v>141.1</v>
       </c>
       <c r="K68" t="n">
-        <v>36.11</v>
+        <v>23.37</v>
       </c>
       <c r="L68" t="n">
-        <v>221.04</v>
+        <v>143.03</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-220.74</v>
+        <v>-111.6</v>
       </c>
       <c r="K69" t="n">
-        <v>100.38</v>
+        <v>50.75</v>
       </c>
       <c r="L69" t="n">
-        <v>242.49</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-31.26</v>
+        <v>-17.47</v>
       </c>
       <c r="K70" t="n">
-        <v>179.38</v>
+        <v>100.26</v>
       </c>
       <c r="L70" t="n">
-        <v>182.09</v>
+        <v>101.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-316.13</v>
+        <v>-170.94</v>
       </c>
       <c r="K71" t="n">
-        <v>315.53</v>
+        <v>170.62</v>
       </c>
       <c r="L71" t="n">
-        <v>446.65</v>
+        <v>241.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>479.04</v>
+        <v>269.72</v>
       </c>
       <c r="K72" t="n">
-        <v>185.53</v>
+        <v>104.46</v>
       </c>
       <c r="L72" t="n">
-        <v>513.71</v>
+        <v>289.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-277.46</v>
+        <v>-156.87</v>
       </c>
       <c r="K73" t="n">
-        <v>-176.05</v>
+        <v>-99.53</v>
       </c>
       <c r="L73" t="n">
-        <v>328.6</v>
+        <v>185.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>99.23999999999999</v>
+        <v>41.24</v>
       </c>
       <c r="K74" t="n">
-        <v>-183.64</v>
+        <v>-76.31</v>
       </c>
       <c r="L74" t="n">
-        <v>208.74</v>
+        <v>86.73999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-51.47</v>
+        <v>-22.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-109.32</v>
+        <v>-48.2</v>
       </c>
       <c r="L75" t="n">
-        <v>120.83</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-114.91</v>
+        <v>-50.37</v>
       </c>
       <c r="K76" t="n">
-        <v>20.91</v>
+        <v>9.17</v>
       </c>
       <c r="L76" t="n">
-        <v>116.79</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>91.84999999999999</v>
+        <v>47.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-10.21</v>
+        <v>-5.32</v>
       </c>
       <c r="L77" t="n">
-        <v>92.41</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-267.39</v>
+        <v>-135.15</v>
       </c>
       <c r="K78" t="n">
-        <v>173.86</v>
+        <v>87.88</v>
       </c>
       <c r="L78" t="n">
-        <v>318.94</v>
+        <v>161.2</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-258.28</v>
+        <v>-109.56</v>
       </c>
       <c r="K79" t="n">
-        <v>158.3</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>302.93</v>
+        <v>128.51</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>250.01</v>
+        <v>124.46</v>
       </c>
       <c r="K80" t="n">
-        <v>-128.49</v>
+        <v>-63.97</v>
       </c>
       <c r="L80" t="n">
-        <v>281.1</v>
+        <v>139.93</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-166.02</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-78.77</v>
+        <v>-40.14</v>
       </c>
       <c r="L81" t="n">
-        <v>183.76</v>
+        <v>93.64</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-14.2</v>
+        <v>-7.27</v>
       </c>
       <c r="K82" t="n">
-        <v>-188.34</v>
+        <v>-96.34</v>
       </c>
       <c r="L82" t="n">
-        <v>188.88</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-98.98</v>
+        <v>-17.17</v>
       </c>
       <c r="K83" t="n">
-        <v>54.19</v>
+        <v>9.4</v>
       </c>
       <c r="L83" t="n">
-        <v>112.85</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-242.85</v>
+        <v>-128.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-228.93</v>
+        <v>-121.22</v>
       </c>
       <c r="L84" t="n">
-        <v>333.75</v>
+        <v>176.71</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-356.71</v>
+        <v>-201.64</v>
       </c>
       <c r="K85" t="n">
-        <v>267.83</v>
+        <v>151.4</v>
       </c>
       <c r="L85" t="n">
-        <v>446.07</v>
+        <v>252.15</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-323.4</v>
+        <v>-173.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-276.48</v>
+        <v>-147.96</v>
       </c>
       <c r="L86" t="n">
-        <v>425.48</v>
+        <v>227.71</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-235.72</v>
+        <v>-130.81</v>
       </c>
       <c r="K87" t="n">
-        <v>393.94</v>
+        <v>218.61</v>
       </c>
       <c r="L87" t="n">
-        <v>459.07</v>
+        <v>254.76</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>266.93</v>
+        <v>148.29</v>
       </c>
       <c r="K88" t="n">
-        <v>-115.01</v>
+        <v>-63.89</v>
       </c>
       <c r="L88" t="n">
-        <v>290.65</v>
+        <v>161.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="K14" t="n">
-        <v>57.27</v>
+        <v>56.76</v>
       </c>
       <c r="L14" t="n">
-        <v>73.08</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="K15" t="n">
-        <v>64.09</v>
+        <v>63.09</v>
       </c>
       <c r="L15" t="n">
-        <v>64.42</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>35.25</v>
+        <v>35.62</v>
       </c>
       <c r="K16" t="n">
-        <v>-50.78</v>
+        <v>-51.3</v>
       </c>
       <c r="L16" t="n">
-        <v>61.81</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.42</v>
+        <v>-12.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-86.12</v>
+        <v>-85.16</v>
       </c>
       <c r="L17" t="n">
-        <v>87.01000000000001</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.76</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-98.56</v>
+        <v>-95.44</v>
       </c>
       <c r="L18" t="n">
-        <v>99.04000000000001</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-37.77</v>
+        <v>-38.28</v>
       </c>
       <c r="K19" t="n">
-        <v>62.85</v>
+        <v>63.7</v>
       </c>
       <c r="L19" t="n">
-        <v>73.33</v>
+        <v>74.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-62.47</v>
+        <v>-63.94</v>
       </c>
       <c r="K20" t="n">
-        <v>62.06</v>
+        <v>63.52</v>
       </c>
       <c r="L20" t="n">
-        <v>88.06</v>
+        <v>90.13</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>8.359999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.6</v>
+        <v>-18.88</v>
       </c>
       <c r="L21" t="n">
-        <v>22.24</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-99.92</v>
+        <v>-101.12</v>
       </c>
       <c r="K22" t="n">
-        <v>-31.43</v>
+        <v>-31.81</v>
       </c>
       <c r="L22" t="n">
-        <v>104.75</v>
+        <v>106.01</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-122.32</v>
+        <v>-118.98</v>
       </c>
       <c r="K23" t="n">
-        <v>174.55</v>
+        <v>169.79</v>
       </c>
       <c r="L23" t="n">
-        <v>213.14</v>
+        <v>207.33</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>26.47</v>
+        <v>27.84</v>
       </c>
       <c r="K24" t="n">
-        <v>101.69</v>
+        <v>106.95</v>
       </c>
       <c r="L24" t="n">
-        <v>105.08</v>
+        <v>110.51</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>28.4</v>
+        <v>28.65</v>
       </c>
       <c r="K25" t="n">
-        <v>138.08</v>
+        <v>139.27</v>
       </c>
       <c r="L25" t="n">
-        <v>140.97</v>
+        <v>142.19</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>47.49</v>
+        <v>49.92</v>
       </c>
       <c r="K26" t="n">
-        <v>131.5</v>
+        <v>138.21</v>
       </c>
       <c r="L26" t="n">
-        <v>139.81</v>
+        <v>146.95</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>92.19</v>
+        <v>101.32</v>
       </c>
       <c r="K27" t="n">
-        <v>-68.59</v>
+        <v>-75.38</v>
       </c>
       <c r="L27" t="n">
-        <v>114.91</v>
+        <v>126.29</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-190.93</v>
+        <v>-190.31</v>
       </c>
       <c r="K28" t="n">
-        <v>-33.2</v>
+        <v>-33.1</v>
       </c>
       <c r="L28" t="n">
-        <v>193.8</v>
+        <v>193.16</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-43.08</v>
+        <v>-46.64</v>
       </c>
       <c r="K29" t="n">
-        <v>4.86</v>
+        <v>5.26</v>
       </c>
       <c r="L29" t="n">
-        <v>43.35</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.02</v>
+        <v>-18.27</v>
       </c>
       <c r="K30" t="n">
-        <v>54.55</v>
+        <v>55.31</v>
       </c>
       <c r="L30" t="n">
-        <v>57.45</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>74.11</v>
+        <v>73.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.61</v>
+        <v>-20.32</v>
       </c>
       <c r="L31" t="n">
-        <v>76.92</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-29.4</v>
+        <v>-29.02</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.40000000000001</v>
+        <v>-80.33</v>
       </c>
       <c r="L32" t="n">
-        <v>86.54000000000001</v>
+        <v>85.41</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-77.11</v>
+        <v>-76.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-37.96</v>
+        <v>-37.52</v>
       </c>
       <c r="L33" t="n">
-        <v>85.94</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-28.12</v>
+        <v>-27.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-90.05</v>
+        <v>-88.66</v>
       </c>
       <c r="L34" t="n">
-        <v>94.34</v>
+        <v>92.88</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-137.63</v>
+        <v>-133.31</v>
       </c>
       <c r="K35" t="n">
-        <v>86.23999999999999</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>162.42</v>
+        <v>157.33</v>
       </c>
     </row>
     <row r="36">
@@ -1567,10 +1567,10 @@
         <v>-0.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.35</v>
+        <v>-2.34</v>
       </c>
       <c r="L36" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>77.47</v>
+        <v>80.62</v>
       </c>
       <c r="K37" t="n">
-        <v>35.46</v>
+        <v>36.9</v>
       </c>
       <c r="L37" t="n">
-        <v>85.2</v>
+        <v>88.67</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-106.57</v>
+        <v>-111.85</v>
       </c>
       <c r="K38" t="n">
-        <v>12.54</v>
+        <v>13.17</v>
       </c>
       <c r="L38" t="n">
-        <v>107.31</v>
+        <v>112.62</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.75</v>
+        <v>-137.49</v>
       </c>
       <c r="K39" t="n">
-        <v>156.4</v>
+        <v>150.64</v>
       </c>
       <c r="L39" t="n">
-        <v>211.75</v>
+        <v>203.95</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>63.28</v>
+        <v>63.48</v>
       </c>
       <c r="K40" t="n">
-        <v>-124.55</v>
+        <v>-124.94</v>
       </c>
       <c r="L40" t="n">
-        <v>139.71</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.92</v>
+        <v>-10.28</v>
       </c>
       <c r="K41" t="n">
-        <v>-157.86</v>
+        <v>-163.7</v>
       </c>
       <c r="L41" t="n">
-        <v>158.17</v>
+        <v>164.02</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-190.84</v>
+        <v>-225.07</v>
       </c>
       <c r="K42" t="n">
-        <v>-77.04000000000001</v>
+        <v>-90.86</v>
       </c>
       <c r="L42" t="n">
-        <v>205.81</v>
+        <v>242.72</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>260.25</v>
+        <v>261.25</v>
       </c>
       <c r="K43" t="n">
-        <v>39.91</v>
+        <v>40.06</v>
       </c>
       <c r="L43" t="n">
-        <v>263.29</v>
+        <v>264.3</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>55.14</v>
+        <v>54.23</v>
       </c>
       <c r="K44" t="n">
-        <v>42.78</v>
+        <v>42.07</v>
       </c>
       <c r="L44" t="n">
-        <v>69.79000000000001</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-61.2</v>
+        <v>-60.32</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.92</v>
+        <v>-40.34</v>
       </c>
       <c r="L45" t="n">
-        <v>73.62</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.74</v>
+        <v>-54.95</v>
       </c>
       <c r="K46" t="n">
-        <v>-39.85</v>
+        <v>-40.01</v>
       </c>
       <c r="L46" t="n">
-        <v>67.72</v>
+        <v>67.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>40.86</v>
+        <v>43.44</v>
       </c>
       <c r="K47" t="n">
-        <v>-20.76</v>
+        <v>-22.07</v>
       </c>
       <c r="L47" t="n">
-        <v>45.83</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.54000000000001</v>
+        <v>-70.31</v>
       </c>
       <c r="L48" t="n">
-        <v>70.11</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.48</v>
+        <v>-27.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-73.34999999999999</v>
+        <v>-71.84</v>
       </c>
       <c r="L49" t="n">
-        <v>78.69</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.39</v>
+        <v>-12.43</v>
       </c>
       <c r="K50" t="n">
-        <v>-104.88</v>
+        <v>-105.25</v>
       </c>
       <c r="L50" t="n">
-        <v>105.61</v>
+        <v>105.98</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>71.26000000000001</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-46.26</v>
+        <v>-48.22</v>
       </c>
       <c r="L51" t="n">
-        <v>84.95999999999999</v>
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-96.88</v>
+        <v>-98.95</v>
       </c>
       <c r="K52" t="n">
-        <v>21.06</v>
+        <v>21.51</v>
       </c>
       <c r="L52" t="n">
-        <v>99.15000000000001</v>
+        <v>101.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-20.52</v>
+        <v>-20.11</v>
       </c>
       <c r="K53" t="n">
-        <v>31.37</v>
+        <v>30.73</v>
       </c>
       <c r="L53" t="n">
-        <v>37.49</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-22.63</v>
+        <v>-22.54</v>
       </c>
       <c r="K54" t="n">
-        <v>-170.6</v>
+        <v>-169.89</v>
       </c>
       <c r="L54" t="n">
-        <v>172.09</v>
+        <v>171.38</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>90.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>36.08</v>
+        <v>38.03</v>
       </c>
       <c r="L55" t="n">
-        <v>97.42</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-92.36</v>
+        <v>-91.31</v>
       </c>
       <c r="K56" t="n">
-        <v>203.53</v>
+        <v>201.22</v>
       </c>
       <c r="L56" t="n">
-        <v>223.51</v>
+        <v>220.97</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-54.89</v>
+        <v>-66.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-178.06</v>
+        <v>-215.26</v>
       </c>
       <c r="L57" t="n">
-        <v>186.33</v>
+        <v>225.26</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-136.35</v>
+        <v>-135.33</v>
       </c>
       <c r="K58" t="n">
-        <v>-191.36</v>
+        <v>-189.92</v>
       </c>
       <c r="L58" t="n">
-        <v>234.97</v>
+        <v>233.2</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-23.14</v>
+        <v>-22.58</v>
       </c>
       <c r="K59" t="n">
-        <v>-79.75</v>
+        <v>-77.8</v>
       </c>
       <c r="L59" t="n">
-        <v>83.04000000000001</v>
+        <v>81.01000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-67.84</v>
+        <v>-66.98999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-19.92</v>
+        <v>-19.67</v>
       </c>
       <c r="L60" t="n">
-        <v>70.7</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>12.86</v>
+        <v>12.92</v>
       </c>
       <c r="K61" t="n">
-        <v>-63.77</v>
+        <v>-64.11</v>
       </c>
       <c r="L61" t="n">
-        <v>65.06</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-83.98</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>41.32</v>
+        <v>40.59</v>
       </c>
       <c r="L62" t="n">
-        <v>93.59</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>15.02</v>
+        <v>15.91</v>
       </c>
       <c r="K63" t="n">
-        <v>-46.13</v>
+        <v>-48.86</v>
       </c>
       <c r="L63" t="n">
-        <v>48.51</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>65.22</v>
+        <v>65.72</v>
       </c>
       <c r="K64" t="n">
-        <v>39.89</v>
+        <v>40.19</v>
       </c>
       <c r="L64" t="n">
-        <v>76.45</v>
+        <v>77.03</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-88.55</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>67.72</v>
+        <v>67.22</v>
       </c>
       <c r="L65" t="n">
-        <v>111.48</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-38.02</v>
+        <v>-38.62</v>
       </c>
       <c r="K66" t="n">
-        <v>-48.52</v>
+        <v>-49.29</v>
       </c>
       <c r="L66" t="n">
-        <v>61.64</v>
+        <v>62.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.32</v>
+        <v>-7.21</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.47</v>
+        <v>-1.44</v>
       </c>
       <c r="L67" t="n">
-        <v>7.46</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>141.1</v>
+        <v>139.58</v>
       </c>
       <c r="K68" t="n">
-        <v>23.37</v>
+        <v>23.12</v>
       </c>
       <c r="L68" t="n">
-        <v>143.03</v>
+        <v>141.49</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-111.6</v>
+        <v>-115.79</v>
       </c>
       <c r="K69" t="n">
-        <v>50.75</v>
+        <v>52.65</v>
       </c>
       <c r="L69" t="n">
-        <v>122.59</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-17.47</v>
+        <v>-18.71</v>
       </c>
       <c r="K70" t="n">
-        <v>100.26</v>
+        <v>107.38</v>
       </c>
       <c r="L70" t="n">
-        <v>101.77</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-170.94</v>
+        <v>-178.02</v>
       </c>
       <c r="K71" t="n">
-        <v>170.62</v>
+        <v>177.68</v>
       </c>
       <c r="L71" t="n">
-        <v>241.52</v>
+        <v>251.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>269.72</v>
+        <v>262.46</v>
       </c>
       <c r="K72" t="n">
-        <v>104.46</v>
+        <v>101.65</v>
       </c>
       <c r="L72" t="n">
-        <v>289.24</v>
+        <v>281.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-156.87</v>
+        <v>-159.43</v>
       </c>
       <c r="K73" t="n">
-        <v>-99.53</v>
+        <v>-101.16</v>
       </c>
       <c r="L73" t="n">
-        <v>185.78</v>
+        <v>188.81</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>41.24</v>
+        <v>38.85</v>
       </c>
       <c r="K74" t="n">
-        <v>-76.31</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>86.73999999999999</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-22.69</v>
+        <v>-22.82</v>
       </c>
       <c r="K75" t="n">
-        <v>-48.2</v>
+        <v>-48.48</v>
       </c>
       <c r="L75" t="n">
-        <v>53.28</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-50.37</v>
+        <v>-51.11</v>
       </c>
       <c r="K76" t="n">
-        <v>9.17</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>51.2</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>47.83</v>
+        <v>51.66</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.32</v>
+        <v>-5.74</v>
       </c>
       <c r="L77" t="n">
-        <v>48.12</v>
+        <v>51.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-135.15</v>
+        <v>-125.81</v>
       </c>
       <c r="K78" t="n">
-        <v>87.88</v>
+        <v>81.8</v>
       </c>
       <c r="L78" t="n">
-        <v>161.2</v>
+        <v>150.07</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-109.56</v>
+        <v>-100.72</v>
       </c>
       <c r="K79" t="n">
-        <v>67.15000000000001</v>
+        <v>61.73</v>
       </c>
       <c r="L79" t="n">
-        <v>128.51</v>
+        <v>118.13</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>124.46</v>
+        <v>120.86</v>
       </c>
       <c r="K80" t="n">
-        <v>-63.97</v>
+        <v>-62.12</v>
       </c>
       <c r="L80" t="n">
-        <v>139.93</v>
+        <v>135.89</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-84.59999999999999</v>
+        <v>-85.78</v>
       </c>
       <c r="K81" t="n">
-        <v>-40.14</v>
+        <v>-40.7</v>
       </c>
       <c r="L81" t="n">
-        <v>93.64</v>
+        <v>94.95</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-7.27</v>
+        <v>-7.43</v>
       </c>
       <c r="K82" t="n">
-        <v>-96.34</v>
+        <v>-98.56</v>
       </c>
       <c r="L82" t="n">
-        <v>96.62</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-17.17</v>
+        <v>-16.88</v>
       </c>
       <c r="K83" t="n">
-        <v>9.4</v>
+        <v>9.24</v>
       </c>
       <c r="L83" t="n">
-        <v>19.57</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-128.59</v>
+        <v>-127.81</v>
       </c>
       <c r="K84" t="n">
-        <v>-121.22</v>
+        <v>-120.49</v>
       </c>
       <c r="L84" t="n">
-        <v>176.71</v>
+        <v>175.66</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-201.64</v>
+        <v>-190.97</v>
       </c>
       <c r="K85" t="n">
-        <v>151.4</v>
+        <v>143.39</v>
       </c>
       <c r="L85" t="n">
-        <v>252.15</v>
+        <v>238.81</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-173.08</v>
+        <v>-204.8</v>
       </c>
       <c r="K86" t="n">
-        <v>-147.96</v>
+        <v>-175.08</v>
       </c>
       <c r="L86" t="n">
-        <v>227.71</v>
+        <v>269.44</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-130.81</v>
+        <v>-131.72</v>
       </c>
       <c r="K87" t="n">
-        <v>218.61</v>
+        <v>220.14</v>
       </c>
       <c r="L87" t="n">
-        <v>254.76</v>
+        <v>256.54</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>148.29</v>
+        <v>155.85</v>
       </c>
       <c r="K88" t="n">
-        <v>-63.89</v>
+        <v>-67.15000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>161.47</v>
+        <v>169.71</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>45</v>
+        <v>45.04</v>
       </c>
       <c r="K14" t="n">
-        <v>56.76</v>
+        <v>56.82</v>
       </c>
       <c r="L14" t="n">
-        <v>72.43000000000001</v>
+        <v>72.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.5</v>
+        <v>-6.38</v>
       </c>
       <c r="K15" t="n">
-        <v>63.09</v>
+        <v>61.94</v>
       </c>
       <c r="L15" t="n">
-        <v>63.42</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>35.62</v>
+        <v>36.03</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.3</v>
+        <v>-51.9</v>
       </c>
       <c r="L16" t="n">
-        <v>62.45</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.28</v>
+        <v>-12.12</v>
       </c>
       <c r="K17" t="n">
-        <v>-85.16</v>
+        <v>-84.06</v>
       </c>
       <c r="L17" t="n">
-        <v>86.04000000000001</v>
+        <v>84.93000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="K18" t="n">
-        <v>-95.44</v>
+        <v>-91.87</v>
       </c>
       <c r="L18" t="n">
-        <v>95.90000000000001</v>
+        <v>92.31999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-38.28</v>
+        <v>-39.07</v>
       </c>
       <c r="K19" t="n">
-        <v>63.7</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>74.31</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-63.94</v>
+        <v>-65.62</v>
       </c>
       <c r="K20" t="n">
-        <v>63.52</v>
+        <v>65.19</v>
       </c>
       <c r="L20" t="n">
-        <v>90.13</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>7.66</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-18.88</v>
+        <v>-20.26</v>
       </c>
       <c r="L21" t="n">
-        <v>20.38</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-101.12</v>
+        <v>-102.86</v>
       </c>
       <c r="K22" t="n">
-        <v>-31.81</v>
+        <v>-32.36</v>
       </c>
       <c r="L22" t="n">
-        <v>106.01</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-118.98</v>
+        <v>-114.71</v>
       </c>
       <c r="K23" t="n">
-        <v>169.79</v>
+        <v>163.69</v>
       </c>
       <c r="L23" t="n">
-        <v>207.33</v>
+        <v>199.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>27.84</v>
+        <v>29.41</v>
       </c>
       <c r="K24" t="n">
-        <v>106.95</v>
+        <v>112.96</v>
       </c>
       <c r="L24" t="n">
-        <v>110.51</v>
+        <v>116.73</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>28.65</v>
+        <v>28.93</v>
       </c>
       <c r="K25" t="n">
-        <v>139.27</v>
+        <v>140.63</v>
       </c>
       <c r="L25" t="n">
-        <v>142.19</v>
+        <v>143.58</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>49.92</v>
+        <v>52.69</v>
       </c>
       <c r="K26" t="n">
-        <v>138.21</v>
+        <v>145.88</v>
       </c>
       <c r="L26" t="n">
-        <v>146.95</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>101.32</v>
+        <v>111.42</v>
       </c>
       <c r="K27" t="n">
-        <v>-75.38</v>
+        <v>-82.90000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>126.29</v>
+        <v>138.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-190.31</v>
+        <v>-189.59</v>
       </c>
       <c r="K28" t="n">
-        <v>-33.1</v>
+        <v>-32.97</v>
       </c>
       <c r="L28" t="n">
-        <v>193.16</v>
+        <v>192.44</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-46.64</v>
+        <v>-50.7</v>
       </c>
       <c r="K29" t="n">
-        <v>5.26</v>
+        <v>5.72</v>
       </c>
       <c r="L29" t="n">
-        <v>46.93</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.27</v>
+        <v>-18.56</v>
       </c>
       <c r="K30" t="n">
-        <v>55.31</v>
+        <v>56.19</v>
       </c>
       <c r="L30" t="n">
-        <v>58.25</v>
+        <v>59.17</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>73.06</v>
+        <v>71.87</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.32</v>
+        <v>-19.99</v>
       </c>
       <c r="L31" t="n">
-        <v>75.83</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-29.02</v>
+        <v>-28.58</v>
       </c>
       <c r="K32" t="n">
-        <v>-80.33</v>
+        <v>-79.11</v>
       </c>
       <c r="L32" t="n">
-        <v>85.41</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.22</v>
+        <v>-76.02</v>
       </c>
       <c r="K33" t="n">
-        <v>-37.52</v>
+        <v>-37.43</v>
       </c>
       <c r="L33" t="n">
-        <v>84.95</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-27.69</v>
+        <v>-27.27</v>
       </c>
       <c r="K34" t="n">
-        <v>-88.66</v>
+        <v>-87.31999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>92.88</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-133.31</v>
+        <v>-129.21</v>
       </c>
       <c r="K35" t="n">
-        <v>83.54000000000001</v>
+        <v>80.97</v>
       </c>
       <c r="L35" t="n">
-        <v>157.33</v>
+        <v>152.49</v>
       </c>
     </row>
     <row r="36">
@@ -1567,10 +1567,10 @@
         <v>-0.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.34</v>
+        <v>-2.4</v>
       </c>
       <c r="L36" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>80.62</v>
+        <v>84.23</v>
       </c>
       <c r="K37" t="n">
-        <v>36.9</v>
+        <v>38.55</v>
       </c>
       <c r="L37" t="n">
-        <v>88.67</v>
+        <v>92.63</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-111.85</v>
+        <v>-117.87</v>
       </c>
       <c r="K38" t="n">
-        <v>13.17</v>
+        <v>13.87</v>
       </c>
       <c r="L38" t="n">
-        <v>112.62</v>
+        <v>118.69</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-137.49</v>
+        <v>-131.48</v>
       </c>
       <c r="K39" t="n">
-        <v>150.64</v>
+        <v>144.05</v>
       </c>
       <c r="L39" t="n">
-        <v>203.95</v>
+        <v>195.03</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>63.48</v>
+        <v>63.7</v>
       </c>
       <c r="K40" t="n">
-        <v>-124.94</v>
+        <v>-125.37</v>
       </c>
       <c r="L40" t="n">
-        <v>140.14</v>
+        <v>140.62</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.28</v>
+        <v>-10.7</v>
       </c>
       <c r="K41" t="n">
-        <v>-163.7</v>
+        <v>-170.36</v>
       </c>
       <c r="L41" t="n">
-        <v>164.02</v>
+        <v>170.7</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-225.07</v>
+        <v>-235.99</v>
       </c>
       <c r="K42" t="n">
-        <v>-90.86</v>
+        <v>-95.27</v>
       </c>
       <c r="L42" t="n">
-        <v>242.72</v>
+        <v>254.49</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>261.25</v>
+        <v>257.38</v>
       </c>
       <c r="K43" t="n">
-        <v>40.06</v>
+        <v>39.47</v>
       </c>
       <c r="L43" t="n">
-        <v>264.3</v>
+        <v>260.39</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>54.23</v>
+        <v>53.18</v>
       </c>
       <c r="K44" t="n">
-        <v>42.07</v>
+        <v>41.26</v>
       </c>
       <c r="L44" t="n">
-        <v>68.63</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-60.32</v>
+        <v>-59.32</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.34</v>
+        <v>-39.66</v>
       </c>
       <c r="L45" t="n">
-        <v>72.56</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-54.95</v>
+        <v>-55.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-40.01</v>
+        <v>-40.18</v>
       </c>
       <c r="L46" t="n">
-        <v>67.97</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>43.44</v>
+        <v>46.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.07</v>
+        <v>-23.57</v>
       </c>
       <c r="L47" t="n">
-        <v>48.72</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>9.09</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-70.31</v>
+        <v>-71.2</v>
       </c>
       <c r="L48" t="n">
-        <v>70.90000000000001</v>
+        <v>71.79000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-27.9</v>
+        <v>-27.93</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.84</v>
+        <v>-71.92</v>
       </c>
       <c r="L49" t="n">
-        <v>77.06999999999999</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.43</v>
+        <v>-12.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-105.25</v>
+        <v>-105.67</v>
       </c>
       <c r="L50" t="n">
-        <v>105.98</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>74.29000000000001</v>
+        <v>78.19</v>
       </c>
       <c r="K51" t="n">
-        <v>-48.22</v>
+        <v>-50.76</v>
       </c>
       <c r="L51" t="n">
-        <v>88.56999999999999</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-98.95</v>
+        <v>-102.01</v>
       </c>
       <c r="K52" t="n">
-        <v>21.51</v>
+        <v>22.18</v>
       </c>
       <c r="L52" t="n">
-        <v>101.27</v>
+        <v>104.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-20.11</v>
+        <v>-21.75</v>
       </c>
       <c r="K53" t="n">
-        <v>30.73</v>
+        <v>33.25</v>
       </c>
       <c r="L53" t="n">
-        <v>36.72</v>
+        <v>39.73</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-22.54</v>
+        <v>-22.37</v>
       </c>
       <c r="K54" t="n">
-        <v>-169.89</v>
+        <v>-168.65</v>
       </c>
       <c r="L54" t="n">
-        <v>171.38</v>
+        <v>170.13</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>95.40000000000001</v>
+        <v>101</v>
       </c>
       <c r="K55" t="n">
-        <v>38.03</v>
+        <v>40.26</v>
       </c>
       <c r="L55" t="n">
-        <v>102.7</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-91.31</v>
+        <v>-90.11</v>
       </c>
       <c r="K56" t="n">
-        <v>201.22</v>
+        <v>198.59</v>
       </c>
       <c r="L56" t="n">
-        <v>220.97</v>
+        <v>218.07</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-66.36</v>
+        <v>-71.55</v>
       </c>
       <c r="K57" t="n">
-        <v>-215.26</v>
+        <v>-232.1</v>
       </c>
       <c r="L57" t="n">
-        <v>225.26</v>
+        <v>242.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-135.33</v>
+        <v>-133.73</v>
       </c>
       <c r="K58" t="n">
-        <v>-189.92</v>
+        <v>-187.68</v>
       </c>
       <c r="L58" t="n">
-        <v>233.2</v>
+        <v>230.45</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-22.58</v>
+        <v>-21.93</v>
       </c>
       <c r="K59" t="n">
-        <v>-77.8</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>81.01000000000001</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-66.98999999999999</v>
+        <v>-66.63</v>
       </c>
       <c r="K60" t="n">
-        <v>-19.67</v>
+        <v>-19.56</v>
       </c>
       <c r="L60" t="n">
-        <v>69.81999999999999</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>12.92</v>
+        <v>13.06</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.11</v>
+        <v>-64.79000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>65.40000000000001</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-82.48999999999999</v>
+        <v>-80.8</v>
       </c>
       <c r="K62" t="n">
-        <v>40.59</v>
+        <v>39.76</v>
       </c>
       <c r="L62" t="n">
-        <v>91.94</v>
+        <v>90.05</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>15.91</v>
+        <v>17.51</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.86</v>
+        <v>-53.78</v>
       </c>
       <c r="L63" t="n">
-        <v>51.39</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>65.72</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>40.19</v>
+        <v>40.73</v>
       </c>
       <c r="L64" t="n">
-        <v>77.03</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-87.90000000000001</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>67.22</v>
+        <v>66.8</v>
       </c>
       <c r="L65" t="n">
-        <v>110.66</v>
+        <v>109.97</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-38.62</v>
+        <v>-42.49</v>
       </c>
       <c r="K66" t="n">
-        <v>-49.29</v>
+        <v>-54.23</v>
       </c>
       <c r="L66" t="n">
-        <v>62.62</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.21</v>
+        <v>-7.57</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.44</v>
+        <v>-1.52</v>
       </c>
       <c r="L67" t="n">
-        <v>7.35</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>139.58</v>
+        <v>137.85</v>
       </c>
       <c r="K68" t="n">
-        <v>23.12</v>
+        <v>22.83</v>
       </c>
       <c r="L68" t="n">
-        <v>141.49</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-115.79</v>
+        <v>-120.01</v>
       </c>
       <c r="K69" t="n">
-        <v>52.65</v>
+        <v>54.57</v>
       </c>
       <c r="L69" t="n">
-        <v>127.2</v>
+        <v>131.84</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-18.71</v>
+        <v>-20.11</v>
       </c>
       <c r="K70" t="n">
-        <v>107.38</v>
+        <v>115.39</v>
       </c>
       <c r="L70" t="n">
-        <v>109</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-178.02</v>
+        <v>-177.51</v>
       </c>
       <c r="K71" t="n">
-        <v>177.68</v>
+        <v>177.17</v>
       </c>
       <c r="L71" t="n">
-        <v>251.52</v>
+        <v>250.8</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>262.46</v>
+        <v>252.15</v>
       </c>
       <c r="K72" t="n">
-        <v>101.65</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>281.45</v>
+        <v>270.39</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-159.43</v>
+        <v>-161.87</v>
       </c>
       <c r="K73" t="n">
-        <v>-101.16</v>
+        <v>-102.71</v>
       </c>
       <c r="L73" t="n">
-        <v>188.81</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>38.85</v>
+        <v>37.74</v>
       </c>
       <c r="K74" t="n">
-        <v>-71.90000000000001</v>
+        <v>-69.83</v>
       </c>
       <c r="L74" t="n">
-        <v>81.73</v>
+        <v>79.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-22.82</v>
+        <v>-23.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-48.48</v>
+        <v>-50.2</v>
       </c>
       <c r="L75" t="n">
-        <v>53.58</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.11</v>
+        <v>-53.46</v>
       </c>
       <c r="K76" t="n">
-        <v>9.300000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="L76" t="n">
-        <v>51.95</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>51.66</v>
+        <v>56.31</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.74</v>
+        <v>-6.26</v>
       </c>
       <c r="L77" t="n">
-        <v>51.98</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-125.81</v>
+        <v>-116.55</v>
       </c>
       <c r="K78" t="n">
-        <v>81.8</v>
+        <v>75.78</v>
       </c>
       <c r="L78" t="n">
-        <v>150.07</v>
+        <v>139.02</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-100.72</v>
+        <v>-95.14</v>
       </c>
       <c r="K79" t="n">
-        <v>61.73</v>
+        <v>58.32</v>
       </c>
       <c r="L79" t="n">
-        <v>118.13</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>120.86</v>
+        <v>117.63</v>
       </c>
       <c r="K80" t="n">
-        <v>-62.12</v>
+        <v>-60.46</v>
       </c>
       <c r="L80" t="n">
-        <v>135.89</v>
+        <v>132.26</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-85.78</v>
+        <v>-87.33</v>
       </c>
       <c r="K81" t="n">
-        <v>-40.7</v>
+        <v>-41.43</v>
       </c>
       <c r="L81" t="n">
-        <v>94.95</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-7.43</v>
+        <v>-7.64</v>
       </c>
       <c r="K82" t="n">
-        <v>-98.56</v>
+        <v>-101.25</v>
       </c>
       <c r="L82" t="n">
-        <v>98.84</v>
+        <v>101.54</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-16.88</v>
+        <v>-18.02</v>
       </c>
       <c r="K83" t="n">
-        <v>9.24</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>19.24</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-127.81</v>
+        <v>-126.51</v>
       </c>
       <c r="K84" t="n">
-        <v>-120.49</v>
+        <v>-119.26</v>
       </c>
       <c r="L84" t="n">
-        <v>175.66</v>
+        <v>173.86</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-190.97</v>
+        <v>-178.61</v>
       </c>
       <c r="K85" t="n">
-        <v>143.39</v>
+        <v>134.11</v>
       </c>
       <c r="L85" t="n">
-        <v>238.81</v>
+        <v>223.35</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-204.8</v>
+        <v>-214.2</v>
       </c>
       <c r="K86" t="n">
-        <v>-175.08</v>
+        <v>-183.12</v>
       </c>
       <c r="L86" t="n">
-        <v>269.44</v>
+        <v>281.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-131.72</v>
+        <v>-129.81</v>
       </c>
       <c r="K87" t="n">
-        <v>220.14</v>
+        <v>216.94</v>
       </c>
       <c r="L87" t="n">
-        <v>256.54</v>
+        <v>252.81</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>155.85</v>
+        <v>161.34</v>
       </c>
       <c r="K88" t="n">
-        <v>-67.15000000000001</v>
+        <v>-69.52</v>
       </c>
       <c r="L88" t="n">
-        <v>169.71</v>
+        <v>175.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -628,25 +628,25 @@
         <v>3.58</v>
       </c>
       <c r="F14" t="n">
-        <v>12.11</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>227.6</v>
+        <v>227.9</v>
       </c>
       <c r="H14" t="n">
-        <v>74.3</v>
+        <v>77.2</v>
       </c>
       <c r="I14" t="n">
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>45.04</v>
+        <v>49.76</v>
       </c>
       <c r="K14" t="n">
-        <v>56.82</v>
+        <v>63.13</v>
       </c>
       <c r="L14" t="n">
-        <v>72.51000000000001</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>2.24</v>
       </c>
       <c r="F15" t="n">
-        <v>11.97</v>
+        <v>6.53</v>
       </c>
       <c r="G15" t="n">
-        <v>245.3</v>
+        <v>225.1</v>
       </c>
       <c r="H15" t="n">
-        <v>78.5</v>
+        <v>86</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.38</v>
+        <v>-6.97</v>
       </c>
       <c r="K15" t="n">
-        <v>61.94</v>
+        <v>64.91</v>
       </c>
       <c r="L15" t="n">
-        <v>62.27</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>2.9</v>
       </c>
       <c r="F16" t="n">
-        <v>12.36</v>
+        <v>9.67</v>
       </c>
       <c r="G16" t="n">
-        <v>241.9</v>
+        <v>232.9</v>
       </c>
       <c r="H16" t="n">
-        <v>79.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>36.03</v>
+        <v>38.31</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.9</v>
+        <v>-56.95</v>
       </c>
       <c r="L16" t="n">
-        <v>63.18</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.17</v>
       </c>
       <c r="F17" t="n">
-        <v>11.48</v>
+        <v>13.84</v>
       </c>
       <c r="G17" t="n">
-        <v>237.1</v>
+        <v>215.3</v>
       </c>
       <c r="H17" t="n">
-        <v>80.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.12</v>
+        <v>-16.82</v>
       </c>
       <c r="K17" t="n">
-        <v>-84.06</v>
+        <v>-113.13</v>
       </c>
       <c r="L17" t="n">
-        <v>84.93000000000001</v>
+        <v>114.37</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.08</v>
       </c>
       <c r="F18" t="n">
-        <v>11.58</v>
+        <v>11.68</v>
       </c>
       <c r="G18" t="n">
-        <v>243.1</v>
+        <v>217.3</v>
       </c>
       <c r="H18" t="n">
-        <v>81.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.1</v>
+        <v>-11.79</v>
       </c>
       <c r="K18" t="n">
-        <v>-91.87</v>
+        <v>-114.27</v>
       </c>
       <c r="L18" t="n">
-        <v>92.31999999999999</v>
+        <v>114.88</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.41</v>
       </c>
       <c r="F19" t="n">
-        <v>12.51</v>
+        <v>14.14</v>
       </c>
       <c r="G19" t="n">
-        <v>224.6</v>
+        <v>235.7</v>
       </c>
       <c r="H19" t="n">
-        <v>81.2</v>
+        <v>75.7</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-39.07</v>
+        <v>-48.3</v>
       </c>
       <c r="K19" t="n">
-        <v>65.01000000000001</v>
+        <v>72.58</v>
       </c>
       <c r="L19" t="n">
-        <v>75.84999999999999</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>2.13</v>
       </c>
       <c r="F20" t="n">
-        <v>12.45</v>
+        <v>8.93</v>
       </c>
       <c r="G20" t="n">
-        <v>211.2</v>
+        <v>234.7</v>
       </c>
       <c r="H20" t="n">
-        <v>82.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-65.62</v>
+        <v>-87.34</v>
       </c>
       <c r="K20" t="n">
-        <v>65.19</v>
+        <v>73.36</v>
       </c>
       <c r="L20" t="n">
-        <v>92.5</v>
+        <v>114.06</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.01</v>
       </c>
       <c r="F21" t="n">
-        <v>12.16</v>
+        <v>10.32</v>
       </c>
       <c r="G21" t="n">
-        <v>240.4</v>
+        <v>228.9</v>
       </c>
       <c r="H21" t="n">
-        <v>79.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>8.220000000000001</v>
+        <v>-10.24</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.26</v>
+        <v>-58.91</v>
       </c>
       <c r="L21" t="n">
-        <v>21.87</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.53</v>
       </c>
       <c r="F22" t="n">
-        <v>11.44</v>
+        <v>10.15</v>
       </c>
       <c r="G22" t="n">
-        <v>223.1</v>
+        <v>214.5</v>
       </c>
       <c r="H22" t="n">
-        <v>75.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-102.86</v>
+        <v>-115.91</v>
       </c>
       <c r="K22" t="n">
-        <v>-32.36</v>
+        <v>-47.28</v>
       </c>
       <c r="L22" t="n">
-        <v>107.83</v>
+        <v>125.18</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.7</v>
       </c>
       <c r="F23" t="n">
-        <v>12.25</v>
+        <v>13.68</v>
       </c>
       <c r="G23" t="n">
-        <v>242.8</v>
+        <v>230.6</v>
       </c>
       <c r="H23" t="n">
-        <v>73.5</v>
+        <v>84.8</v>
       </c>
       <c r="I23" t="n">
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-114.71</v>
+        <v>-161.55</v>
       </c>
       <c r="K23" t="n">
-        <v>163.69</v>
+        <v>177.26</v>
       </c>
       <c r="L23" t="n">
-        <v>199.88</v>
+        <v>239.83</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>2.86</v>
       </c>
       <c r="F24" t="n">
-        <v>12.36</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>232</v>
+        <v>232.8</v>
       </c>
       <c r="H24" t="n">
-        <v>77.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>29.41</v>
+        <v>-0.73</v>
       </c>
       <c r="K24" t="n">
-        <v>112.96</v>
+        <v>125.03</v>
       </c>
       <c r="L24" t="n">
-        <v>116.73</v>
+        <v>125.03</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.99</v>
       </c>
       <c r="F25" t="n">
-        <v>11.73</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>226.8</v>
+        <v>220.2</v>
       </c>
       <c r="H25" t="n">
-        <v>84.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>28.93</v>
+        <v>17.94</v>
       </c>
       <c r="K25" t="n">
-        <v>140.63</v>
+        <v>161.33</v>
       </c>
       <c r="L25" t="n">
-        <v>143.58</v>
+        <v>162.33</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.66</v>
       </c>
       <c r="F26" t="n">
-        <v>12.07</v>
+        <v>9.92</v>
       </c>
       <c r="G26" t="n">
-        <v>231.6</v>
+        <v>226.9</v>
       </c>
       <c r="H26" t="n">
-        <v>80.7</v>
+        <v>79.2</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>52.69</v>
+        <v>7.53</v>
       </c>
       <c r="K26" t="n">
-        <v>145.88</v>
+        <v>168.14</v>
       </c>
       <c r="L26" t="n">
-        <v>155.1</v>
+        <v>168.31</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.31</v>
       </c>
       <c r="F27" t="n">
-        <v>11.77</v>
+        <v>9.02</v>
       </c>
       <c r="G27" t="n">
-        <v>233.5</v>
+        <v>221.1</v>
       </c>
       <c r="H27" t="n">
-        <v>80.5</v>
+        <v>80.2</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>111.42</v>
+        <v>46.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-82.90000000000001</v>
+        <v>-172.27</v>
       </c>
       <c r="L27" t="n">
-        <v>138.88</v>
+        <v>178.55</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.35</v>
       </c>
       <c r="F28" t="n">
-        <v>13.34</v>
+        <v>6.51</v>
       </c>
       <c r="G28" t="n">
-        <v>236.1</v>
+        <v>252.4</v>
       </c>
       <c r="H28" t="n">
-        <v>76.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-189.59</v>
+        <v>-234.77</v>
       </c>
       <c r="K28" t="n">
-        <v>-32.97</v>
+        <v>-40.95</v>
       </c>
       <c r="L28" t="n">
-        <v>192.44</v>
+        <v>238.31</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.17</v>
       </c>
       <c r="F29" t="n">
-        <v>12.3</v>
+        <v>13.63</v>
       </c>
       <c r="G29" t="n">
-        <v>235.9</v>
+        <v>231.6</v>
       </c>
       <c r="H29" t="n">
-        <v>84.8</v>
+        <v>81.3</v>
       </c>
       <c r="I29" t="n">
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-50.7</v>
+        <v>-68.37</v>
       </c>
       <c r="K29" t="n">
-        <v>5.72</v>
+        <v>5.25</v>
       </c>
       <c r="L29" t="n">
-        <v>51.02</v>
+        <v>68.56999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>3.07</v>
       </c>
       <c r="F30" t="n">
-        <v>11.35</v>
+        <v>13.36</v>
       </c>
       <c r="G30" t="n">
-        <v>237</v>
+        <v>212.6</v>
       </c>
       <c r="H30" t="n">
-        <v>84.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.56</v>
+        <v>-25.01</v>
       </c>
       <c r="K30" t="n">
-        <v>56.19</v>
+        <v>73.56</v>
       </c>
       <c r="L30" t="n">
-        <v>59.17</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.21</v>
       </c>
       <c r="F31" t="n">
-        <v>12.65</v>
+        <v>11.16</v>
       </c>
       <c r="G31" t="n">
-        <v>221.8</v>
+        <v>238.5</v>
       </c>
       <c r="H31" t="n">
-        <v>75.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>71.87</v>
+        <v>79.31</v>
       </c>
       <c r="K31" t="n">
-        <v>-19.99</v>
+        <v>-22.56</v>
       </c>
       <c r="L31" t="n">
-        <v>74.59999999999999</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>2.81</v>
       </c>
       <c r="F32" t="n">
-        <v>12.51</v>
+        <v>7.93</v>
       </c>
       <c r="G32" t="n">
-        <v>229.1</v>
+        <v>235.8</v>
       </c>
       <c r="H32" t="n">
-        <v>75.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-28.58</v>
+        <v>-31.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-79.11</v>
+        <v>-83.75</v>
       </c>
       <c r="L32" t="n">
-        <v>84.12</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>3.56</v>
       </c>
       <c r="F33" t="n">
-        <v>12.21</v>
+        <v>13.7</v>
       </c>
       <c r="G33" t="n">
-        <v>240.3</v>
+        <v>229.7</v>
       </c>
       <c r="H33" t="n">
-        <v>81.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I33" t="n">
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.02</v>
+        <v>-94.59</v>
       </c>
       <c r="K33" t="n">
-        <v>-37.43</v>
+        <v>-48.27</v>
       </c>
       <c r="L33" t="n">
-        <v>84.73999999999999</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>3.33</v>
       </c>
       <c r="F34" t="n">
-        <v>12.12</v>
+        <v>12.26</v>
       </c>
       <c r="G34" t="n">
-        <v>243.3</v>
+        <v>228</v>
       </c>
       <c r="H34" t="n">
-        <v>80.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-27.27</v>
+        <v>-31.02</v>
       </c>
       <c r="K34" t="n">
-        <v>-87.31999999999999</v>
+        <v>-96.5</v>
       </c>
       <c r="L34" t="n">
-        <v>91.48</v>
+        <v>101.36</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.74</v>
       </c>
       <c r="F35" t="n">
-        <v>12.7</v>
+        <v>11.45</v>
       </c>
       <c r="G35" t="n">
-        <v>222.1</v>
+        <v>239.7</v>
       </c>
       <c r="H35" t="n">
-        <v>77</v>
+        <v>74.5</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-129.21</v>
+        <v>-148.74</v>
       </c>
       <c r="K35" t="n">
-        <v>80.97</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>152.49</v>
+        <v>169.59</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.12</v>
       </c>
       <c r="F36" t="n">
-        <v>12.14</v>
+        <v>6.91</v>
       </c>
       <c r="G36" t="n">
-        <v>233.4</v>
+        <v>228.3</v>
       </c>
       <c r="H36" t="n">
-        <v>71.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.05</v>
+        <v>-18.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.4</v>
+        <v>-23.16</v>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.18</v>
       </c>
       <c r="F37" t="n">
-        <v>12.66</v>
+        <v>10.73</v>
       </c>
       <c r="G37" t="n">
-        <v>236.6</v>
+        <v>238.7</v>
       </c>
       <c r="H37" t="n">
-        <v>82.7</v>
+        <v>81.7</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>84.23</v>
+        <v>103.11</v>
       </c>
       <c r="K37" t="n">
-        <v>38.55</v>
+        <v>44.91</v>
       </c>
       <c r="L37" t="n">
-        <v>92.63</v>
+        <v>112.47</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>2.77</v>
       </c>
       <c r="F38" t="n">
-        <v>12.15</v>
+        <v>14.14</v>
       </c>
       <c r="G38" t="n">
-        <v>228.5</v>
+        <v>228.7</v>
       </c>
       <c r="H38" t="n">
-        <v>88.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-117.87</v>
+        <v>-168.64</v>
       </c>
       <c r="K38" t="n">
-        <v>13.87</v>
+        <v>-11.16</v>
       </c>
       <c r="L38" t="n">
-        <v>118.69</v>
+        <v>169.01</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>3.07</v>
       </c>
       <c r="F39" t="n">
-        <v>12.21</v>
+        <v>10.64</v>
       </c>
       <c r="G39" t="n">
-        <v>232</v>
+        <v>229.8</v>
       </c>
       <c r="H39" t="n">
-        <v>87</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-131.48</v>
+        <v>-180.83</v>
       </c>
       <c r="K39" t="n">
-        <v>144.05</v>
+        <v>164.2</v>
       </c>
       <c r="L39" t="n">
-        <v>195.03</v>
+        <v>244.26</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.87</v>
       </c>
       <c r="F40" t="n">
-        <v>12.13</v>
+        <v>13.25</v>
       </c>
       <c r="G40" t="n">
-        <v>227.4</v>
+        <v>228.2</v>
       </c>
       <c r="H40" t="n">
-        <v>85</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>63.7</v>
+        <v>58.83</v>
       </c>
       <c r="K40" t="n">
-        <v>-125.37</v>
+        <v>-176.78</v>
       </c>
       <c r="L40" t="n">
-        <v>140.62</v>
+        <v>186.32</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>3.22</v>
       </c>
       <c r="F41" t="n">
-        <v>12.34</v>
+        <v>8.85</v>
       </c>
       <c r="G41" t="n">
-        <v>232.6</v>
+        <v>232.5</v>
       </c>
       <c r="H41" t="n">
-        <v>75</v>
+        <v>79.7</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.7</v>
+        <v>-53.17</v>
       </c>
       <c r="K41" t="n">
-        <v>-170.36</v>
+        <v>-198.85</v>
       </c>
       <c r="L41" t="n">
-        <v>170.7</v>
+        <v>205.84</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>5.02</v>
       </c>
       <c r="F42" t="n">
-        <v>12.54</v>
+        <v>14.03</v>
       </c>
       <c r="G42" t="n">
-        <v>234.2</v>
+        <v>236.4</v>
       </c>
       <c r="H42" t="n">
-        <v>72.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I42" t="n">
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-235.99</v>
+        <v>-286.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-95.27</v>
+        <v>-123.42</v>
       </c>
       <c r="L42" t="n">
-        <v>254.49</v>
+        <v>312.23</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>3.57</v>
       </c>
       <c r="F43" t="n">
-        <v>12.21</v>
+        <v>14.12</v>
       </c>
       <c r="G43" t="n">
-        <v>229.5</v>
+        <v>229.9</v>
       </c>
       <c r="H43" t="n">
-        <v>80.5</v>
+        <v>78.2</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>257.38</v>
+        <v>291.31</v>
       </c>
       <c r="K43" t="n">
-        <v>39.47</v>
+        <v>19.46</v>
       </c>
       <c r="L43" t="n">
-        <v>260.39</v>
+        <v>291.96</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.93</v>
       </c>
       <c r="F44" t="n">
-        <v>11.84</v>
+        <v>7.92</v>
       </c>
       <c r="G44" t="n">
-        <v>216.5</v>
+        <v>222.3</v>
       </c>
       <c r="H44" t="n">
-        <v>74.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>53.18</v>
+        <v>63.34</v>
       </c>
       <c r="K44" t="n">
-        <v>41.26</v>
+        <v>49.1</v>
       </c>
       <c r="L44" t="n">
-        <v>67.31</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.85</v>
       </c>
       <c r="F45" t="n">
-        <v>12.62</v>
+        <v>8.09</v>
       </c>
       <c r="G45" t="n">
-        <v>230.3</v>
+        <v>238</v>
       </c>
       <c r="H45" t="n">
-        <v>68.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-59.32</v>
+        <v>-63.88</v>
       </c>
       <c r="K45" t="n">
-        <v>-39.66</v>
+        <v>-42.52</v>
       </c>
       <c r="L45" t="n">
-        <v>71.34999999999999</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>3.18</v>
       </c>
       <c r="F46" t="n">
-        <v>12.27</v>
+        <v>10.91</v>
       </c>
       <c r="G46" t="n">
-        <v>236.7</v>
+        <v>230.9</v>
       </c>
       <c r="H46" t="n">
-        <v>78.5</v>
+        <v>81.7</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-55.19</v>
+        <v>-63.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-40.18</v>
+        <v>-46.8</v>
       </c>
       <c r="L46" t="n">
-        <v>68.27</v>
+        <v>79.22</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>2.83</v>
       </c>
       <c r="F47" t="n">
-        <v>12.69</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>235.4</v>
+        <v>239.4</v>
       </c>
       <c r="H47" t="n">
-        <v>64.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>46.38</v>
+        <v>62.15</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.57</v>
+        <v>-36.41</v>
       </c>
       <c r="L47" t="n">
-        <v>52.03</v>
+        <v>72.03</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>2.49</v>
       </c>
       <c r="F48" t="n">
-        <v>12.05</v>
+        <v>8.44</v>
       </c>
       <c r="G48" t="n">
-        <v>233.2</v>
+        <v>226.6</v>
       </c>
       <c r="H48" t="n">
-        <v>78.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>9.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.2</v>
+        <v>-76.34999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>71.79000000000001</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>12.71</v>
+        <v>14.14</v>
       </c>
       <c r="G49" t="n">
-        <v>225.5</v>
+        <v>239.8</v>
       </c>
       <c r="H49" t="n">
-        <v>78.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-27.93</v>
+        <v>-41.68</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.92</v>
+        <v>-97.37</v>
       </c>
       <c r="L49" t="n">
-        <v>77.15000000000001</v>
+        <v>105.92</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.73</v>
       </c>
       <c r="F50" t="n">
-        <v>12.7</v>
+        <v>9.24</v>
       </c>
       <c r="G50" t="n">
-        <v>241.1</v>
+        <v>239.5</v>
       </c>
       <c r="H50" t="n">
-        <v>78.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.48</v>
+        <v>-23.85</v>
       </c>
       <c r="K50" t="n">
-        <v>-105.67</v>
+        <v>-130.63</v>
       </c>
       <c r="L50" t="n">
-        <v>106.4</v>
+        <v>132.78</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>3.77</v>
       </c>
       <c r="F51" t="n">
-        <v>11.97</v>
+        <v>14.14</v>
       </c>
       <c r="G51" t="n">
-        <v>227.1</v>
+        <v>225</v>
       </c>
       <c r="H51" t="n">
-        <v>83.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>78.19</v>
+        <v>79.37</v>
       </c>
       <c r="K51" t="n">
-        <v>-50.76</v>
+        <v>-81.63</v>
       </c>
       <c r="L51" t="n">
-        <v>93.22</v>
+        <v>113.86</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>3.84</v>
       </c>
       <c r="F52" t="n">
-        <v>12.29</v>
+        <v>14.14</v>
       </c>
       <c r="G52" t="n">
-        <v>227.1</v>
+        <v>231.5</v>
       </c>
       <c r="H52" t="n">
-        <v>80.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-102.01</v>
+        <v>-132.68</v>
       </c>
       <c r="K52" t="n">
-        <v>22.18</v>
+        <v>13.56</v>
       </c>
       <c r="L52" t="n">
-        <v>104.39</v>
+        <v>133.37</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>3.12</v>
       </c>
       <c r="F53" t="n">
-        <v>12.56</v>
+        <v>10.55</v>
       </c>
       <c r="G53" t="n">
-        <v>236.6</v>
+        <v>236.7</v>
       </c>
       <c r="H53" t="n">
-        <v>72.3</v>
+        <v>81.7</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-21.75</v>
+        <v>-107.25</v>
       </c>
       <c r="K53" t="n">
-        <v>33.25</v>
+        <v>2.01</v>
       </c>
       <c r="L53" t="n">
-        <v>39.73</v>
+        <v>107.27</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>3.56</v>
       </c>
       <c r="F54" t="n">
-        <v>12.29</v>
+        <v>14.14</v>
       </c>
       <c r="G54" t="n">
-        <v>234.2</v>
+        <v>231.3</v>
       </c>
       <c r="H54" t="n">
-        <v>83</v>
+        <v>80.5</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-22.37</v>
+        <v>-48.51</v>
       </c>
       <c r="K54" t="n">
-        <v>-168.65</v>
+        <v>-202.59</v>
       </c>
       <c r="L54" t="n">
-        <v>170.13</v>
+        <v>208.32</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.79</v>
       </c>
       <c r="F55" t="n">
-        <v>12.32</v>
+        <v>10.31</v>
       </c>
       <c r="G55" t="n">
-        <v>230.6</v>
+        <v>232</v>
       </c>
       <c r="H55" t="n">
-        <v>89.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>101</v>
+        <v>124.97</v>
       </c>
       <c r="K55" t="n">
-        <v>40.26</v>
+        <v>32.49</v>
       </c>
       <c r="L55" t="n">
-        <v>108.73</v>
+        <v>129.13</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>3.14</v>
       </c>
       <c r="F56" t="n">
-        <v>12.21</v>
+        <v>10.47</v>
       </c>
       <c r="G56" t="n">
-        <v>224.9</v>
+        <v>229.8</v>
       </c>
       <c r="H56" t="n">
-        <v>77.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-90.11</v>
+        <v>-138.51</v>
       </c>
       <c r="K56" t="n">
-        <v>198.59</v>
+        <v>205.41</v>
       </c>
       <c r="L56" t="n">
-        <v>218.07</v>
+        <v>247.75</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>4.97</v>
       </c>
       <c r="F57" t="n">
-        <v>12.14</v>
+        <v>14.14</v>
       </c>
       <c r="G57" t="n">
-        <v>231.1</v>
+        <v>228.4</v>
       </c>
       <c r="H57" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-71.55</v>
+        <v>-118.78</v>
       </c>
       <c r="K57" t="n">
-        <v>-232.1</v>
+        <v>-277.12</v>
       </c>
       <c r="L57" t="n">
-        <v>242.88</v>
+        <v>301.5</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>3.3</v>
       </c>
       <c r="F58" t="n">
-        <v>12.14</v>
+        <v>11.78</v>
       </c>
       <c r="G58" t="n">
-        <v>232.2</v>
+        <v>228.4</v>
       </c>
       <c r="H58" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-133.73</v>
+        <v>-162.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-187.68</v>
+        <v>-216.84</v>
       </c>
       <c r="L58" t="n">
-        <v>230.45</v>
+        <v>271.22</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>3.08</v>
       </c>
       <c r="F59" t="n">
-        <v>12.81</v>
+        <v>8.41</v>
       </c>
       <c r="G59" t="n">
-        <v>235.6</v>
+        <v>241.8</v>
       </c>
       <c r="H59" t="n">
-        <v>72.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.93</v>
+        <v>-24.67</v>
       </c>
       <c r="K59" t="n">
-        <v>-75.56999999999999</v>
+        <v>-82.63</v>
       </c>
       <c r="L59" t="n">
-        <v>78.69</v>
+        <v>86.23999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>3.51</v>
       </c>
       <c r="F60" t="n">
-        <v>11.39</v>
+        <v>12.59</v>
       </c>
       <c r="G60" t="n">
-        <v>225.2</v>
+        <v>213.4</v>
       </c>
       <c r="H60" t="n">
-        <v>78.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-66.63</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-19.56</v>
+        <v>-24.06</v>
       </c>
       <c r="L60" t="n">
-        <v>69.44</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.39</v>
       </c>
       <c r="F61" t="n">
-        <v>12.43</v>
+        <v>13.36</v>
       </c>
       <c r="G61" t="n">
-        <v>234.7</v>
+        <v>234.1</v>
       </c>
       <c r="H61" t="n">
-        <v>76.2</v>
+        <v>80.7</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>13.06</v>
+        <v>14.33</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.79000000000001</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>66.09</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>2.99</v>
       </c>
       <c r="F62" t="n">
-        <v>12.45</v>
+        <v>10.65</v>
       </c>
       <c r="G62" t="n">
-        <v>228.3</v>
+        <v>234.6</v>
       </c>
       <c r="H62" t="n">
-        <v>78.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-80.8</v>
+        <v>-91.77</v>
       </c>
       <c r="K62" t="n">
-        <v>39.76</v>
+        <v>42.98</v>
       </c>
       <c r="L62" t="n">
-        <v>90.05</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.57</v>
       </c>
       <c r="F63" t="n">
-        <v>13.15</v>
+        <v>12.76</v>
       </c>
       <c r="G63" t="n">
-        <v>229</v>
+        <v>248.5</v>
       </c>
       <c r="H63" t="n">
-        <v>82.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>17.51</v>
+        <v>8.18</v>
       </c>
       <c r="K63" t="n">
-        <v>-53.78</v>
+        <v>-63.11</v>
       </c>
       <c r="L63" t="n">
-        <v>56.56</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>3.39</v>
       </c>
       <c r="F64" t="n">
-        <v>11.76</v>
+        <v>12.68</v>
       </c>
       <c r="G64" t="n">
-        <v>237.1</v>
+        <v>220.8</v>
       </c>
       <c r="H64" t="n">
-        <v>79.7</v>
+        <v>82</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>66.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K64" t="n">
-        <v>40.73</v>
+        <v>45.01</v>
       </c>
       <c r="L64" t="n">
-        <v>78.06</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>3.42</v>
       </c>
       <c r="F65" t="n">
-        <v>13.15</v>
+        <v>14.14</v>
       </c>
       <c r="G65" t="n">
-        <v>231.8</v>
+        <v>248.7</v>
       </c>
       <c r="H65" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-87.34999999999999</v>
+        <v>-131.39</v>
       </c>
       <c r="K65" t="n">
-        <v>66.8</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>109.97</v>
+        <v>157.56</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.63</v>
       </c>
       <c r="F66" t="n">
-        <v>12.28</v>
+        <v>10.93</v>
       </c>
       <c r="G66" t="n">
-        <v>233.5</v>
+        <v>231.1</v>
       </c>
       <c r="H66" t="n">
-        <v>74.8</v>
+        <v>80.2</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-42.49</v>
+        <v>-66.06</v>
       </c>
       <c r="K66" t="n">
-        <v>-54.23</v>
+        <v>-73.47</v>
       </c>
       <c r="L66" t="n">
-        <v>68.90000000000001</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>3.45</v>
       </c>
       <c r="F67" t="n">
-        <v>12.83</v>
+        <v>8.85</v>
       </c>
       <c r="G67" t="n">
-        <v>227.7</v>
+        <v>242.2</v>
       </c>
       <c r="H67" t="n">
-        <v>74.8</v>
+        <v>77.3</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.57</v>
+        <v>-47.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.52</v>
+        <v>-13.79</v>
       </c>
       <c r="L67" t="n">
-        <v>7.72</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>2.53</v>
       </c>
       <c r="F68" t="n">
-        <v>11.8</v>
+        <v>10.29</v>
       </c>
       <c r="G68" t="n">
-        <v>233.9</v>
+        <v>221.6</v>
       </c>
       <c r="H68" t="n">
-        <v>81</v>
+        <v>80.3</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>137.85</v>
+        <v>171.66</v>
       </c>
       <c r="K68" t="n">
-        <v>22.83</v>
+        <v>12.39</v>
       </c>
       <c r="L68" t="n">
-        <v>139.73</v>
+        <v>172.11</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>3.88</v>
       </c>
       <c r="F69" t="n">
-        <v>11.79</v>
+        <v>14.14</v>
       </c>
       <c r="G69" t="n">
-        <v>213.4</v>
+        <v>221.4</v>
       </c>
       <c r="H69" t="n">
-        <v>74</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-120.01</v>
+        <v>-178.23</v>
       </c>
       <c r="K69" t="n">
-        <v>54.57</v>
+        <v>29.06</v>
       </c>
       <c r="L69" t="n">
-        <v>131.84</v>
+        <v>180.58</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>3.4</v>
       </c>
       <c r="F70" t="n">
-        <v>12.32</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>221.4</v>
+        <v>231.9</v>
       </c>
       <c r="H70" t="n">
-        <v>74.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I70" t="n">
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.11</v>
+        <v>-88.86</v>
       </c>
       <c r="K70" t="n">
-        <v>115.39</v>
+        <v>105.48</v>
       </c>
       <c r="L70" t="n">
-        <v>117.13</v>
+        <v>137.92</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>4.16</v>
       </c>
       <c r="F71" t="n">
-        <v>12.72</v>
+        <v>14.14</v>
       </c>
       <c r="G71" t="n">
-        <v>237.1</v>
+        <v>240</v>
       </c>
       <c r="H71" t="n">
-        <v>80.8</v>
+        <v>82</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-177.51</v>
+        <v>-256.07</v>
       </c>
       <c r="K71" t="n">
-        <v>177.17</v>
+        <v>196.95</v>
       </c>
       <c r="L71" t="n">
-        <v>250.8</v>
+        <v>323.05</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>3.37</v>
       </c>
       <c r="F72" t="n">
-        <v>12.46</v>
+        <v>12.76</v>
       </c>
       <c r="G72" t="n">
-        <v>240.8</v>
+        <v>234.7</v>
       </c>
       <c r="H72" t="n">
-        <v>79.7</v>
+        <v>83.8</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>252.15</v>
+        <v>303.55</v>
       </c>
       <c r="K72" t="n">
-        <v>97.65000000000001</v>
+        <v>103.83</v>
       </c>
       <c r="L72" t="n">
-        <v>270.39</v>
+        <v>320.81</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.3</v>
       </c>
       <c r="F73" t="n">
-        <v>12.73</v>
+        <v>14.14</v>
       </c>
       <c r="G73" t="n">
-        <v>238</v>
+        <v>240.2</v>
       </c>
       <c r="H73" t="n">
-        <v>75.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-161.87</v>
+        <v>-237.92</v>
       </c>
       <c r="K73" t="n">
-        <v>-102.71</v>
+        <v>-146.55</v>
       </c>
       <c r="L73" t="n">
-        <v>191.7</v>
+        <v>279.43</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>4.48</v>
       </c>
       <c r="F74" t="n">
-        <v>12.64</v>
+        <v>14.14</v>
       </c>
       <c r="G74" t="n">
-        <v>224.9</v>
+        <v>238.3</v>
       </c>
       <c r="H74" t="n">
-        <v>82.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>37.74</v>
+        <v>42.52</v>
       </c>
       <c r="K74" t="n">
-        <v>-69.83</v>
+        <v>-81.62</v>
       </c>
       <c r="L74" t="n">
-        <v>79.38</v>
+        <v>92.03</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>4.16</v>
       </c>
       <c r="F75" t="n">
-        <v>12.63</v>
+        <v>14.14</v>
       </c>
       <c r="G75" t="n">
-        <v>221.4</v>
+        <v>238.3</v>
       </c>
       <c r="H75" t="n">
-        <v>81.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-23.64</v>
+        <v>-33.44</v>
       </c>
       <c r="K75" t="n">
-        <v>-50.2</v>
+        <v>-66.42</v>
       </c>
       <c r="L75" t="n">
-        <v>55.49</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>4.19</v>
       </c>
       <c r="F76" t="n">
-        <v>12.74</v>
+        <v>14.14</v>
       </c>
       <c r="G76" t="n">
-        <v>226.6</v>
+        <v>240.3</v>
       </c>
       <c r="H76" t="n">
-        <v>80.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-53.46</v>
+        <v>-71.15000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>9.73</v>
+        <v>11.91</v>
       </c>
       <c r="L76" t="n">
-        <v>54.34</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>3.41</v>
       </c>
       <c r="F77" t="n">
-        <v>13.2</v>
+        <v>12.19</v>
       </c>
       <c r="G77" t="n">
-        <v>228.4</v>
+        <v>249.5</v>
       </c>
       <c r="H77" t="n">
-        <v>82.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>56.31</v>
+        <v>62.63</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.26</v>
+        <v>-8.52</v>
       </c>
       <c r="L77" t="n">
-        <v>56.66</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>3.55</v>
       </c>
       <c r="F78" t="n">
-        <v>12.46</v>
+        <v>13.39</v>
       </c>
       <c r="G78" t="n">
-        <v>233.4</v>
+        <v>234.9</v>
       </c>
       <c r="H78" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-116.55</v>
+        <v>-124.18</v>
       </c>
       <c r="K78" t="n">
-        <v>75.78</v>
+        <v>78.59</v>
       </c>
       <c r="L78" t="n">
-        <v>139.02</v>
+        <v>146.96</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>4.58</v>
       </c>
       <c r="F79" t="n">
-        <v>12.97</v>
+        <v>14.14</v>
       </c>
       <c r="G79" t="n">
-        <v>238.9</v>
+        <v>245</v>
       </c>
       <c r="H79" t="n">
-        <v>84.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-95.14</v>
+        <v>-122.44</v>
       </c>
       <c r="K79" t="n">
-        <v>58.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>111.59</v>
+        <v>142.04</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>3.83</v>
       </c>
       <c r="F80" t="n">
-        <v>12.31</v>
+        <v>11.02</v>
       </c>
       <c r="G80" t="n">
-        <v>221.9</v>
+        <v>231.7</v>
       </c>
       <c r="H80" t="n">
-        <v>73.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>117.63</v>
+        <v>126.78</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.46</v>
+        <v>-77.48</v>
       </c>
       <c r="L80" t="n">
-        <v>132.26</v>
+        <v>148.58</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>3.43</v>
       </c>
       <c r="F81" t="n">
-        <v>12.49</v>
+        <v>11.66</v>
       </c>
       <c r="G81" t="n">
-        <v>228</v>
+        <v>235.4</v>
       </c>
       <c r="H81" t="n">
-        <v>81.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-87.33</v>
+        <v>-105.95</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.43</v>
+        <v>-51.39</v>
       </c>
       <c r="L81" t="n">
-        <v>96.66</v>
+        <v>117.75</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>3.37</v>
       </c>
       <c r="F82" t="n">
-        <v>12.06</v>
+        <v>13.78</v>
       </c>
       <c r="G82" t="n">
-        <v>246.7</v>
+        <v>226.9</v>
       </c>
       <c r="H82" t="n">
-        <v>81.3</v>
+        <v>86.8</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-7.64</v>
+        <v>-17.01</v>
       </c>
       <c r="K82" t="n">
-        <v>-101.25</v>
+        <v>-119.06</v>
       </c>
       <c r="L82" t="n">
-        <v>101.54</v>
+        <v>120.27</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>2.95</v>
       </c>
       <c r="F83" t="n">
-        <v>12.07</v>
+        <v>11.26</v>
       </c>
       <c r="G83" t="n">
-        <v>216.2</v>
+        <v>226.9</v>
       </c>
       <c r="H83" t="n">
-        <v>79.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-18.02</v>
+        <v>-102.36</v>
       </c>
       <c r="K83" t="n">
-        <v>9.869999999999999</v>
+        <v>-31.67</v>
       </c>
       <c r="L83" t="n">
-        <v>20.54</v>
+        <v>107.14</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>3.65</v>
       </c>
       <c r="F84" t="n">
-        <v>12.44</v>
+        <v>11.88</v>
       </c>
       <c r="G84" t="n">
-        <v>230.1</v>
+        <v>234.5</v>
       </c>
       <c r="H84" t="n">
-        <v>75.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-126.51</v>
+        <v>-146.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-119.26</v>
+        <v>-131.13</v>
       </c>
       <c r="L84" t="n">
-        <v>173.86</v>
+        <v>196.68</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>3.35</v>
       </c>
       <c r="F85" t="n">
-        <v>12.18</v>
+        <v>10.22</v>
       </c>
       <c r="G85" t="n">
-        <v>241.5</v>
+        <v>229.2</v>
       </c>
       <c r="H85" t="n">
-        <v>77.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-178.61</v>
+        <v>-215.9</v>
       </c>
       <c r="K85" t="n">
-        <v>134.11</v>
+        <v>137.62</v>
       </c>
       <c r="L85" t="n">
-        <v>223.35</v>
+        <v>256.03</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>5.16</v>
       </c>
       <c r="F86" t="n">
-        <v>11.8</v>
+        <v>14.14</v>
       </c>
       <c r="G86" t="n">
-        <v>231</v>
+        <v>221.7</v>
       </c>
       <c r="H86" t="n">
-        <v>81.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>-214.2</v>
+        <v>-223.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-183.12</v>
+        <v>-216.38</v>
       </c>
       <c r="L86" t="n">
-        <v>281.81</v>
+        <v>311.01</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>3.63</v>
       </c>
       <c r="F87" t="n">
-        <v>12.31</v>
+        <v>14.14</v>
       </c>
       <c r="G87" t="n">
-        <v>227</v>
+        <v>231.8</v>
       </c>
       <c r="H87" t="n">
-        <v>81</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-129.81</v>
+        <v>-172.34</v>
       </c>
       <c r="K87" t="n">
-        <v>216.94</v>
+        <v>211.69</v>
       </c>
       <c r="L87" t="n">
-        <v>252.81</v>
+        <v>272.97</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>3.61</v>
       </c>
       <c r="F88" t="n">
-        <v>11.94</v>
+        <v>10.61</v>
       </c>
       <c r="G88" t="n">
-        <v>236.8</v>
+        <v>224.5</v>
       </c>
       <c r="H88" t="n">
-        <v>73.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="I88" t="n">
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>161.34</v>
+        <v>159.26</v>
       </c>
       <c r="K88" t="n">
-        <v>-69.52</v>
+        <v>-131.03</v>
       </c>
       <c r="L88" t="n">
-        <v>175.68</v>
+        <v>206.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>49.76</v>
+        <v>51.59</v>
       </c>
       <c r="K14" t="n">
-        <v>63.13</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>80.39</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.97</v>
+        <v>-6.68</v>
       </c>
       <c r="K15" t="n">
-        <v>64.91</v>
+        <v>62.21</v>
       </c>
       <c r="L15" t="n">
-        <v>65.29000000000001</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>38.31</v>
+        <v>35.87</v>
       </c>
       <c r="K16" t="n">
-        <v>-56.95</v>
+        <v>-53.31</v>
       </c>
       <c r="L16" t="n">
-        <v>68.64</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>-16.82</v>
+        <v>-17.15</v>
       </c>
       <c r="K17" t="n">
-        <v>-113.13</v>
+        <v>-115.35</v>
       </c>
       <c r="L17" t="n">
-        <v>114.37</v>
+        <v>116.62</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-11.79</v>
+        <v>-11.03</v>
       </c>
       <c r="K18" t="n">
-        <v>-114.27</v>
+        <v>-106.98</v>
       </c>
       <c r="L18" t="n">
-        <v>114.88</v>
+        <v>107.54</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-48.3</v>
+        <v>-44.06</v>
       </c>
       <c r="K19" t="n">
-        <v>72.58</v>
+        <v>66.22</v>
       </c>
       <c r="L19" t="n">
-        <v>87.19</v>
+        <v>79.54000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -934,13 +934,13 @@
         <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.24</v>
+        <v>-10.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-58.91</v>
+        <v>-57.71</v>
       </c>
       <c r="L21" t="n">
-        <v>59.79</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-115.91</v>
+        <v>-113.48</v>
       </c>
       <c r="K22" t="n">
-        <v>-47.28</v>
+        <v>-46.29</v>
       </c>
       <c r="L22" t="n">
-        <v>125.18</v>
+        <v>122.56</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-161.55</v>
+        <v>-158.34</v>
       </c>
       <c r="K23" t="n">
-        <v>177.26</v>
+        <v>173.73</v>
       </c>
       <c r="L23" t="n">
-        <v>239.83</v>
+        <v>235.06</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.73</v>
+        <v>-0.68</v>
       </c>
       <c r="K24" t="n">
-        <v>125.03</v>
+        <v>117.05</v>
       </c>
       <c r="L24" t="n">
-        <v>125.03</v>
+        <v>117.05</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>17.94</v>
+        <v>18.3</v>
       </c>
       <c r="K25" t="n">
-        <v>161.33</v>
+        <v>164.5</v>
       </c>
       <c r="L25" t="n">
-        <v>162.33</v>
+        <v>165.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>7.53</v>
+        <v>6.88</v>
       </c>
       <c r="K26" t="n">
-        <v>168.14</v>
+        <v>153.52</v>
       </c>
       <c r="L26" t="n">
-        <v>168.31</v>
+        <v>153.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>46.95</v>
+        <v>46.98</v>
       </c>
       <c r="K27" t="n">
-        <v>-172.27</v>
+        <v>-172.36</v>
       </c>
       <c r="L27" t="n">
-        <v>178.55</v>
+        <v>178.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-234.77</v>
+        <v>-229.98</v>
       </c>
       <c r="K28" t="n">
-        <v>-40.95</v>
+        <v>-40.12</v>
       </c>
       <c r="L28" t="n">
-        <v>238.31</v>
+        <v>233.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-68.37</v>
+        <v>-71</v>
       </c>
       <c r="K29" t="n">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="L29" t="n">
-        <v>68.56999999999999</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-25.01</v>
+        <v>-23.96</v>
       </c>
       <c r="K30" t="n">
-        <v>73.56</v>
+        <v>70.5</v>
       </c>
       <c r="L30" t="n">
-        <v>77.7</v>
+        <v>74.45999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>79.31</v>
+        <v>72.42</v>
       </c>
       <c r="K31" t="n">
-        <v>-22.56</v>
+        <v>-20.6</v>
       </c>
       <c r="L31" t="n">
-        <v>82.45999999999999</v>
+        <v>75.29000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-31.76</v>
+        <v>-29.73</v>
       </c>
       <c r="K32" t="n">
-        <v>-83.75</v>
+        <v>-78.41</v>
       </c>
       <c r="L32" t="n">
-        <v>89.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-94.59</v>
+        <v>-94.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-48.27</v>
+        <v>-48.2</v>
       </c>
       <c r="L33" t="n">
-        <v>106.2</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-31.02</v>
+        <v>-28.31</v>
       </c>
       <c r="K34" t="n">
-        <v>-96.5</v>
+        <v>-88.06999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>101.36</v>
+        <v>92.51000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-148.74</v>
+        <v>-148.61</v>
       </c>
       <c r="K35" t="n">
-        <v>81.45999999999999</v>
+        <v>81.39</v>
       </c>
       <c r="L35" t="n">
-        <v>169.59</v>
+        <v>169.44</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.05</v>
+        <v>-18.41</v>
       </c>
       <c r="K36" t="n">
-        <v>-23.16</v>
+        <v>-23.61</v>
       </c>
       <c r="L36" t="n">
-        <v>29.36</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>103.11</v>
+        <v>107.08</v>
       </c>
       <c r="K37" t="n">
-        <v>44.91</v>
+        <v>46.64</v>
       </c>
       <c r="L37" t="n">
-        <v>112.47</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-168.64</v>
+        <v>-165.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-11.16</v>
+        <v>-10.93</v>
       </c>
       <c r="L38" t="n">
-        <v>169.01</v>
+        <v>165.56</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-180.83</v>
+        <v>-184.38</v>
       </c>
       <c r="K39" t="n">
-        <v>164.2</v>
+        <v>167.42</v>
       </c>
       <c r="L39" t="n">
-        <v>244.26</v>
+        <v>249.05</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>58.83</v>
+        <v>55.08</v>
       </c>
       <c r="K40" t="n">
-        <v>-176.78</v>
+        <v>-165.5</v>
       </c>
       <c r="L40" t="n">
-        <v>186.32</v>
+        <v>174.42</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-53.17</v>
+        <v>-50.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-198.85</v>
+        <v>-190.57</v>
       </c>
       <c r="L41" t="n">
-        <v>205.84</v>
+        <v>197.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-286.81</v>
+        <v>-266.71</v>
       </c>
       <c r="K42" t="n">
-        <v>-123.42</v>
+        <v>-114.77</v>
       </c>
       <c r="L42" t="n">
-        <v>312.23</v>
+        <v>290.35</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>291.31</v>
+        <v>292.1</v>
       </c>
       <c r="K43" t="n">
-        <v>19.46</v>
+        <v>19.51</v>
       </c>
       <c r="L43" t="n">
-        <v>291.96</v>
+        <v>292.75</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>63.34</v>
+        <v>64.58</v>
       </c>
       <c r="K44" t="n">
-        <v>49.1</v>
+        <v>50.06</v>
       </c>
       <c r="L44" t="n">
-        <v>80.14</v>
+        <v>81.70999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-63.88</v>
+        <v>-62.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-42.52</v>
+        <v>-41.65</v>
       </c>
       <c r="L45" t="n">
-        <v>76.73999999999999</v>
+        <v>75.18000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-63.91</v>
+        <v>-62.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-46.8</v>
+        <v>-45.84</v>
       </c>
       <c r="L46" t="n">
-        <v>79.22</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>62.15</v>
+        <v>63.37</v>
       </c>
       <c r="K47" t="n">
-        <v>-36.41</v>
+        <v>-37.13</v>
       </c>
       <c r="L47" t="n">
-        <v>72.03</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>8.19</v>
+        <v>7.48</v>
       </c>
       <c r="K48" t="n">
-        <v>-76.34999999999999</v>
+        <v>-69.70999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>76.78</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-41.68</v>
+        <v>-43.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-97.37</v>
+        <v>-100.75</v>
       </c>
       <c r="L49" t="n">
-        <v>105.92</v>
+        <v>109.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-23.85</v>
+        <v>-24.76</v>
       </c>
       <c r="K50" t="n">
-        <v>-130.63</v>
+        <v>-135.65</v>
       </c>
       <c r="L50" t="n">
-        <v>132.78</v>
+        <v>137.89</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>79.37</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-81.63</v>
+        <v>-76.34999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>113.86</v>
+        <v>106.49</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-132.68</v>
+        <v>-129.84</v>
       </c>
       <c r="K52" t="n">
-        <v>13.56</v>
+        <v>13.27</v>
       </c>
       <c r="L52" t="n">
-        <v>133.37</v>
+        <v>130.52</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>28</v>
       </c>
       <c r="J53" t="n">
-        <v>-107.25</v>
+        <v>-97.92</v>
       </c>
       <c r="K53" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="L53" t="n">
-        <v>107.27</v>
+        <v>97.94</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-48.51</v>
+        <v>-45.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-202.59</v>
+        <v>-189.73</v>
       </c>
       <c r="L54" t="n">
-        <v>208.32</v>
+        <v>195.1</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>124.97</v>
+        <v>119.77</v>
       </c>
       <c r="K55" t="n">
-        <v>32.49</v>
+        <v>31.13</v>
       </c>
       <c r="L55" t="n">
-        <v>129.13</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-138.51</v>
+        <v>-132.74</v>
       </c>
       <c r="K56" t="n">
-        <v>205.41</v>
+        <v>196.85</v>
       </c>
       <c r="L56" t="n">
-        <v>247.75</v>
+        <v>237.42</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-118.78</v>
+        <v>-120.95</v>
       </c>
       <c r="K57" t="n">
-        <v>-277.12</v>
+        <v>-282.16</v>
       </c>
       <c r="L57" t="n">
-        <v>301.5</v>
+        <v>306.99</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-162.91</v>
+        <v>-152.58</v>
       </c>
       <c r="K58" t="n">
-        <v>-216.84</v>
+        <v>-203.09</v>
       </c>
       <c r="L58" t="n">
-        <v>271.22</v>
+        <v>254.02</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-24.67</v>
+        <v>-24.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-82.63</v>
+        <v>-80.95</v>
       </c>
       <c r="L59" t="n">
-        <v>86.23999999999999</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-78.29000000000001</v>
+        <v>-73.2</v>
       </c>
       <c r="K60" t="n">
-        <v>-24.06</v>
+        <v>-22.49</v>
       </c>
       <c r="L60" t="n">
-        <v>81.90000000000001</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>14.33</v>
+        <v>13.41</v>
       </c>
       <c r="K61" t="n">
-        <v>-77.18000000000001</v>
+        <v>-72.2</v>
       </c>
       <c r="L61" t="n">
-        <v>78.48999999999999</v>
+        <v>73.43000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-91.77</v>
+        <v>-87.94</v>
       </c>
       <c r="K62" t="n">
-        <v>42.98</v>
+        <v>41.19</v>
       </c>
       <c r="L62" t="n">
-        <v>101.33</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>8.18</v>
+        <v>7.82</v>
       </c>
       <c r="K63" t="n">
-        <v>-63.11</v>
+        <v>-60.39</v>
       </c>
       <c r="L63" t="n">
-        <v>63.64</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>77.8</v>
+        <v>74.5</v>
       </c>
       <c r="K64" t="n">
-        <v>45.01</v>
+        <v>43.1</v>
       </c>
       <c r="L64" t="n">
-        <v>89.88</v>
+        <v>86.06999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-131.39</v>
+        <v>-133.92</v>
       </c>
       <c r="K65" t="n">
-        <v>86.95999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="L65" t="n">
-        <v>157.56</v>
+        <v>160.6</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-66.06</v>
+        <v>-63.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-73.47</v>
+        <v>-70.36</v>
       </c>
       <c r="L66" t="n">
-        <v>98.8</v>
+        <v>94.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-47.19</v>
+        <v>-44.16</v>
       </c>
       <c r="K67" t="n">
-        <v>-13.79</v>
+        <v>-12.91</v>
       </c>
       <c r="L67" t="n">
-        <v>49.16</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>171.66</v>
+        <v>160.71</v>
       </c>
       <c r="K68" t="n">
-        <v>12.39</v>
+        <v>11.6</v>
       </c>
       <c r="L68" t="n">
-        <v>172.11</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>-178.23</v>
+        <v>-178.36</v>
       </c>
       <c r="K69" t="n">
-        <v>29.06</v>
+        <v>29.08</v>
       </c>
       <c r="L69" t="n">
-        <v>180.58</v>
+        <v>180.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-88.86</v>
+        <v>-88.87</v>
       </c>
       <c r="K70" t="n">
-        <v>105.48</v>
+        <v>105.5</v>
       </c>
       <c r="L70" t="n">
-        <v>137.92</v>
+        <v>137.95</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-256.07</v>
+        <v>-257.83</v>
       </c>
       <c r="K71" t="n">
-        <v>196.95</v>
+        <v>198.31</v>
       </c>
       <c r="L71" t="n">
-        <v>323.05</v>
+        <v>325.27</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>303.55</v>
+        <v>309.83</v>
       </c>
       <c r="K72" t="n">
-        <v>103.83</v>
+        <v>105.98</v>
       </c>
       <c r="L72" t="n">
-        <v>320.81</v>
+        <v>327.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-237.92</v>
+        <v>-242.69</v>
       </c>
       <c r="K73" t="n">
-        <v>-146.55</v>
+        <v>-149.49</v>
       </c>
       <c r="L73" t="n">
-        <v>279.43</v>
+        <v>285.04</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>42.52</v>
+        <v>41.41</v>
       </c>
       <c r="K74" t="n">
-        <v>-81.62</v>
+        <v>-79.48999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>92.03</v>
+        <v>89.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-33.44</v>
+        <v>-34.58</v>
       </c>
       <c r="K75" t="n">
-        <v>-66.42</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>74.37</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-71.15000000000001</v>
+        <v>-73.55</v>
       </c>
       <c r="K76" t="n">
-        <v>11.91</v>
+        <v>12.31</v>
       </c>
       <c r="L76" t="n">
-        <v>72.14</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>62.63</v>
+        <v>57.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-8.52</v>
+        <v>-7.77</v>
       </c>
       <c r="L77" t="n">
-        <v>63.21</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-124.18</v>
+        <v>-113.21</v>
       </c>
       <c r="K78" t="n">
-        <v>78.59</v>
+        <v>71.64</v>
       </c>
       <c r="L78" t="n">
-        <v>146.96</v>
+        <v>133.98</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-122.44</v>
+        <v>-126.37</v>
       </c>
       <c r="K79" t="n">
-        <v>71.98999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="L79" t="n">
-        <v>142.04</v>
+        <v>146.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>126.78</v>
+        <v>124.07</v>
       </c>
       <c r="K80" t="n">
-        <v>-77.48</v>
+        <v>-75.81999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>148.58</v>
+        <v>145.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-105.95</v>
+        <v>-96.7</v>
       </c>
       <c r="K81" t="n">
-        <v>-51.39</v>
+        <v>-46.9</v>
       </c>
       <c r="L81" t="n">
-        <v>117.75</v>
+        <v>107.48</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-17.01</v>
+        <v>-15.53</v>
       </c>
       <c r="K82" t="n">
-        <v>-119.06</v>
+        <v>-108.68</v>
       </c>
       <c r="L82" t="n">
-        <v>120.27</v>
+        <v>109.79</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-102.36</v>
+        <v>-95.81999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-31.67</v>
+        <v>-29.65</v>
       </c>
       <c r="L83" t="n">
-        <v>107.14</v>
+        <v>100.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-146.59</v>
+        <v>-137.29</v>
       </c>
       <c r="K84" t="n">
-        <v>-131.13</v>
+        <v>-122.82</v>
       </c>
       <c r="L84" t="n">
-        <v>196.68</v>
+        <v>184.21</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-215.9</v>
+        <v>-202.14</v>
       </c>
       <c r="K85" t="n">
-        <v>137.62</v>
+        <v>128.85</v>
       </c>
       <c r="L85" t="n">
-        <v>256.03</v>
+        <v>239.72</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>-223.4</v>
+        <v>-207.9</v>
       </c>
       <c r="K86" t="n">
-        <v>-216.38</v>
+        <v>-201.37</v>
       </c>
       <c r="L86" t="n">
-        <v>311.01</v>
+        <v>289.44</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>-172.34</v>
+        <v>-157.85</v>
       </c>
       <c r="K87" t="n">
-        <v>211.69</v>
+        <v>193.9</v>
       </c>
       <c r="L87" t="n">
-        <v>272.97</v>
+        <v>250.03</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>159.26</v>
+        <v>149.54</v>
       </c>
       <c r="K88" t="n">
-        <v>-131.03</v>
+        <v>-123.03</v>
       </c>
       <c r="L88" t="n">
-        <v>206.23</v>
+        <v>193.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.58</v>
+        <v>2.72</v>
       </c>
       <c r="F14" t="n">
-        <v>9.279999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="G14" t="n">
-        <v>227.9</v>
+        <v>226.3</v>
       </c>
       <c r="H14" t="n">
-        <v>77.2</v>
+        <v>26.9</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>51.59</v>
+        <v>-29.15</v>
       </c>
       <c r="K14" t="n">
-        <v>65.45999999999999</v>
+        <v>-25.5</v>
       </c>
       <c r="L14" t="n">
-        <v>83.34</v>
+        <v>38.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:04</t>
+          <t>04:40:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.24</v>
+        <v>3.28</v>
       </c>
       <c r="F15" t="n">
-        <v>6.53</v>
+        <v>11.84</v>
       </c>
       <c r="G15" t="n">
-        <v>225.1</v>
+        <v>232.8</v>
       </c>
       <c r="H15" t="n">
-        <v>86</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.68</v>
+        <v>22.52</v>
       </c>
       <c r="K15" t="n">
-        <v>62.21</v>
+        <v>-46.48</v>
       </c>
       <c r="L15" t="n">
-        <v>62.57</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:42:17</t>
+          <t>04:42:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="F16" t="n">
-        <v>9.67</v>
+        <v>8.48</v>
       </c>
       <c r="G16" t="n">
-        <v>232.9</v>
+        <v>218</v>
       </c>
       <c r="H16" t="n">
-        <v>84.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>35.87</v>
+        <v>13.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-53.31</v>
+        <v>-66.15000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>64.26000000000001</v>
+        <v>67.56999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:46:36</t>
+          <t>04:46:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.17</v>
+        <v>4.03</v>
       </c>
       <c r="F17" t="n">
-        <v>13.84</v>
+        <v>11.41</v>
       </c>
       <c r="G17" t="n">
-        <v>215.3</v>
+        <v>242</v>
       </c>
       <c r="H17" t="n">
-        <v>82</v>
+        <v>32.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.15</v>
+        <v>53.79</v>
       </c>
       <c r="K17" t="n">
-        <v>-115.35</v>
+        <v>-54.88</v>
       </c>
       <c r="L17" t="n">
-        <v>116.62</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:48:01</t>
+          <t>04:47:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="F18" t="n">
-        <v>11.68</v>
+        <v>11.88</v>
       </c>
       <c r="G18" t="n">
-        <v>217.3</v>
+        <v>232.8</v>
       </c>
       <c r="H18" t="n">
-        <v>84.90000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-11.03</v>
+        <v>-67.2</v>
       </c>
       <c r="K18" t="n">
-        <v>-106.98</v>
+        <v>-19.29</v>
       </c>
       <c r="L18" t="n">
-        <v>107.54</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:07</t>
+          <t>04:49:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="F19" t="n">
-        <v>14.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>235.7</v>
+        <v>229.9</v>
       </c>
       <c r="H19" t="n">
-        <v>75.7</v>
+        <v>39.1</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-44.06</v>
+        <v>28.42</v>
       </c>
       <c r="K19" t="n">
-        <v>66.22</v>
+        <v>-63.11</v>
       </c>
       <c r="L19" t="n">
-        <v>79.54000000000001</v>
+        <v>69.20999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:54:37</t>
+          <t>04:52:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="F20" t="n">
-        <v>8.93</v>
+        <v>9.19</v>
       </c>
       <c r="G20" t="n">
-        <v>234.7</v>
+        <v>219.8</v>
       </c>
       <c r="H20" t="n">
-        <v>69</v>
+        <v>52.5</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>-87.34</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>73.36</v>
+        <v>43.28</v>
       </c>
       <c r="L20" t="n">
-        <v>114.06</v>
+        <v>92.93000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:56:38</t>
+          <t>04:54:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>10.32</v>
+        <v>8.24</v>
       </c>
       <c r="G21" t="n">
-        <v>228.9</v>
+        <v>225.1</v>
       </c>
       <c r="H21" t="n">
-        <v>83.59999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.04</v>
+        <v>63.13</v>
       </c>
       <c r="K21" t="n">
-        <v>-57.71</v>
+        <v>-45.03</v>
       </c>
       <c r="L21" t="n">
-        <v>58.57</v>
+        <v>77.54000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:58:31</t>
+          <t>04:56:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.53</v>
+        <v>3.05</v>
       </c>
       <c r="F22" t="n">
-        <v>10.15</v>
+        <v>7.76</v>
       </c>
       <c r="G22" t="n">
-        <v>214.5</v>
+        <v>246.7</v>
       </c>
       <c r="H22" t="n">
-        <v>75</v>
+        <v>61.7</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-113.48</v>
+        <v>52.65</v>
       </c>
       <c r="K22" t="n">
-        <v>-46.29</v>
+        <v>68.52</v>
       </c>
       <c r="L22" t="n">
-        <v>122.56</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:03:03</t>
+          <t>05:00:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.7</v>
+        <v>4.71</v>
       </c>
       <c r="F23" t="n">
-        <v>13.68</v>
+        <v>13.45</v>
       </c>
       <c r="G23" t="n">
-        <v>230.6</v>
+        <v>230.7</v>
       </c>
       <c r="H23" t="n">
-        <v>84.8</v>
+        <v>50.9</v>
       </c>
       <c r="I23" t="n">
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-158.34</v>
+        <v>-201.99</v>
       </c>
       <c r="K23" t="n">
-        <v>173.73</v>
+        <v>123.27</v>
       </c>
       <c r="L23" t="n">
-        <v>235.06</v>
+        <v>236.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:05:30</t>
+          <t>05:02:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="F24" t="n">
-        <v>8.779999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="G24" t="n">
-        <v>232.8</v>
+        <v>229.6</v>
       </c>
       <c r="H24" t="n">
-        <v>79.40000000000001</v>
+        <v>57.7</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.68</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>117.05</v>
+        <v>96.3</v>
       </c>
       <c r="L24" t="n">
-        <v>117.05</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:07:38</t>
+          <t>05:04:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="F25" t="n">
-        <v>9.119999999999999</v>
+        <v>11.67</v>
       </c>
       <c r="G25" t="n">
-        <v>220.2</v>
+        <v>233.3</v>
       </c>
       <c r="H25" t="n">
-        <v>76.8</v>
+        <v>62.8</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>18.3</v>
+        <v>-67.48</v>
       </c>
       <c r="K25" t="n">
-        <v>164.5</v>
+        <v>159.83</v>
       </c>
       <c r="L25" t="n">
-        <v>165.51</v>
+        <v>173.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:12:05</t>
+          <t>05:09:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="F26" t="n">
-        <v>9.92</v>
+        <v>11.7</v>
       </c>
       <c r="G26" t="n">
-        <v>226.9</v>
+        <v>248.2</v>
       </c>
       <c r="H26" t="n">
-        <v>79.2</v>
+        <v>60.5</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>6.88</v>
+        <v>-62.79</v>
       </c>
       <c r="K26" t="n">
-        <v>153.52</v>
+        <v>-142.66</v>
       </c>
       <c r="L26" t="n">
-        <v>153.67</v>
+        <v>155.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:13:54</t>
+          <t>05:10:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.31</v>
+        <v>2.69</v>
       </c>
       <c r="F27" t="n">
-        <v>9.02</v>
+        <v>10.11</v>
       </c>
       <c r="G27" t="n">
-        <v>221.1</v>
+        <v>239.8</v>
       </c>
       <c r="H27" t="n">
-        <v>80.2</v>
+        <v>20.5</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>46.98</v>
+        <v>-203.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-172.36</v>
+        <v>-75.48</v>
       </c>
       <c r="L27" t="n">
-        <v>178.65</v>
+        <v>217.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:15:57</t>
+          <t>05:12:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.35</v>
+        <v>3.48</v>
       </c>
       <c r="F28" t="n">
-        <v>6.51</v>
+        <v>10.04</v>
       </c>
       <c r="G28" t="n">
-        <v>252.4</v>
+        <v>228.3</v>
       </c>
       <c r="H28" t="n">
-        <v>81.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>-229.98</v>
+        <v>-11.31</v>
       </c>
       <c r="K28" t="n">
-        <v>-40.12</v>
+        <v>-289.7</v>
       </c>
       <c r="L28" t="n">
-        <v>233.45</v>
+        <v>289.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:28:59</t>
+          <t>05:22:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="F29" t="n">
-        <v>13.63</v>
+        <v>11.65</v>
       </c>
       <c r="G29" t="n">
-        <v>231.6</v>
+        <v>216</v>
       </c>
       <c r="H29" t="n">
-        <v>81.3</v>
+        <v>33.2</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>-71</v>
+        <v>-22.49</v>
       </c>
       <c r="K29" t="n">
-        <v>5.45</v>
+        <v>-37.69</v>
       </c>
       <c r="L29" t="n">
-        <v>71.20999999999999</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:30:41</t>
+          <t>05:23:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="F30" t="n">
-        <v>13.36</v>
+        <v>14.14</v>
       </c>
       <c r="G30" t="n">
-        <v>212.6</v>
+        <v>231</v>
       </c>
       <c r="H30" t="n">
-        <v>81.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="I30" t="n">
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.96</v>
+        <v>2.76</v>
       </c>
       <c r="K30" t="n">
-        <v>70.5</v>
+        <v>57.2</v>
       </c>
       <c r="L30" t="n">
-        <v>74.45999999999999</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:32:57</t>
+          <t>05:25:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.21</v>
+        <v>3.85</v>
       </c>
       <c r="F31" t="n">
-        <v>11.16</v>
+        <v>13.74</v>
       </c>
       <c r="G31" t="n">
-        <v>238.5</v>
+        <v>228.1</v>
       </c>
       <c r="H31" t="n">
-        <v>74.3</v>
+        <v>39.4</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>72.42</v>
+        <v>-67.69</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.6</v>
+        <v>34.87</v>
       </c>
       <c r="L31" t="n">
-        <v>75.29000000000001</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:37:21</t>
+          <t>05:29:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.81</v>
+        <v>3.21</v>
       </c>
       <c r="F32" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="G32" t="n">
-        <v>235.8</v>
+        <v>233.9</v>
       </c>
       <c r="H32" t="n">
-        <v>78</v>
+        <v>46.9</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-29.73</v>
+        <v>111.48</v>
       </c>
       <c r="K32" t="n">
-        <v>-78.41</v>
+        <v>-1.48</v>
       </c>
       <c r="L32" t="n">
-        <v>83.84999999999999</v>
+        <v>111.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:38:47</t>
+          <t>05:31:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.56</v>
+        <v>3.36</v>
       </c>
       <c r="F33" t="n">
-        <v>13.7</v>
+        <v>14.14</v>
       </c>
       <c r="G33" t="n">
-        <v>229.7</v>
+        <v>227.5</v>
       </c>
       <c r="H33" t="n">
-        <v>83.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-94.44</v>
+        <v>71.3</v>
       </c>
       <c r="K33" t="n">
-        <v>-48.2</v>
+        <v>-90.95</v>
       </c>
       <c r="L33" t="n">
-        <v>106.03</v>
+        <v>115.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:40:42</t>
+          <t>05:32:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.33</v>
+        <v>3.48</v>
       </c>
       <c r="F34" t="n">
-        <v>12.26</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>228</v>
+        <v>223.2</v>
       </c>
       <c r="H34" t="n">
-        <v>85.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-28.31</v>
+        <v>-22.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-88.06999999999999</v>
+        <v>-62.42</v>
       </c>
       <c r="L34" t="n">
-        <v>92.51000000000001</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:45:41</t>
+          <t>05:36:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.74</v>
+        <v>2.87</v>
       </c>
       <c r="F35" t="n">
-        <v>11.45</v>
+        <v>10.81</v>
       </c>
       <c r="G35" t="n">
-        <v>239.7</v>
+        <v>239.1</v>
       </c>
       <c r="H35" t="n">
-        <v>74.5</v>
+        <v>91.3</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-148.61</v>
+        <v>-74.79000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>81.39</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>169.44</v>
+        <v>122.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:48:02</t>
+          <t>05:38:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.12</v>
+        <v>2.68</v>
       </c>
       <c r="F36" t="n">
-        <v>6.91</v>
+        <v>9.66</v>
       </c>
       <c r="G36" t="n">
-        <v>228.3</v>
+        <v>227.7</v>
       </c>
       <c r="H36" t="n">
-        <v>80.09999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.41</v>
+        <v>2.31</v>
       </c>
       <c r="K36" t="n">
-        <v>-23.61</v>
+        <v>-112.8</v>
       </c>
       <c r="L36" t="n">
-        <v>29.94</v>
+        <v>112.82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:49:42</t>
+          <t>05:40:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.18</v>
+        <v>2.65</v>
       </c>
       <c r="F37" t="n">
-        <v>10.73</v>
+        <v>10.79</v>
       </c>
       <c r="G37" t="n">
-        <v>238.7</v>
+        <v>226.3</v>
       </c>
       <c r="H37" t="n">
-        <v>81.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>107.08</v>
+        <v>-90.47</v>
       </c>
       <c r="K37" t="n">
-        <v>46.64</v>
+        <v>-14.3</v>
       </c>
       <c r="L37" t="n">
-        <v>116.79</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:55:51</t>
+          <t>05:45:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.77</v>
+        <v>3.69</v>
       </c>
       <c r="F38" t="n">
-        <v>14.14</v>
+        <v>9.41</v>
       </c>
       <c r="G38" t="n">
-        <v>228.7</v>
+        <v>224</v>
       </c>
       <c r="H38" t="n">
-        <v>77.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-165.2</v>
+        <v>-58.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-10.93</v>
+        <v>180.27</v>
       </c>
       <c r="L38" t="n">
-        <v>165.56</v>
+        <v>189.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:57:50</t>
+          <t>05:47:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="F39" t="n">
-        <v>10.64</v>
+        <v>10.27</v>
       </c>
       <c r="G39" t="n">
-        <v>229.8</v>
+        <v>228.6</v>
       </c>
       <c r="H39" t="n">
-        <v>79.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-184.38</v>
+        <v>29.89</v>
       </c>
       <c r="K39" t="n">
-        <v>167.42</v>
+        <v>-144.17</v>
       </c>
       <c r="L39" t="n">
-        <v>249.05</v>
+        <v>147.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:00:17</t>
+          <t>05:49:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.87</v>
+        <v>3.85</v>
       </c>
       <c r="F40" t="n">
-        <v>13.25</v>
+        <v>10.89</v>
       </c>
       <c r="G40" t="n">
-        <v>228.2</v>
+        <v>237</v>
       </c>
       <c r="H40" t="n">
-        <v>77.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>55.08</v>
+        <v>-70.95</v>
       </c>
       <c r="K40" t="n">
-        <v>-165.5</v>
+        <v>-244.05</v>
       </c>
       <c r="L40" t="n">
-        <v>174.42</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:04:20</t>
+          <t>05:54:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.22</v>
+        <v>3.57</v>
       </c>
       <c r="F41" t="n">
-        <v>8.85</v>
+        <v>14.14</v>
       </c>
       <c r="G41" t="n">
-        <v>232.5</v>
+        <v>233.1</v>
       </c>
       <c r="H41" t="n">
-        <v>79.7</v>
+        <v>55.7</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-50.96</v>
+        <v>-214.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-190.57</v>
+        <v>157.79</v>
       </c>
       <c r="L41" t="n">
-        <v>197.26</v>
+        <v>266.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:05:46</t>
+          <t>05:56:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.02</v>
+        <v>2.84</v>
       </c>
       <c r="F42" t="n">
-        <v>14.03</v>
+        <v>9.9</v>
       </c>
       <c r="G42" t="n">
-        <v>236.4</v>
+        <v>225.3</v>
       </c>
       <c r="H42" t="n">
-        <v>80.5</v>
+        <v>50.2</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J42" t="n">
-        <v>-266.71</v>
+        <v>-66.72</v>
       </c>
       <c r="K42" t="n">
-        <v>-114.77</v>
+        <v>-164.58</v>
       </c>
       <c r="L42" t="n">
-        <v>290.35</v>
+        <v>177.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:07:09</t>
+          <t>05:57:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.57</v>
+        <v>3.28</v>
       </c>
       <c r="F43" t="n">
-        <v>14.12</v>
+        <v>10.5</v>
       </c>
       <c r="G43" t="n">
-        <v>229.9</v>
+        <v>239.3</v>
       </c>
       <c r="H43" t="n">
-        <v>78.2</v>
+        <v>57.7</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>292.1</v>
+        <v>-163.12</v>
       </c>
       <c r="K43" t="n">
-        <v>19.51</v>
+        <v>91.7</v>
       </c>
       <c r="L43" t="n">
-        <v>292.75</v>
+        <v>187.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:17:30</t>
+          <t>06:06:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.93</v>
+        <v>3.19</v>
       </c>
       <c r="F44" t="n">
-        <v>7.92</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>222.3</v>
+        <v>230.4</v>
       </c>
       <c r="H44" t="n">
-        <v>71.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>64.58</v>
+        <v>34.23</v>
       </c>
       <c r="K44" t="n">
-        <v>50.06</v>
+        <v>-50.77</v>
       </c>
       <c r="L44" t="n">
-        <v>81.70999999999999</v>
+        <v>61.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:19:30</t>
+          <t>06:07:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.85</v>
+        <v>3.98</v>
       </c>
       <c r="F45" t="n">
-        <v>8.09</v>
+        <v>13.65</v>
       </c>
       <c r="G45" t="n">
-        <v>238</v>
+        <v>237.9</v>
       </c>
       <c r="H45" t="n">
-        <v>78.5</v>
+        <v>38.5</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-62.58</v>
+        <v>-58.49</v>
       </c>
       <c r="K45" t="n">
-        <v>-41.65</v>
+        <v>-49.36</v>
       </c>
       <c r="L45" t="n">
-        <v>75.18000000000001</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:12</t>
+          <t>06:08:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.18</v>
+        <v>3.57</v>
       </c>
       <c r="F46" t="n">
-        <v>10.91</v>
+        <v>11.02</v>
       </c>
       <c r="G46" t="n">
-        <v>230.9</v>
+        <v>223.5</v>
       </c>
       <c r="H46" t="n">
-        <v>81.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-62.61</v>
+        <v>37.56</v>
       </c>
       <c r="K46" t="n">
-        <v>-45.84</v>
+        <v>-74.81999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>77.59999999999999</v>
+        <v>83.70999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:24:02</t>
+          <t>06:13:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.83</v>
+        <v>3.97</v>
       </c>
       <c r="F47" t="n">
-        <v>9.449999999999999</v>
+        <v>10.77</v>
       </c>
       <c r="G47" t="n">
-        <v>239.4</v>
+        <v>232.5</v>
       </c>
       <c r="H47" t="n">
-        <v>81.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>63.37</v>
+        <v>60.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.13</v>
+        <v>57.6</v>
       </c>
       <c r="L47" t="n">
-        <v>73.44</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:26:03</t>
+          <t>06:15:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.49</v>
+        <v>2.83</v>
       </c>
       <c r="F48" t="n">
-        <v>8.44</v>
+        <v>7.86</v>
       </c>
       <c r="G48" t="n">
-        <v>226.6</v>
+        <v>231.6</v>
       </c>
       <c r="H48" t="n">
-        <v>80</v>
+        <v>24.3</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>7.48</v>
+        <v>-37.16</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.70999999999999</v>
+        <v>-43.29</v>
       </c>
       <c r="L48" t="n">
-        <v>70.11</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:28:06</t>
+          <t>06:16:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="F49" t="n">
-        <v>14.14</v>
+        <v>9.02</v>
       </c>
       <c r="G49" t="n">
-        <v>239.8</v>
+        <v>236.6</v>
       </c>
       <c r="H49" t="n">
-        <v>76.2</v>
+        <v>46.4</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-43.13</v>
+        <v>75.06</v>
       </c>
       <c r="K49" t="n">
-        <v>-100.75</v>
+        <v>45.08</v>
       </c>
       <c r="L49" t="n">
-        <v>109.59</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:33:51</t>
+          <t>06:20:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.73</v>
+        <v>3.74</v>
       </c>
       <c r="F50" t="n">
-        <v>9.24</v>
+        <v>14.14</v>
       </c>
       <c r="G50" t="n">
-        <v>239.5</v>
+        <v>251.8</v>
       </c>
       <c r="H50" t="n">
-        <v>83.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-24.76</v>
+        <v>40.86</v>
       </c>
       <c r="K50" t="n">
-        <v>-135.65</v>
+        <v>109.53</v>
       </c>
       <c r="L50" t="n">
-        <v>137.89</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:34:39</t>
+          <t>06:21:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.77</v>
+        <v>3.38</v>
       </c>
       <c r="F51" t="n">
-        <v>14.14</v>
+        <v>13.57</v>
       </c>
       <c r="G51" t="n">
-        <v>225</v>
+        <v>228.3</v>
       </c>
       <c r="H51" t="n">
-        <v>76.90000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>74.23999999999999</v>
+        <v>39.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-76.34999999999999</v>
+        <v>-131.73</v>
       </c>
       <c r="L51" t="n">
-        <v>106.49</v>
+        <v>137.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:36:02</t>
+          <t>06:22:53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="F52" t="n">
-        <v>14.14</v>
+        <v>12.73</v>
       </c>
       <c r="G52" t="n">
-        <v>231.5</v>
+        <v>244</v>
       </c>
       <c r="H52" t="n">
-        <v>76.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-129.84</v>
+        <v>-33.75</v>
       </c>
       <c r="K52" t="n">
-        <v>13.27</v>
+        <v>148.69</v>
       </c>
       <c r="L52" t="n">
-        <v>130.52</v>
+        <v>152.47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:40:18</t>
+          <t>06:28:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="F53" t="n">
-        <v>10.55</v>
+        <v>13.64</v>
       </c>
       <c r="G53" t="n">
-        <v>236.7</v>
+        <v>234.9</v>
       </c>
       <c r="H53" t="n">
-        <v>81.7</v>
+        <v>62.1</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-97.92</v>
+        <v>-119.08</v>
       </c>
       <c r="K53" t="n">
-        <v>1.83</v>
+        <v>-155.16</v>
       </c>
       <c r="L53" t="n">
-        <v>97.94</v>
+        <v>195.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:42:27</t>
+          <t>06:30:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.56</v>
+        <v>3.24</v>
       </c>
       <c r="F54" t="n">
-        <v>14.14</v>
+        <v>11.04</v>
       </c>
       <c r="G54" t="n">
-        <v>231.3</v>
+        <v>223.9</v>
       </c>
       <c r="H54" t="n">
-        <v>80.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-45.43</v>
+        <v>87.88</v>
       </c>
       <c r="K54" t="n">
-        <v>-189.73</v>
+        <v>125.28</v>
       </c>
       <c r="L54" t="n">
-        <v>195.1</v>
+        <v>153.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:44:05</t>
+          <t>06:30:42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.79</v>
+        <v>3.29</v>
       </c>
       <c r="F55" t="n">
-        <v>10.31</v>
+        <v>12.54</v>
       </c>
       <c r="G55" t="n">
-        <v>232</v>
+        <v>231.3</v>
       </c>
       <c r="H55" t="n">
-        <v>78.7</v>
+        <v>53.8</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>119.77</v>
+        <v>144.84</v>
       </c>
       <c r="K55" t="n">
-        <v>31.13</v>
+        <v>45.89</v>
       </c>
       <c r="L55" t="n">
-        <v>123.75</v>
+        <v>151.93</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:49:30</t>
+          <t>06:34:38</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.14</v>
+        <v>4.9</v>
       </c>
       <c r="F56" t="n">
-        <v>10.47</v>
+        <v>14.14</v>
       </c>
       <c r="G56" t="n">
-        <v>229.8</v>
+        <v>222.9</v>
       </c>
       <c r="H56" t="n">
-        <v>75.8</v>
+        <v>44</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-132.74</v>
+        <v>-384.48</v>
       </c>
       <c r="K56" t="n">
-        <v>196.85</v>
+        <v>83.81</v>
       </c>
       <c r="L56" t="n">
-        <v>237.42</v>
+        <v>393.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:50:34</t>
+          <t>06:37:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.97</v>
+        <v>3.62</v>
       </c>
       <c r="F57" t="n">
-        <v>14.14</v>
+        <v>10.2</v>
       </c>
       <c r="G57" t="n">
-        <v>228.4</v>
+        <v>218</v>
       </c>
       <c r="H57" t="n">
-        <v>78.90000000000001</v>
+        <v>38.1</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-120.95</v>
+        <v>-179.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-282.16</v>
+        <v>-263.08</v>
       </c>
       <c r="L57" t="n">
-        <v>306.99</v>
+        <v>318.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:51:49</t>
+          <t>06:39:32</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.3</v>
+        <v>3.87</v>
       </c>
       <c r="F58" t="n">
-        <v>11.78</v>
+        <v>12.47</v>
       </c>
       <c r="G58" t="n">
-        <v>228.4</v>
+        <v>236.9</v>
       </c>
       <c r="H58" t="n">
-        <v>79.5</v>
+        <v>55.8</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-152.58</v>
+        <v>-279.36</v>
       </c>
       <c r="K58" t="n">
-        <v>-203.09</v>
+        <v>4.04</v>
       </c>
       <c r="L58" t="n">
-        <v>254.02</v>
+        <v>279.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:02:48</t>
+          <t>06:52:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.08</v>
+        <v>3.63</v>
       </c>
       <c r="F59" t="n">
-        <v>8.41</v>
+        <v>14.14</v>
       </c>
       <c r="G59" t="n">
-        <v>241.8</v>
+        <v>227.6</v>
       </c>
       <c r="H59" t="n">
-        <v>81.2</v>
+        <v>24.5</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J59" t="n">
-        <v>-24.17</v>
+        <v>53.54</v>
       </c>
       <c r="K59" t="n">
-        <v>-80.95</v>
+        <v>39.99</v>
       </c>
       <c r="L59" t="n">
-        <v>84.48</v>
+        <v>66.81999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:05:15</t>
+          <t>06:54:39</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="F60" t="n">
-        <v>12.59</v>
+        <v>9.52</v>
       </c>
       <c r="G60" t="n">
-        <v>213.4</v>
+        <v>230</v>
       </c>
       <c r="H60" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-73.2</v>
+        <v>-39.52</v>
       </c>
       <c r="K60" t="n">
-        <v>-22.49</v>
+        <v>63.86</v>
       </c>
       <c r="L60" t="n">
-        <v>76.58</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:07:08</t>
+          <t>06:55:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.39</v>
+        <v>2.92</v>
       </c>
       <c r="F61" t="n">
-        <v>13.36</v>
+        <v>11.21</v>
       </c>
       <c r="G61" t="n">
-        <v>234.1</v>
+        <v>230.9</v>
       </c>
       <c r="H61" t="n">
-        <v>80.7</v>
+        <v>41.9</v>
       </c>
       <c r="I61" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>13.41</v>
+        <v>-11.28</v>
       </c>
       <c r="K61" t="n">
-        <v>-72.2</v>
+        <v>-45.04</v>
       </c>
       <c r="L61" t="n">
-        <v>73.43000000000001</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:11:17</t>
+          <t>07:00:52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="F62" t="n">
-        <v>10.65</v>
+        <v>14.14</v>
       </c>
       <c r="G62" t="n">
-        <v>234.6</v>
+        <v>226.2</v>
       </c>
       <c r="H62" t="n">
-        <v>77.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-87.94</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>41.19</v>
+        <v>72.52</v>
       </c>
       <c r="L62" t="n">
-        <v>97.11</v>
+        <v>105.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:13:23</t>
+          <t>07:01:36</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="F63" t="n">
-        <v>12.76</v>
+        <v>14.14</v>
       </c>
       <c r="G63" t="n">
-        <v>248.5</v>
+        <v>242.1</v>
       </c>
       <c r="H63" t="n">
-        <v>77.90000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>7.82</v>
+        <v>-59.81</v>
       </c>
       <c r="K63" t="n">
-        <v>-60.39</v>
+        <v>47.65</v>
       </c>
       <c r="L63" t="n">
-        <v>60.89</v>
+        <v>76.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:14:41</t>
+          <t>07:02:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="F64" t="n">
-        <v>12.68</v>
+        <v>13.35</v>
       </c>
       <c r="G64" t="n">
-        <v>220.8</v>
+        <v>242.9</v>
       </c>
       <c r="H64" t="n">
-        <v>82</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>74.5</v>
+        <v>-94.08</v>
       </c>
       <c r="K64" t="n">
-        <v>43.1</v>
+        <v>18.41</v>
       </c>
       <c r="L64" t="n">
-        <v>86.06999999999999</v>
+        <v>95.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:19:22</t>
+          <t>07:06:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="F65" t="n">
-        <v>14.14</v>
+        <v>10.84</v>
       </c>
       <c r="G65" t="n">
-        <v>248.7</v>
+        <v>230.4</v>
       </c>
       <c r="H65" t="n">
-        <v>79.3</v>
+        <v>65.5</v>
       </c>
       <c r="I65" t="n">
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-133.92</v>
+        <v>-104</v>
       </c>
       <c r="K65" t="n">
-        <v>88.64</v>
+        <v>105.41</v>
       </c>
       <c r="L65" t="n">
-        <v>160.6</v>
+        <v>148.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:21:21</t>
+          <t>07:07:49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.63</v>
+        <v>3.44</v>
       </c>
       <c r="F66" t="n">
-        <v>10.93</v>
+        <v>11.73</v>
       </c>
       <c r="G66" t="n">
-        <v>231.1</v>
+        <v>222.4</v>
       </c>
       <c r="H66" t="n">
-        <v>80.2</v>
+        <v>31.1</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-63.27</v>
+        <v>73.3</v>
       </c>
       <c r="K66" t="n">
-        <v>-70.36</v>
+        <v>-104.55</v>
       </c>
       <c r="L66" t="n">
-        <v>94.62</v>
+        <v>127.68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:22:35</t>
+          <t>07:08:40</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="F67" t="n">
-        <v>8.85</v>
+        <v>14.14</v>
       </c>
       <c r="G67" t="n">
-        <v>242.2</v>
+        <v>241.2</v>
       </c>
       <c r="H67" t="n">
-        <v>77.3</v>
+        <v>59.4</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-44.16</v>
+        <v>-18.81</v>
       </c>
       <c r="K67" t="n">
-        <v>-12.91</v>
+        <v>130.05</v>
       </c>
       <c r="L67" t="n">
-        <v>46.01</v>
+        <v>131.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:26:43</t>
+          <t>07:14:46</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.53</v>
+        <v>3.55</v>
       </c>
       <c r="F68" t="n">
-        <v>10.29</v>
+        <v>12.1</v>
       </c>
       <c r="G68" t="n">
-        <v>221.6</v>
+        <v>227.7</v>
       </c>
       <c r="H68" t="n">
-        <v>80.3</v>
+        <v>30.5</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>160.71</v>
+        <v>-44.24</v>
       </c>
       <c r="K68" t="n">
-        <v>11.6</v>
+        <v>190.94</v>
       </c>
       <c r="L68" t="n">
-        <v>161.12</v>
+        <v>195.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:28:06</t>
+          <t>07:16:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="F69" t="n">
-        <v>14.14</v>
+        <v>13.03</v>
       </c>
       <c r="G69" t="n">
-        <v>221.4</v>
+        <v>249.2</v>
       </c>
       <c r="H69" t="n">
-        <v>70.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>-178.36</v>
+        <v>8.84</v>
       </c>
       <c r="K69" t="n">
-        <v>29.08</v>
+        <v>-200.2</v>
       </c>
       <c r="L69" t="n">
-        <v>180.72</v>
+        <v>200.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:30:34</t>
+          <t>07:18:33</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="F70" t="n">
-        <v>9.960000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G70" t="n">
-        <v>231.9</v>
+        <v>226.2</v>
       </c>
       <c r="H70" t="n">
-        <v>74.09999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="I70" t="n">
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-88.87</v>
+        <v>-95.91</v>
       </c>
       <c r="K70" t="n">
-        <v>105.5</v>
+        <v>-345.78</v>
       </c>
       <c r="L70" t="n">
-        <v>137.95</v>
+        <v>358.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:36:06</t>
+          <t>07:22:14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.16</v>
+        <v>2.87</v>
       </c>
       <c r="F71" t="n">
-        <v>14.14</v>
+        <v>10</v>
       </c>
       <c r="G71" t="n">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="H71" t="n">
-        <v>82</v>
+        <v>60.2</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-257.83</v>
+        <v>149.36</v>
       </c>
       <c r="K71" t="n">
-        <v>198.31</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>325.27</v>
+        <v>162.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:37:40</t>
+          <t>07:24:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.37</v>
+        <v>3.79</v>
       </c>
       <c r="F72" t="n">
-        <v>12.76</v>
+        <v>14.14</v>
       </c>
       <c r="G72" t="n">
-        <v>234.7</v>
+        <v>226.9</v>
       </c>
       <c r="H72" t="n">
-        <v>83.8</v>
+        <v>34</v>
       </c>
       <c r="I72" t="n">
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>309.83</v>
+        <v>-262.31</v>
       </c>
       <c r="K72" t="n">
-        <v>105.98</v>
+        <v>-227.4</v>
       </c>
       <c r="L72" t="n">
-        <v>327.45</v>
+        <v>347.16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:39:31</t>
+          <t>07:26:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="F73" t="n">
-        <v>14.14</v>
+        <v>12.61</v>
       </c>
       <c r="G73" t="n">
-        <v>240.2</v>
+        <v>242.1</v>
       </c>
       <c r="H73" t="n">
-        <v>82.40000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-242.69</v>
+        <v>-491.36</v>
       </c>
       <c r="K73" t="n">
-        <v>-149.49</v>
+        <v>-224.15</v>
       </c>
       <c r="L73" t="n">
-        <v>285.04</v>
+        <v>540.0700000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:49:41</t>
+          <t>07:34:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.48</v>
+        <v>3.18</v>
       </c>
       <c r="F74" t="n">
-        <v>14.14</v>
+        <v>9.82</v>
       </c>
       <c r="G74" t="n">
-        <v>238.3</v>
+        <v>233.6</v>
       </c>
       <c r="H74" t="n">
-        <v>75.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>41.41</v>
+        <v>51.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.48999999999999</v>
+        <v>22.59</v>
       </c>
       <c r="L74" t="n">
-        <v>89.63</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:50:43</t>
+          <t>07:35:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.16</v>
+        <v>3.67</v>
       </c>
       <c r="F75" t="n">
         <v>14.14</v>
       </c>
       <c r="G75" t="n">
-        <v>238.3</v>
+        <v>224.5</v>
       </c>
       <c r="H75" t="n">
-        <v>74.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-34.58</v>
+        <v>-56.7</v>
       </c>
       <c r="K75" t="n">
-        <v>-68.68000000000001</v>
+        <v>23.67</v>
       </c>
       <c r="L75" t="n">
-        <v>76.89</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:52:42</t>
+          <t>07:36:45</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.19</v>
+        <v>4.07</v>
       </c>
       <c r="F76" t="n">
         <v>14.14</v>
       </c>
       <c r="G76" t="n">
-        <v>240.3</v>
+        <v>244.7</v>
       </c>
       <c r="H76" t="n">
-        <v>76.7</v>
+        <v>56.4</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-73.55</v>
+        <v>47.26</v>
       </c>
       <c r="K76" t="n">
-        <v>12.31</v>
+        <v>-48.07</v>
       </c>
       <c r="L76" t="n">
-        <v>74.58</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:57:20</t>
+          <t>07:41:18</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="F77" t="n">
-        <v>12.19</v>
+        <v>14.14</v>
       </c>
       <c r="G77" t="n">
-        <v>249.5</v>
+        <v>239</v>
       </c>
       <c r="H77" t="n">
-        <v>77.59999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="I77" t="n">
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>57.14</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-7.77</v>
+        <v>-38.03</v>
       </c>
       <c r="L77" t="n">
-        <v>57.67</v>
+        <v>93.26000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:59:08</t>
+          <t>07:42:52</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="F78" t="n">
-        <v>13.39</v>
+        <v>12.23</v>
       </c>
       <c r="G78" t="n">
-        <v>234.9</v>
+        <v>229.8</v>
       </c>
       <c r="H78" t="n">
-        <v>80.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-113.21</v>
+        <v>-61.17</v>
       </c>
       <c r="K78" t="n">
-        <v>71.64</v>
+        <v>5.69</v>
       </c>
       <c r="L78" t="n">
-        <v>133.98</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:00:03</t>
+          <t>07:43:58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.58</v>
+        <v>3.85</v>
       </c>
       <c r="F79" t="n">
         <v>14.14</v>
       </c>
       <c r="G79" t="n">
-        <v>245</v>
+        <v>237.1</v>
       </c>
       <c r="H79" t="n">
-        <v>82.90000000000001</v>
+        <v>52.3</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J79" t="n">
-        <v>-126.37</v>
+        <v>55.56</v>
       </c>
       <c r="K79" t="n">
-        <v>74.3</v>
+        <v>-66.61</v>
       </c>
       <c r="L79" t="n">
-        <v>146.59</v>
+        <v>86.73999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:06:10</t>
+          <t>07:47:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="F80" t="n">
-        <v>11.02</v>
+        <v>14.14</v>
       </c>
       <c r="G80" t="n">
-        <v>231.7</v>
+        <v>226.6</v>
       </c>
       <c r="H80" t="n">
-        <v>74.3</v>
+        <v>55.3</v>
       </c>
       <c r="I80" t="n">
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>124.07</v>
+        <v>75.67</v>
       </c>
       <c r="K80" t="n">
-        <v>-75.81999999999999</v>
+        <v>-120.68</v>
       </c>
       <c r="L80" t="n">
-        <v>145.4</v>
+        <v>142.44</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:07:43</t>
+          <t>07:48:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.43</v>
+        <v>3.13</v>
       </c>
       <c r="F81" t="n">
-        <v>11.66</v>
+        <v>12.77</v>
       </c>
       <c r="G81" t="n">
-        <v>235.4</v>
+        <v>225.6</v>
       </c>
       <c r="H81" t="n">
-        <v>77.40000000000001</v>
+        <v>43.2</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>-96.7</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-46.9</v>
+        <v>-106.79</v>
       </c>
       <c r="L81" t="n">
-        <v>107.48</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:08:31</t>
+          <t>07:49:56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.37</v>
+        <v>3.79</v>
       </c>
       <c r="F82" t="n">
-        <v>13.78</v>
+        <v>13.72</v>
       </c>
       <c r="G82" t="n">
-        <v>226.9</v>
+        <v>238.5</v>
       </c>
       <c r="H82" t="n">
-        <v>86.8</v>
+        <v>68.2</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>-15.53</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-108.68</v>
+        <v>107.8</v>
       </c>
       <c r="L82" t="n">
-        <v>109.79</v>
+        <v>131.08</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:13:23</t>
+          <t>07:54:28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="F83" t="n">
-        <v>11.26</v>
+        <v>11.85</v>
       </c>
       <c r="G83" t="n">
-        <v>226.9</v>
+        <v>235.8</v>
       </c>
       <c r="H83" t="n">
-        <v>71.5</v>
+        <v>59.3</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-95.81999999999999</v>
+        <v>-114.5</v>
       </c>
       <c r="K83" t="n">
-        <v>-29.65</v>
+        <v>-53.36</v>
       </c>
       <c r="L83" t="n">
-        <v>100.31</v>
+        <v>126.32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:14:53</t>
+          <t>07:56:10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="F84" t="n">
-        <v>11.88</v>
+        <v>14.14</v>
       </c>
       <c r="G84" t="n">
-        <v>234.5</v>
+        <v>228.7</v>
       </c>
       <c r="H84" t="n">
-        <v>78.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>-137.29</v>
+        <v>-137.35</v>
       </c>
       <c r="K84" t="n">
-        <v>-122.82</v>
+        <v>-143.36</v>
       </c>
       <c r="L84" t="n">
-        <v>184.21</v>
+        <v>198.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:16:37</t>
+          <t>07:57:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="F85" t="n">
-        <v>10.22</v>
+        <v>11.01</v>
       </c>
       <c r="G85" t="n">
-        <v>229.2</v>
+        <v>245.7</v>
       </c>
       <c r="H85" t="n">
-        <v>84.09999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-202.14</v>
+        <v>-145.16</v>
       </c>
       <c r="K85" t="n">
-        <v>128.85</v>
+        <v>87.75</v>
       </c>
       <c r="L85" t="n">
-        <v>239.72</v>
+        <v>169.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:21:24</t>
+          <t>08:02:01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.16</v>
+        <v>3.97</v>
       </c>
       <c r="F86" t="n">
-        <v>14.14</v>
+        <v>12.26</v>
       </c>
       <c r="G86" t="n">
-        <v>221.7</v>
+        <v>214.3</v>
       </c>
       <c r="H86" t="n">
-        <v>78.90000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-207.9</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-201.37</v>
+        <v>-314.1</v>
       </c>
       <c r="L86" t="n">
-        <v>289.44</v>
+        <v>321.34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:22:41</t>
+          <t>08:04:11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.63</v>
+        <v>4.14</v>
       </c>
       <c r="F87" t="n">
         <v>14.14</v>
       </c>
       <c r="G87" t="n">
-        <v>231.8</v>
+        <v>235</v>
       </c>
       <c r="H87" t="n">
-        <v>76.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-157.85</v>
+        <v>350.5</v>
       </c>
       <c r="K87" t="n">
-        <v>193.9</v>
+        <v>-91.7</v>
       </c>
       <c r="L87" t="n">
-        <v>250.03</v>
+        <v>362.29</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:24:14</t>
+          <t>08:05:25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.61</v>
+        <v>3.33</v>
       </c>
       <c r="F88" t="n">
-        <v>10.61</v>
+        <v>13.67</v>
       </c>
       <c r="G88" t="n">
-        <v>224.5</v>
+        <v>230.8</v>
       </c>
       <c r="H88" t="n">
-        <v>81.8</v>
+        <v>73.3</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>149.54</v>
+        <v>-203.74</v>
       </c>
       <c r="K88" t="n">
-        <v>-123.03</v>
+        <v>-33.12</v>
       </c>
       <c r="L88" t="n">
-        <v>193.65</v>
+        <v>206.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="F14" t="n">
-        <v>7.61</v>
+        <v>8.33</v>
       </c>
       <c r="G14" t="n">
-        <v>226.3</v>
+        <v>224.2</v>
       </c>
       <c r="H14" t="n">
-        <v>26.9</v>
+        <v>95.2</v>
       </c>
       <c r="I14" t="n">
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-29.15</v>
+        <v>42.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.5</v>
+        <v>-4.83</v>
       </c>
       <c r="L14" t="n">
-        <v>38.73</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:07</t>
+          <t>04:40:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="F15" t="n">
-        <v>11.84</v>
+        <v>11.88</v>
       </c>
       <c r="G15" t="n">
-        <v>232.8</v>
+        <v>221.5</v>
       </c>
       <c r="H15" t="n">
-        <v>73.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>22.52</v>
+        <v>30.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-46.48</v>
+        <v>-16.02</v>
       </c>
       <c r="L15" t="n">
-        <v>51.65</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:42:27</t>
+          <t>04:42:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>8.48</v>
+        <v>11.83</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>222.4</v>
       </c>
       <c r="H16" t="n">
-        <v>61.1</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>13.8</v>
+        <v>-29.56</v>
       </c>
       <c r="K16" t="n">
-        <v>-66.15000000000001</v>
+        <v>-19.18</v>
       </c>
       <c r="L16" t="n">
-        <v>67.56999999999999</v>
+        <v>35.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:46:25</t>
+          <t>04:45:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.03</v>
+        <v>3.76</v>
       </c>
       <c r="F17" t="n">
-        <v>11.41</v>
+        <v>12.12</v>
       </c>
       <c r="G17" t="n">
-        <v>242</v>
+        <v>238.9</v>
       </c>
       <c r="H17" t="n">
-        <v>32.7</v>
+        <v>39</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>53.79</v>
+        <v>-54.99</v>
       </c>
       <c r="K17" t="n">
-        <v>-54.88</v>
+        <v>-57.36</v>
       </c>
       <c r="L17" t="n">
-        <v>76.84</v>
+        <v>79.45999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:47:41</t>
+          <t>04:46:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.26</v>
+        <v>2.98</v>
       </c>
       <c r="F18" t="n">
-        <v>11.88</v>
+        <v>10.69</v>
       </c>
       <c r="G18" t="n">
-        <v>232.8</v>
+        <v>229.4</v>
       </c>
       <c r="H18" t="n">
-        <v>32.1</v>
+        <v>75</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.2</v>
+        <v>69.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.29</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>69.91</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:49:26</t>
+          <t>04:48:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="F19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="G19" t="n">
-        <v>229.9</v>
+        <v>230.7</v>
       </c>
       <c r="H19" t="n">
-        <v>39.1</v>
+        <v>67.3</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>28.42</v>
+        <v>37.93</v>
       </c>
       <c r="K19" t="n">
-        <v>-63.11</v>
+        <v>-66.87</v>
       </c>
       <c r="L19" t="n">
-        <v>69.20999999999999</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:52:40</t>
+          <t>04:53:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.39</v>
+        <v>3.38</v>
       </c>
       <c r="F20" t="n">
-        <v>9.19</v>
+        <v>8.18</v>
       </c>
       <c r="G20" t="n">
-        <v>219.8</v>
+        <v>224.2</v>
       </c>
       <c r="H20" t="n">
-        <v>52.5</v>
+        <v>46.1</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>82.23999999999999</v>
+        <v>-17.24</v>
       </c>
       <c r="K20" t="n">
-        <v>43.28</v>
+        <v>117.57</v>
       </c>
       <c r="L20" t="n">
-        <v>92.93000000000001</v>
+        <v>118.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:54:25</t>
+          <t>04:54:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="F21" t="n">
-        <v>8.24</v>
+        <v>12.06</v>
       </c>
       <c r="G21" t="n">
-        <v>225.1</v>
+        <v>234.4</v>
       </c>
       <c r="H21" t="n">
-        <v>44.4</v>
+        <v>63.2</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>63.13</v>
+        <v>62.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-45.03</v>
+        <v>143.64</v>
       </c>
       <c r="L21" t="n">
-        <v>77.54000000000001</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:56:32</t>
+          <t>04:56:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="F22" t="n">
-        <v>7.76</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>246.7</v>
+        <v>222.8</v>
       </c>
       <c r="H22" t="n">
-        <v>61.7</v>
+        <v>59.6</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>52.65</v>
+        <v>86.28</v>
       </c>
       <c r="K22" t="n">
-        <v>68.52</v>
+        <v>-82.94</v>
       </c>
       <c r="L22" t="n">
-        <v>86.41</v>
+        <v>119.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:00:43</t>
+          <t>05:01:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.71</v>
+        <v>2.75</v>
       </c>
       <c r="F23" t="n">
-        <v>13.45</v>
+        <v>10.28</v>
       </c>
       <c r="G23" t="n">
-        <v>230.7</v>
+        <v>221.1</v>
       </c>
       <c r="H23" t="n">
-        <v>50.9</v>
+        <v>59.9</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-201.99</v>
+        <v>-90.39</v>
       </c>
       <c r="K23" t="n">
-        <v>123.27</v>
+        <v>60.98</v>
       </c>
       <c r="L23" t="n">
-        <v>236.63</v>
+        <v>109.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:02:36</t>
+          <t>05:02:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="F24" t="n">
-        <v>11.4</v>
+        <v>13.34</v>
       </c>
       <c r="G24" t="n">
-        <v>229.6</v>
+        <v>240.2</v>
       </c>
       <c r="H24" t="n">
-        <v>57.7</v>
+        <v>45.5</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>95.45999999999999</v>
+        <v>157.44</v>
       </c>
       <c r="K24" t="n">
-        <v>96.3</v>
+        <v>-49.45</v>
       </c>
       <c r="L24" t="n">
-        <v>135.6</v>
+        <v>165.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:04:10</t>
+          <t>05:05:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="F25" t="n">
-        <v>11.67</v>
+        <v>9.84</v>
       </c>
       <c r="G25" t="n">
-        <v>233.3</v>
+        <v>235.5</v>
       </c>
       <c r="H25" t="n">
-        <v>62.8</v>
+        <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-67.48</v>
+        <v>-101.11</v>
       </c>
       <c r="K25" t="n">
-        <v>159.83</v>
+        <v>117.24</v>
       </c>
       <c r="L25" t="n">
-        <v>173.49</v>
+        <v>154.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:09:06</t>
+          <t>05:11:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.19</v>
+        <v>3.74</v>
       </c>
       <c r="F26" t="n">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="G26" t="n">
-        <v>248.2</v>
+        <v>234.8</v>
       </c>
       <c r="H26" t="n">
-        <v>60.5</v>
+        <v>40.2</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-62.79</v>
+        <v>-230.48</v>
       </c>
       <c r="K26" t="n">
-        <v>-142.66</v>
+        <v>-150.75</v>
       </c>
       <c r="L26" t="n">
-        <v>155.87</v>
+        <v>275.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:10:36</t>
+          <t>05:13:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.69</v>
+        <v>4.35</v>
       </c>
       <c r="F27" t="n">
-        <v>10.11</v>
+        <v>12.65</v>
       </c>
       <c r="G27" t="n">
-        <v>239.8</v>
+        <v>220.6</v>
       </c>
       <c r="H27" t="n">
-        <v>20.5</v>
+        <v>53.3</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-203.95</v>
+        <v>-343.19</v>
       </c>
       <c r="K27" t="n">
-        <v>-75.48</v>
+        <v>187.23</v>
       </c>
       <c r="L27" t="n">
-        <v>217.46</v>
+        <v>390.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:12:21</t>
+          <t>05:14:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1216,31 +1216,31 @@
         <v>3.48</v>
       </c>
       <c r="F28" t="n">
-        <v>10.04</v>
+        <v>12.34</v>
       </c>
       <c r="G28" t="n">
-        <v>228.3</v>
+        <v>225.6</v>
       </c>
       <c r="H28" t="n">
-        <v>76.8</v>
+        <v>35.2</v>
       </c>
       <c r="I28" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-11.31</v>
+        <v>119.6</v>
       </c>
       <c r="K28" t="n">
-        <v>-289.7</v>
+        <v>182.33</v>
       </c>
       <c r="L28" t="n">
-        <v>289.92</v>
+        <v>218.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:22:47</t>
+          <t>05:24:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="F29" t="n">
-        <v>11.65</v>
+        <v>10.32</v>
       </c>
       <c r="G29" t="n">
-        <v>216</v>
+        <v>235.2</v>
       </c>
       <c r="H29" t="n">
-        <v>33.2</v>
+        <v>30.4</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-22.49</v>
+        <v>-35.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-37.69</v>
+        <v>-21.95</v>
       </c>
       <c r="L29" t="n">
-        <v>43.89</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:23:36</t>
+          <t>05:26:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="F30" t="n">
-        <v>14.14</v>
+        <v>11.44</v>
       </c>
       <c r="G30" t="n">
-        <v>231</v>
+        <v>227.2</v>
       </c>
       <c r="H30" t="n">
-        <v>63</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>2.76</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>57.2</v>
+        <v>-46.87</v>
       </c>
       <c r="L30" t="n">
-        <v>57.27</v>
+        <v>47.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:25:27</t>
+          <t>05:27:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="F31" t="n">
-        <v>13.74</v>
+        <v>14.14</v>
       </c>
       <c r="G31" t="n">
-        <v>228.1</v>
+        <v>240.7</v>
       </c>
       <c r="H31" t="n">
-        <v>39.4</v>
+        <v>46.2</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-67.69</v>
+        <v>22.5</v>
       </c>
       <c r="K31" t="n">
-        <v>34.87</v>
+        <v>51.41</v>
       </c>
       <c r="L31" t="n">
-        <v>76.15000000000001</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:29:41</t>
+          <t>05:32:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.21</v>
+        <v>3.09</v>
       </c>
       <c r="F32" t="n">
-        <v>9.18</v>
+        <v>9.52</v>
       </c>
       <c r="G32" t="n">
-        <v>233.9</v>
+        <v>227.9</v>
       </c>
       <c r="H32" t="n">
-        <v>46.9</v>
+        <v>39.7</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>111.48</v>
+        <v>-55.24</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.48</v>
+        <v>20.14</v>
       </c>
       <c r="L32" t="n">
-        <v>111.49</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:31:08</t>
+          <t>05:34:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="F33" t="n">
-        <v>14.14</v>
+        <v>13.65</v>
       </c>
       <c r="G33" t="n">
-        <v>227.5</v>
+        <v>224.2</v>
       </c>
       <c r="H33" t="n">
-        <v>76.7</v>
+        <v>89.3</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>71.3</v>
+        <v>-46.15</v>
       </c>
       <c r="K33" t="n">
-        <v>-90.95</v>
+        <v>-56.71</v>
       </c>
       <c r="L33" t="n">
-        <v>115.57</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:32:39</t>
+          <t>05:36:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
       <c r="F34" t="n">
-        <v>8.210000000000001</v>
+        <v>14.14</v>
       </c>
       <c r="G34" t="n">
-        <v>223.2</v>
+        <v>252.1</v>
       </c>
       <c r="H34" t="n">
-        <v>54.8</v>
+        <v>28.8</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-22.78</v>
+        <v>86.59</v>
       </c>
       <c r="K34" t="n">
-        <v>-62.42</v>
+        <v>7.67</v>
       </c>
       <c r="L34" t="n">
-        <v>66.45</v>
+        <v>86.93000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:36:53</t>
+          <t>05:41:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="F35" t="n">
-        <v>10.81</v>
+        <v>10.72</v>
       </c>
       <c r="G35" t="n">
-        <v>239.1</v>
+        <v>247.2</v>
       </c>
       <c r="H35" t="n">
-        <v>91.3</v>
+        <v>64.3</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-74.79000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="K35" t="n">
-        <v>-96.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="L35" t="n">
-        <v>122.01</v>
+        <v>89.73999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:38:15</t>
+          <t>05:43:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="F36" t="n">
-        <v>9.66</v>
+        <v>7.72</v>
       </c>
       <c r="G36" t="n">
-        <v>227.7</v>
+        <v>235.3</v>
       </c>
       <c r="H36" t="n">
-        <v>44.7</v>
+        <v>75.8</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>2.31</v>
+        <v>-24.54</v>
       </c>
       <c r="K36" t="n">
-        <v>-112.8</v>
+        <v>109.25</v>
       </c>
       <c r="L36" t="n">
-        <v>112.82</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:40:16</t>
+          <t>05:45:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.65</v>
+        <v>3.59</v>
       </c>
       <c r="F37" t="n">
-        <v>10.79</v>
+        <v>14.14</v>
       </c>
       <c r="G37" t="n">
-        <v>226.3</v>
+        <v>225.5</v>
       </c>
       <c r="H37" t="n">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-90.47</v>
+        <v>71.64</v>
       </c>
       <c r="K37" t="n">
-        <v>-14.3</v>
+        <v>-26.16</v>
       </c>
       <c r="L37" t="n">
-        <v>91.59</v>
+        <v>76.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:45:31</t>
+          <t>05:50:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="F38" t="n">
-        <v>9.41</v>
+        <v>11.4</v>
       </c>
       <c r="G38" t="n">
-        <v>224</v>
+        <v>224.7</v>
       </c>
       <c r="H38" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I38" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-58.04</v>
+        <v>-44.71</v>
       </c>
       <c r="K38" t="n">
-        <v>180.27</v>
+        <v>-138.21</v>
       </c>
       <c r="L38" t="n">
-        <v>189.39</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:47:48</t>
+          <t>05:51:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="F39" t="n">
-        <v>10.27</v>
+        <v>7.89</v>
       </c>
       <c r="G39" t="n">
-        <v>228.6</v>
+        <v>227.6</v>
       </c>
       <c r="H39" t="n">
-        <v>69.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>29.89</v>
+        <v>1.91</v>
       </c>
       <c r="K39" t="n">
-        <v>-144.17</v>
+        <v>-135.03</v>
       </c>
       <c r="L39" t="n">
-        <v>147.23</v>
+        <v>135.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:49:11</t>
+          <t>05:52:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.85</v>
+        <v>2.89</v>
       </c>
       <c r="F40" t="n">
-        <v>10.89</v>
+        <v>11.18</v>
       </c>
       <c r="G40" t="n">
-        <v>237</v>
+        <v>227.1</v>
       </c>
       <c r="H40" t="n">
-        <v>70.09999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-70.95</v>
+        <v>-94.93000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-244.05</v>
+        <v>95.72</v>
       </c>
       <c r="L40" t="n">
-        <v>254.15</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:54:56</t>
+          <t>05:56:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.57</v>
+        <v>3.06</v>
       </c>
       <c r="F41" t="n">
-        <v>14.14</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>233.1</v>
+        <v>225.5</v>
       </c>
       <c r="H41" t="n">
-        <v>55.7</v>
+        <v>26.7</v>
       </c>
       <c r="I41" t="n">
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-214.55</v>
+        <v>-68.73</v>
       </c>
       <c r="K41" t="n">
-        <v>157.79</v>
+        <v>-114.35</v>
       </c>
       <c r="L41" t="n">
-        <v>266.32</v>
+        <v>133.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:56:24</t>
+          <t>05:57:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="F42" t="n">
-        <v>9.9</v>
+        <v>12.54</v>
       </c>
       <c r="G42" t="n">
-        <v>225.3</v>
+        <v>224.8</v>
       </c>
       <c r="H42" t="n">
-        <v>50.2</v>
+        <v>37.6</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>-66.72</v>
+        <v>88.72</v>
       </c>
       <c r="K42" t="n">
-        <v>-164.58</v>
+        <v>-172.84</v>
       </c>
       <c r="L42" t="n">
-        <v>177.59</v>
+        <v>194.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:57:52</t>
+          <t>05:58:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="F43" t="n">
-        <v>10.5</v>
+        <v>9.02</v>
       </c>
       <c r="G43" t="n">
-        <v>239.3</v>
+        <v>224.9</v>
       </c>
       <c r="H43" t="n">
-        <v>57.7</v>
+        <v>91.3</v>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-163.12</v>
+        <v>137.75</v>
       </c>
       <c r="K43" t="n">
-        <v>91.7</v>
+        <v>-40.35</v>
       </c>
       <c r="L43" t="n">
-        <v>187.13</v>
+        <v>143.54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:38</t>
+          <t>06:07:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.19</v>
+        <v>4.2</v>
       </c>
       <c r="F44" t="n">
-        <v>8.140000000000001</v>
+        <v>14.14</v>
       </c>
       <c r="G44" t="n">
-        <v>230.4</v>
+        <v>230.2</v>
       </c>
       <c r="H44" t="n">
-        <v>82.5</v>
+        <v>38.3</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>34.23</v>
+        <v>16.36</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.77</v>
+        <v>-46.45</v>
       </c>
       <c r="L44" t="n">
-        <v>61.23</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:07:58</t>
+          <t>06:09:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="F45" t="n">
-        <v>13.65</v>
+        <v>6.87</v>
       </c>
       <c r="G45" t="n">
-        <v>237.9</v>
+        <v>249.5</v>
       </c>
       <c r="H45" t="n">
-        <v>38.5</v>
+        <v>8.4</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-58.49</v>
+        <v>22.61</v>
       </c>
       <c r="K45" t="n">
-        <v>-49.36</v>
+        <v>-43.27</v>
       </c>
       <c r="L45" t="n">
-        <v>76.53</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:08:37</t>
+          <t>06:11:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.57</v>
+        <v>4.07</v>
       </c>
       <c r="F46" t="n">
-        <v>11.02</v>
+        <v>14.14</v>
       </c>
       <c r="G46" t="n">
-        <v>223.5</v>
+        <v>235.1</v>
       </c>
       <c r="H46" t="n">
-        <v>67.59999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>37.56</v>
+        <v>-4.34</v>
       </c>
       <c r="K46" t="n">
-        <v>-74.81999999999999</v>
+        <v>-62.93</v>
       </c>
       <c r="L46" t="n">
-        <v>83.70999999999999</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:13:35</t>
+          <t>06:16:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.97</v>
+        <v>3.47</v>
       </c>
       <c r="F47" t="n">
-        <v>10.77</v>
+        <v>12.63</v>
       </c>
       <c r="G47" t="n">
-        <v>232.5</v>
+        <v>224.1</v>
       </c>
       <c r="H47" t="n">
-        <v>73.2</v>
+        <v>41.6</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>60.45</v>
+        <v>63.81</v>
       </c>
       <c r="K47" t="n">
-        <v>57.6</v>
+        <v>-42.28</v>
       </c>
       <c r="L47" t="n">
-        <v>83.5</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:15:08</t>
+          <t>06:18:02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="F48" t="n">
-        <v>7.86</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>231.6</v>
+        <v>240.1</v>
       </c>
       <c r="H48" t="n">
-        <v>24.3</v>
+        <v>53.1</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-37.16</v>
+        <v>64.16</v>
       </c>
       <c r="K48" t="n">
-        <v>-43.29</v>
+        <v>11.49</v>
       </c>
       <c r="L48" t="n">
-        <v>57.06</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:16:32</t>
+          <t>06:20:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.57</v>
+        <v>3.87</v>
       </c>
       <c r="F49" t="n">
-        <v>9.02</v>
+        <v>13.24</v>
       </c>
       <c r="G49" t="n">
-        <v>236.6</v>
+        <v>239.8</v>
       </c>
       <c r="H49" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>75.06</v>
+        <v>-21.4</v>
       </c>
       <c r="K49" t="n">
-        <v>45.08</v>
+        <v>-71.17</v>
       </c>
       <c r="L49" t="n">
-        <v>87.56</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:20:33</t>
+          <t>06:24:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.74</v>
+        <v>2.98</v>
       </c>
       <c r="F50" t="n">
-        <v>14.14</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>251.8</v>
+        <v>219.4</v>
       </c>
       <c r="H50" t="n">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>40.86</v>
+        <v>-100.85</v>
       </c>
       <c r="K50" t="n">
-        <v>109.53</v>
+        <v>-23.91</v>
       </c>
       <c r="L50" t="n">
-        <v>116.9</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:21:57</t>
+          <t>06:25:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="F51" t="n">
-        <v>13.57</v>
+        <v>11.21</v>
       </c>
       <c r="G51" t="n">
-        <v>228.3</v>
+        <v>241.8</v>
       </c>
       <c r="H51" t="n">
-        <v>56.3</v>
+        <v>75.5</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>39.75</v>
+        <v>82.23</v>
       </c>
       <c r="K51" t="n">
-        <v>-131.73</v>
+        <v>-45.47</v>
       </c>
       <c r="L51" t="n">
-        <v>137.59</v>
+        <v>93.95999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:22:53</t>
+          <t>06:26:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="F52" t="n">
-        <v>12.73</v>
+        <v>10.05</v>
       </c>
       <c r="G52" t="n">
-        <v>244</v>
+        <v>230.7</v>
       </c>
       <c r="H52" t="n">
-        <v>61.5</v>
+        <v>50.9</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-33.75</v>
+        <v>-42.02</v>
       </c>
       <c r="K52" t="n">
-        <v>148.69</v>
+        <v>62.25</v>
       </c>
       <c r="L52" t="n">
-        <v>152.47</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:28:10</t>
+          <t>06:30:48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="F53" t="n">
-        <v>13.64</v>
+        <v>12.82</v>
       </c>
       <c r="G53" t="n">
-        <v>234.9</v>
+        <v>217.8</v>
       </c>
       <c r="H53" t="n">
-        <v>62.1</v>
+        <v>52.3</v>
       </c>
       <c r="I53" t="n">
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-119.08</v>
+        <v>-127.04</v>
       </c>
       <c r="K53" t="n">
-        <v>-155.16</v>
+        <v>-26.8</v>
       </c>
       <c r="L53" t="n">
-        <v>195.59</v>
+        <v>129.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:08</t>
+          <t>06:32:48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="F54" t="n">
-        <v>11.04</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>223.9</v>
+        <v>225.8</v>
       </c>
       <c r="H54" t="n">
-        <v>79.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>87.88</v>
+        <v>116.14</v>
       </c>
       <c r="K54" t="n">
-        <v>125.28</v>
+        <v>78.3</v>
       </c>
       <c r="L54" t="n">
-        <v>153.03</v>
+        <v>140.07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:30:42</t>
+          <t>06:35:16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>12.54</v>
+        <v>11.1</v>
       </c>
       <c r="G55" t="n">
-        <v>231.3</v>
+        <v>247.6</v>
       </c>
       <c r="H55" t="n">
-        <v>53.8</v>
+        <v>55.7</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>144.84</v>
+        <v>-112.39</v>
       </c>
       <c r="K55" t="n">
-        <v>45.89</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>151.93</v>
+        <v>132.54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:34:38</t>
+          <t>06:39:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.9</v>
+        <v>2.64</v>
       </c>
       <c r="F56" t="n">
-        <v>14.14</v>
+        <v>12.69</v>
       </c>
       <c r="G56" t="n">
-        <v>222.9</v>
+        <v>239.7</v>
       </c>
       <c r="H56" t="n">
-        <v>44</v>
+        <v>20.3</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-384.48</v>
+        <v>-160.49</v>
       </c>
       <c r="K56" t="n">
-        <v>83.81</v>
+        <v>46.51</v>
       </c>
       <c r="L56" t="n">
-        <v>393.51</v>
+        <v>167.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:37:24</t>
+          <t>06:40:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.62</v>
+        <v>3.19</v>
       </c>
       <c r="F57" t="n">
-        <v>10.2</v>
+        <v>14.14</v>
       </c>
       <c r="G57" t="n">
-        <v>218</v>
+        <v>229.3</v>
       </c>
       <c r="H57" t="n">
-        <v>38.1</v>
+        <v>47.9</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-179.36</v>
+        <v>-113.54</v>
       </c>
       <c r="K57" t="n">
-        <v>-263.08</v>
+        <v>164.02</v>
       </c>
       <c r="L57" t="n">
-        <v>318.4</v>
+        <v>199.48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:32</t>
+          <t>06:42:31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.87</v>
+        <v>3.17</v>
       </c>
       <c r="F58" t="n">
-        <v>12.47</v>
+        <v>7.1</v>
       </c>
       <c r="G58" t="n">
-        <v>236.9</v>
+        <v>226.4</v>
       </c>
       <c r="H58" t="n">
-        <v>55.8</v>
+        <v>68.2</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-279.36</v>
+        <v>225.67</v>
       </c>
       <c r="K58" t="n">
-        <v>4.04</v>
+        <v>-87.19</v>
       </c>
       <c r="L58" t="n">
-        <v>279.39</v>
+        <v>241.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:52:12</t>
+          <t>06:51:16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="F59" t="n">
-        <v>14.14</v>
+        <v>12.2</v>
       </c>
       <c r="G59" t="n">
-        <v>227.6</v>
+        <v>225</v>
       </c>
       <c r="H59" t="n">
-        <v>24.5</v>
+        <v>45.5</v>
       </c>
       <c r="I59" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>53.54</v>
+        <v>-50.97</v>
       </c>
       <c r="K59" t="n">
-        <v>39.99</v>
+        <v>17.72</v>
       </c>
       <c r="L59" t="n">
-        <v>66.81999999999999</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:54:39</t>
+          <t>06:52:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="F60" t="n">
-        <v>9.52</v>
+        <v>12.19</v>
       </c>
       <c r="G60" t="n">
-        <v>230</v>
+        <v>247.8</v>
       </c>
       <c r="H60" t="n">
-        <v>44</v>
+        <v>45.3</v>
       </c>
       <c r="I60" t="n">
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-39.52</v>
+        <v>2.43</v>
       </c>
       <c r="K60" t="n">
-        <v>63.86</v>
+        <v>53.81</v>
       </c>
       <c r="L60" t="n">
-        <v>75.09999999999999</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:55:47</t>
+          <t>06:55:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="F61" t="n">
-        <v>11.21</v>
+        <v>14.14</v>
       </c>
       <c r="G61" t="n">
-        <v>230.9</v>
+        <v>241.1</v>
       </c>
       <c r="H61" t="n">
-        <v>41.9</v>
+        <v>75.2</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.28</v>
+        <v>-24.62</v>
       </c>
       <c r="K61" t="n">
-        <v>-45.04</v>
+        <v>-42.36</v>
       </c>
       <c r="L61" t="n">
-        <v>46.44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:00:52</t>
+          <t>07:00:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.83</v>
+        <v>3.24</v>
       </c>
       <c r="F62" t="n">
         <v>14.14</v>
       </c>
       <c r="G62" t="n">
-        <v>226.2</v>
+        <v>234.3</v>
       </c>
       <c r="H62" t="n">
-        <v>60.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>76.04000000000001</v>
+        <v>57.56</v>
       </c>
       <c r="K62" t="n">
-        <v>72.52</v>
+        <v>-58.44</v>
       </c>
       <c r="L62" t="n">
-        <v>105.08</v>
+        <v>82.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:01:36</t>
+          <t>07:00:58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="F63" t="n">
-        <v>14.14</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>242.1</v>
+        <v>236.3</v>
       </c>
       <c r="H63" t="n">
-        <v>51.6</v>
+        <v>46.2</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-59.81</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>47.65</v>
+        <v>12.39</v>
       </c>
       <c r="L63" t="n">
-        <v>76.47</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:02:47</t>
+          <t>07:02:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="F64" t="n">
-        <v>13.35</v>
+        <v>12.6</v>
       </c>
       <c r="G64" t="n">
-        <v>242.9</v>
+        <v>229</v>
       </c>
       <c r="H64" t="n">
-        <v>74.09999999999999</v>
+        <v>39.6</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-94.08</v>
+        <v>44.68</v>
       </c>
       <c r="K64" t="n">
-        <v>18.41</v>
+        <v>-62.71</v>
       </c>
       <c r="L64" t="n">
-        <v>95.87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:06:15</t>
+          <t>07:06:41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.6</v>
+        <v>4.11</v>
       </c>
       <c r="F65" t="n">
-        <v>10.84</v>
+        <v>14.14</v>
       </c>
       <c r="G65" t="n">
-        <v>230.4</v>
+        <v>224.8</v>
       </c>
       <c r="H65" t="n">
-        <v>65.5</v>
+        <v>86.2</v>
       </c>
       <c r="I65" t="n">
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-104</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>105.41</v>
+        <v>102.31</v>
       </c>
       <c r="L65" t="n">
-        <v>148.08</v>
+        <v>138.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:07:49</t>
+          <t>07:08:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.44</v>
+        <v>3.91</v>
       </c>
       <c r="F66" t="n">
-        <v>11.73</v>
+        <v>12.45</v>
       </c>
       <c r="G66" t="n">
-        <v>222.4</v>
+        <v>227</v>
       </c>
       <c r="H66" t="n">
-        <v>31.1</v>
+        <v>50.7</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>73.3</v>
+        <v>-59.16</v>
       </c>
       <c r="K66" t="n">
-        <v>-104.55</v>
+        <v>-90.48999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>127.68</v>
+        <v>108.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:08:40</t>
+          <t>07:09:13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.49</v>
+        <v>3.08</v>
       </c>
       <c r="F67" t="n">
-        <v>14.14</v>
+        <v>9.66</v>
       </c>
       <c r="G67" t="n">
-        <v>241.2</v>
+        <v>229.3</v>
       </c>
       <c r="H67" t="n">
-        <v>59.4</v>
+        <v>58.1</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-18.81</v>
+        <v>-53.16</v>
       </c>
       <c r="K67" t="n">
-        <v>130.05</v>
+        <v>-70.51000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>131.4</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:14:46</t>
+          <t>07:14:11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="F68" t="n">
-        <v>12.1</v>
+        <v>11.49</v>
       </c>
       <c r="G68" t="n">
-        <v>227.7</v>
+        <v>232.9</v>
       </c>
       <c r="H68" t="n">
-        <v>30.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-44.24</v>
+        <v>123.82</v>
       </c>
       <c r="K68" t="n">
-        <v>190.94</v>
+        <v>10.25</v>
       </c>
       <c r="L68" t="n">
-        <v>195.99</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:16:47</t>
+          <t>07:16:28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.42</v>
+        <v>4.11</v>
       </c>
       <c r="F69" t="n">
-        <v>13.03</v>
+        <v>14.14</v>
       </c>
       <c r="G69" t="n">
-        <v>249.2</v>
+        <v>231.1</v>
       </c>
       <c r="H69" t="n">
-        <v>72.09999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="I69" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>8.84</v>
+        <v>-143.4</v>
       </c>
       <c r="K69" t="n">
-        <v>-200.2</v>
+        <v>197.02</v>
       </c>
       <c r="L69" t="n">
-        <v>200.39</v>
+        <v>243.68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:18:33</t>
+          <t>07:18:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.63</v>
+        <v>4.13</v>
       </c>
       <c r="F70" t="n">
-        <v>9.4</v>
+        <v>14.14</v>
       </c>
       <c r="G70" t="n">
-        <v>226.2</v>
+        <v>240.3</v>
       </c>
       <c r="H70" t="n">
-        <v>47.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-95.91</v>
+        <v>67.52</v>
       </c>
       <c r="K70" t="n">
-        <v>-345.78</v>
+        <v>-222.66</v>
       </c>
       <c r="L70" t="n">
-        <v>358.83</v>
+        <v>232.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:22:14</t>
+          <t>07:22:57</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.87</v>
+        <v>3.71</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>11.56</v>
       </c>
       <c r="G71" t="n">
-        <v>218</v>
+        <v>238.5</v>
       </c>
       <c r="H71" t="n">
-        <v>60.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>149.36</v>
+        <v>-67.38</v>
       </c>
       <c r="K71" t="n">
-        <v>64.68000000000001</v>
+        <v>197.74</v>
       </c>
       <c r="L71" t="n">
-        <v>162.77</v>
+        <v>208.91</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:24:19</t>
+          <t>07:24:16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.79</v>
+        <v>2.93</v>
       </c>
       <c r="F72" t="n">
-        <v>14.14</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>226.9</v>
+        <v>230.8</v>
       </c>
       <c r="H72" t="n">
-        <v>34</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-262.31</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-227.4</v>
+        <v>-145.37</v>
       </c>
       <c r="L72" t="n">
-        <v>347.16</v>
+        <v>161.93</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:26:00</t>
+          <t>07:25:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.7</v>
+        <v>3.99</v>
       </c>
       <c r="F73" t="n">
-        <v>12.61</v>
+        <v>14.14</v>
       </c>
       <c r="G73" t="n">
-        <v>242.1</v>
+        <v>217.8</v>
       </c>
       <c r="H73" t="n">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-491.36</v>
+        <v>-244.05</v>
       </c>
       <c r="K73" t="n">
-        <v>-224.15</v>
+        <v>-18.18</v>
       </c>
       <c r="L73" t="n">
-        <v>540.0700000000001</v>
+        <v>244.73</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:34:06</t>
+          <t>07:34:17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.18</v>
+        <v>3.84</v>
       </c>
       <c r="F74" t="n">
-        <v>9.82</v>
+        <v>14.14</v>
       </c>
       <c r="G74" t="n">
-        <v>233.6</v>
+        <v>236.8</v>
       </c>
       <c r="H74" t="n">
-        <v>67.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>51.06</v>
+        <v>-12.81</v>
       </c>
       <c r="K74" t="n">
-        <v>22.59</v>
+        <v>52.61</v>
       </c>
       <c r="L74" t="n">
-        <v>55.84</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:35:15</t>
+          <t>07:35:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="F75" t="n">
         <v>14.14</v>
       </c>
       <c r="G75" t="n">
-        <v>224.5</v>
+        <v>221.1</v>
       </c>
       <c r="H75" t="n">
-        <v>91.59999999999999</v>
+        <v>27.9</v>
       </c>
       <c r="I75" t="n">
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-56.7</v>
+        <v>-70.86</v>
       </c>
       <c r="K75" t="n">
-        <v>23.67</v>
+        <v>-49.9</v>
       </c>
       <c r="L75" t="n">
-        <v>61.44</v>
+        <v>86.67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:36:45</t>
+          <t>07:36:54</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.07</v>
+        <v>3.83</v>
       </c>
       <c r="F76" t="n">
         <v>14.14</v>
       </c>
       <c r="G76" t="n">
-        <v>244.7</v>
+        <v>222.8</v>
       </c>
       <c r="H76" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>47.26</v>
+        <v>-6.85</v>
       </c>
       <c r="K76" t="n">
-        <v>-48.07</v>
+        <v>-59.05</v>
       </c>
       <c r="L76" t="n">
-        <v>67.42</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:41:18</t>
+          <t>07:43:16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.24</v>
+        <v>3.69</v>
       </c>
       <c r="F77" t="n">
-        <v>14.14</v>
+        <v>11.52</v>
       </c>
       <c r="G77" t="n">
-        <v>239</v>
+        <v>237.7</v>
       </c>
       <c r="H77" t="n">
-        <v>60.5</v>
+        <v>57.3</v>
       </c>
       <c r="I77" t="n">
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>85.15000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="K77" t="n">
-        <v>-38.03</v>
+        <v>-64.08</v>
       </c>
       <c r="L77" t="n">
-        <v>93.26000000000001</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:42:52</t>
+          <t>07:45:38</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.08</v>
+        <v>4.07</v>
       </c>
       <c r="F78" t="n">
-        <v>12.23</v>
+        <v>14.14</v>
       </c>
       <c r="G78" t="n">
-        <v>229.8</v>
+        <v>236.6</v>
       </c>
       <c r="H78" t="n">
-        <v>83.7</v>
+        <v>46.4</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-61.17</v>
+        <v>-81.63</v>
       </c>
       <c r="K78" t="n">
-        <v>5.69</v>
+        <v>-9.57</v>
       </c>
       <c r="L78" t="n">
-        <v>61.43</v>
+        <v>82.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:43:58</t>
+          <t>07:47:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="F79" t="n">
         <v>14.14</v>
       </c>
       <c r="G79" t="n">
-        <v>237.1</v>
+        <v>243.9</v>
       </c>
       <c r="H79" t="n">
-        <v>52.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>55.56</v>
+        <v>38.1</v>
       </c>
       <c r="K79" t="n">
-        <v>-66.61</v>
+        <v>82.39</v>
       </c>
       <c r="L79" t="n">
-        <v>86.73999999999999</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:47:27</t>
+          <t>07:52:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.32</v>
+        <v>2.75</v>
       </c>
       <c r="F80" t="n">
-        <v>14.14</v>
+        <v>13.35</v>
       </c>
       <c r="G80" t="n">
-        <v>226.6</v>
+        <v>237.2</v>
       </c>
       <c r="H80" t="n">
-        <v>55.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>75.67</v>
+        <v>96.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-120.68</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>142.44</v>
+        <v>117.49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:48:32</t>
+          <t>07:54:28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="F81" t="n">
-        <v>12.77</v>
+        <v>11.75</v>
       </c>
       <c r="G81" t="n">
-        <v>225.6</v>
+        <v>233.3</v>
       </c>
       <c r="H81" t="n">
-        <v>43.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>68.56999999999999</v>
+        <v>-43.56</v>
       </c>
       <c r="K81" t="n">
-        <v>-106.79</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>126.9</v>
+        <v>100.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:49:56</t>
+          <t>07:56:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="F82" t="n">
-        <v>13.72</v>
+        <v>14.14</v>
       </c>
       <c r="G82" t="n">
-        <v>238.5</v>
+        <v>224.7</v>
       </c>
       <c r="H82" t="n">
-        <v>68.2</v>
+        <v>73.7</v>
       </c>
       <c r="I82" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J82" t="n">
-        <v>74.56999999999999</v>
+        <v>119.03</v>
       </c>
       <c r="K82" t="n">
-        <v>107.8</v>
+        <v>-49.88</v>
       </c>
       <c r="L82" t="n">
-        <v>131.08</v>
+        <v>129.06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:54:28</t>
+          <t>08:01:02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="F83" t="n">
-        <v>11.85</v>
+        <v>11.75</v>
       </c>
       <c r="G83" t="n">
-        <v>235.8</v>
+        <v>240.4</v>
       </c>
       <c r="H83" t="n">
-        <v>59.3</v>
+        <v>52.3</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-114.5</v>
+        <v>101.73</v>
       </c>
       <c r="K83" t="n">
-        <v>-53.36</v>
+        <v>-181.95</v>
       </c>
       <c r="L83" t="n">
-        <v>126.32</v>
+        <v>208.45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:56:10</t>
+          <t>08:03:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="F84" t="n">
         <v>14.14</v>
       </c>
       <c r="G84" t="n">
-        <v>228.7</v>
+        <v>230.2</v>
       </c>
       <c r="H84" t="n">
-        <v>66.40000000000001</v>
+        <v>42</v>
       </c>
       <c r="I84" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-137.35</v>
+        <v>-190.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-143.36</v>
+        <v>-12.12</v>
       </c>
       <c r="L84" t="n">
-        <v>198.54</v>
+        <v>190.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:57:24</t>
+          <t>08:05:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="F85" t="n">
-        <v>11.01</v>
+        <v>10.83</v>
       </c>
       <c r="G85" t="n">
-        <v>245.7</v>
+        <v>226.3</v>
       </c>
       <c r="H85" t="n">
-        <v>60.6</v>
+        <v>61.7</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-145.16</v>
+        <v>103.08</v>
       </c>
       <c r="K85" t="n">
-        <v>87.75</v>
+        <v>41.99</v>
       </c>
       <c r="L85" t="n">
-        <v>169.62</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:02:01</t>
+          <t>08:08:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.97</v>
+        <v>3.34</v>
       </c>
       <c r="F86" t="n">
-        <v>12.26</v>
+        <v>14.14</v>
       </c>
       <c r="G86" t="n">
-        <v>214.3</v>
+        <v>248.9</v>
       </c>
       <c r="H86" t="n">
-        <v>30.5</v>
+        <v>31.6</v>
       </c>
       <c r="I86" t="n">
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>67.84999999999999</v>
+        <v>102.5</v>
       </c>
       <c r="K86" t="n">
-        <v>-314.1</v>
+        <v>-229.44</v>
       </c>
       <c r="L86" t="n">
-        <v>321.34</v>
+        <v>251.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:04:11</t>
+          <t>08:09:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.14</v>
+        <v>3.47</v>
       </c>
       <c r="F87" t="n">
         <v>14.14</v>
       </c>
       <c r="G87" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H87" t="n">
-        <v>72.5</v>
+        <v>44.1</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>350.5</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-91.7</v>
+        <v>252.62</v>
       </c>
       <c r="L87" t="n">
-        <v>362.29</v>
+        <v>252.76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:05:25</t>
+          <t>08:10:40</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="F88" t="n">
-        <v>13.67</v>
+        <v>12.07</v>
       </c>
       <c r="G88" t="n">
-        <v>230.8</v>
+        <v>227.1</v>
       </c>
       <c r="H88" t="n">
-        <v>73.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-203.74</v>
+        <v>-222.45</v>
       </c>
       <c r="K88" t="n">
-        <v>-33.12</v>
+        <v>105.66</v>
       </c>
       <c r="L88" t="n">
-        <v>206.41</v>
+        <v>246.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>45.04</v>
+        <v>50.02</v>
       </c>
       <c r="K14" t="n">
-        <v>56.82</v>
+        <v>63.1</v>
       </c>
       <c r="L14" t="n">
-        <v>72.51000000000001</v>
+        <v>80.52</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.38</v>
+        <v>-6.6</v>
       </c>
       <c r="K15" t="n">
-        <v>61.94</v>
+        <v>64.02</v>
       </c>
       <c r="L15" t="n">
-        <v>62.27</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>36.03</v>
+        <v>40.03</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.9</v>
+        <v>-57.66</v>
       </c>
       <c r="L16" t="n">
-        <v>63.18</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.12</v>
+        <v>-13.32</v>
       </c>
       <c r="K17" t="n">
-        <v>-84.06</v>
+        <v>-92.40000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>84.93000000000001</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.1</v>
+        <v>-9.6</v>
       </c>
       <c r="K18" t="n">
-        <v>-91.87</v>
+        <v>-96.94</v>
       </c>
       <c r="L18" t="n">
-        <v>92.31999999999999</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-39.07</v>
+        <v>-45.15</v>
       </c>
       <c r="K19" t="n">
-        <v>65.01000000000001</v>
+        <v>75.13</v>
       </c>
       <c r="L19" t="n">
-        <v>75.84999999999999</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-65.62</v>
+        <v>-77.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>65.19</v>
+        <v>77.45</v>
       </c>
       <c r="L20" t="n">
-        <v>92.5</v>
+        <v>109.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>8.220000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="K21" t="n">
-        <v>-20.26</v>
+        <v>-25.53</v>
       </c>
       <c r="L21" t="n">
-        <v>21.87</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-102.86</v>
+        <v>-122.92</v>
       </c>
       <c r="K22" t="n">
-        <v>-32.36</v>
+        <v>-38.67</v>
       </c>
       <c r="L22" t="n">
-        <v>107.83</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-114.71</v>
+        <v>-132.26</v>
       </c>
       <c r="K23" t="n">
-        <v>163.69</v>
+        <v>188.74</v>
       </c>
       <c r="L23" t="n">
-        <v>199.88</v>
+        <v>230.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>29.41</v>
+        <v>37.44</v>
       </c>
       <c r="K24" t="n">
-        <v>112.96</v>
+        <v>143.8</v>
       </c>
       <c r="L24" t="n">
-        <v>116.73</v>
+        <v>148.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>28.93</v>
+        <v>35.29</v>
       </c>
       <c r="K25" t="n">
-        <v>140.63</v>
+        <v>171.55</v>
       </c>
       <c r="L25" t="n">
-        <v>143.58</v>
+        <v>175.14</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>52.69</v>
+        <v>69.42</v>
       </c>
       <c r="K26" t="n">
-        <v>145.88</v>
+        <v>192.21</v>
       </c>
       <c r="L26" t="n">
-        <v>155.1</v>
+        <v>204.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>111.42</v>
+        <v>154.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-82.90000000000001</v>
+        <v>-115.19</v>
       </c>
       <c r="L27" t="n">
-        <v>138.88</v>
+        <v>192.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-189.59</v>
+        <v>-230.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-32.97</v>
+        <v>-40.09</v>
       </c>
       <c r="L28" t="n">
-        <v>192.44</v>
+        <v>233.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-50.7</v>
+        <v>-62.14</v>
       </c>
       <c r="K29" t="n">
-        <v>5.72</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>51.02</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.56</v>
+        <v>-20.77</v>
       </c>
       <c r="K30" t="n">
-        <v>56.19</v>
+        <v>62.88</v>
       </c>
       <c r="L30" t="n">
-        <v>59.17</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>71.87</v>
+        <v>77.28</v>
       </c>
       <c r="K31" t="n">
-        <v>-19.99</v>
+        <v>-21.49</v>
       </c>
       <c r="L31" t="n">
-        <v>74.59999999999999</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-28.58</v>
+        <v>-30.99</v>
       </c>
       <c r="K32" t="n">
-        <v>-79.11</v>
+        <v>-85.78</v>
       </c>
       <c r="L32" t="n">
-        <v>84.12</v>
+        <v>91.20999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.02</v>
+        <v>-85.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-37.43</v>
+        <v>-42.06</v>
       </c>
       <c r="L33" t="n">
-        <v>84.73999999999999</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-27.27</v>
+        <v>-30.08</v>
       </c>
       <c r="K34" t="n">
-        <v>-87.31999999999999</v>
+        <v>-96.33</v>
       </c>
       <c r="L34" t="n">
-        <v>91.48</v>
+        <v>100.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-129.21</v>
+        <v>-146.75</v>
       </c>
       <c r="K35" t="n">
-        <v>80.97</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>152.49</v>
+        <v>173.19</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.4</v>
+        <v>-2.83</v>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>84.23</v>
+        <v>103.71</v>
       </c>
       <c r="K37" t="n">
-        <v>38.55</v>
+        <v>47.47</v>
       </c>
       <c r="L37" t="n">
-        <v>92.63</v>
+        <v>114.06</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-117.87</v>
+        <v>-150.99</v>
       </c>
       <c r="K38" t="n">
-        <v>13.87</v>
+        <v>17.77</v>
       </c>
       <c r="L38" t="n">
-        <v>118.69</v>
+        <v>152.03</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-131.48</v>
+        <v>-149.52</v>
       </c>
       <c r="K39" t="n">
-        <v>144.05</v>
+        <v>163.81</v>
       </c>
       <c r="L39" t="n">
-        <v>195.03</v>
+        <v>221.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>63.7</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-125.37</v>
+        <v>-150.58</v>
       </c>
       <c r="L40" t="n">
-        <v>140.62</v>
+        <v>168.91</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.7</v>
+        <v>-13.92</v>
       </c>
       <c r="K41" t="n">
-        <v>-170.36</v>
+        <v>-221.6</v>
       </c>
       <c r="L41" t="n">
-        <v>170.7</v>
+        <v>222.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-235.99</v>
+        <v>-327.74</v>
       </c>
       <c r="K42" t="n">
-        <v>-95.27</v>
+        <v>-132.31</v>
       </c>
       <c r="L42" t="n">
-        <v>254.49</v>
+        <v>353.44</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>257.38</v>
+        <v>320.36</v>
       </c>
       <c r="K43" t="n">
-        <v>39.47</v>
+        <v>49.13</v>
       </c>
       <c r="L43" t="n">
-        <v>260.39</v>
+        <v>324.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>53.18</v>
+        <v>56.03</v>
       </c>
       <c r="K44" t="n">
-        <v>41.26</v>
+        <v>43.47</v>
       </c>
       <c r="L44" t="n">
-        <v>67.31</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-59.32</v>
+        <v>-62.74</v>
       </c>
       <c r="K45" t="n">
-        <v>-39.66</v>
+        <v>-41.95</v>
       </c>
       <c r="L45" t="n">
-        <v>71.34999999999999</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-55.19</v>
+        <v>-61.3</v>
       </c>
       <c r="K46" t="n">
-        <v>-40.18</v>
+        <v>-44.63</v>
       </c>
       <c r="L46" t="n">
-        <v>68.27</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>46.38</v>
+        <v>54.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.57</v>
+        <v>-27.55</v>
       </c>
       <c r="L47" t="n">
-        <v>52.03</v>
+        <v>60.82</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>9.199999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.2</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>71.79000000000001</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-27.93</v>
+        <v>-31.38</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.92</v>
+        <v>-80.81999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>77.15000000000001</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.48</v>
+        <v>-14.51</v>
       </c>
       <c r="K50" t="n">
-        <v>-105.67</v>
+        <v>-122.83</v>
       </c>
       <c r="L50" t="n">
-        <v>106.4</v>
+        <v>123.68</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>78.19</v>
+        <v>98.25</v>
       </c>
       <c r="K51" t="n">
-        <v>-50.76</v>
+        <v>-63.78</v>
       </c>
       <c r="L51" t="n">
-        <v>93.22</v>
+        <v>117.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-102.01</v>
+        <v>-125.17</v>
       </c>
       <c r="K52" t="n">
-        <v>22.18</v>
+        <v>27.21</v>
       </c>
       <c r="L52" t="n">
-        <v>104.39</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-21.75</v>
+        <v>-28.54</v>
       </c>
       <c r="K53" t="n">
-        <v>33.25</v>
+        <v>43.63</v>
       </c>
       <c r="L53" t="n">
-        <v>39.73</v>
+        <v>52.13</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-22.37</v>
+        <v>-27.08</v>
       </c>
       <c r="K54" t="n">
-        <v>-168.65</v>
+        <v>-204.12</v>
       </c>
       <c r="L54" t="n">
-        <v>170.13</v>
+        <v>205.91</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>101</v>
+        <v>129.38</v>
       </c>
       <c r="K55" t="n">
-        <v>40.26</v>
+        <v>51.58</v>
       </c>
       <c r="L55" t="n">
-        <v>108.73</v>
+        <v>139.28</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-90.11</v>
+        <v>-110.06</v>
       </c>
       <c r="K56" t="n">
-        <v>198.59</v>
+        <v>242.55</v>
       </c>
       <c r="L56" t="n">
-        <v>218.07</v>
+        <v>266.35</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-71.55</v>
+        <v>-104.04</v>
       </c>
       <c r="K57" t="n">
-        <v>-232.1</v>
+        <v>-337.48</v>
       </c>
       <c r="L57" t="n">
-        <v>242.88</v>
+        <v>353.15</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-133.73</v>
+        <v>-165.08</v>
       </c>
       <c r="K58" t="n">
-        <v>-187.68</v>
+        <v>-231.67</v>
       </c>
       <c r="L58" t="n">
-        <v>230.45</v>
+        <v>284.47</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.93</v>
+        <v>-23.04</v>
       </c>
       <c r="K59" t="n">
-        <v>-75.56999999999999</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>78.69</v>
+        <v>82.68000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-66.63</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-19.56</v>
+        <v>-21.46</v>
       </c>
       <c r="L60" t="n">
-        <v>69.44</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>13.06</v>
+        <v>14.62</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.79000000000001</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>66.09</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-80.8</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>39.76</v>
+        <v>43.18</v>
       </c>
       <c r="L62" t="n">
-        <v>90.05</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>17.51</v>
+        <v>22.11</v>
       </c>
       <c r="K63" t="n">
-        <v>-53.78</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>56.56</v>
+        <v>71.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>66.59999999999999</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>40.73</v>
+        <v>46.57</v>
       </c>
       <c r="L64" t="n">
-        <v>78.06</v>
+        <v>89.26000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-87.34999999999999</v>
+        <v>-100.6</v>
       </c>
       <c r="K65" t="n">
-        <v>66.8</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>109.97</v>
+        <v>126.65</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-42.49</v>
+        <v>-55.11</v>
       </c>
       <c r="K66" t="n">
-        <v>-54.23</v>
+        <v>-70.34</v>
       </c>
       <c r="L66" t="n">
-        <v>68.90000000000001</v>
+        <v>89.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.57</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.52</v>
+        <v>-1.86</v>
       </c>
       <c r="L67" t="n">
-        <v>7.72</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>137.85</v>
+        <v>159.34</v>
       </c>
       <c r="K68" t="n">
-        <v>22.83</v>
+        <v>26.39</v>
       </c>
       <c r="L68" t="n">
-        <v>139.73</v>
+        <v>161.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-120.01</v>
+        <v>-151.38</v>
       </c>
       <c r="K69" t="n">
-        <v>54.57</v>
+        <v>68.84</v>
       </c>
       <c r="L69" t="n">
-        <v>131.84</v>
+        <v>166.3</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.11</v>
+        <v>-26.38</v>
       </c>
       <c r="K70" t="n">
-        <v>115.39</v>
+        <v>151.4</v>
       </c>
       <c r="L70" t="n">
-        <v>117.13</v>
+        <v>153.68</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-177.51</v>
+        <v>-226.05</v>
       </c>
       <c r="K71" t="n">
-        <v>177.17</v>
+        <v>225.62</v>
       </c>
       <c r="L71" t="n">
-        <v>250.8</v>
+        <v>319.37</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>252.15</v>
+        <v>299.54</v>
       </c>
       <c r="K72" t="n">
-        <v>97.65000000000001</v>
+        <v>116.01</v>
       </c>
       <c r="L72" t="n">
-        <v>270.39</v>
+        <v>321.22</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-161.87</v>
+        <v>-204.98</v>
       </c>
       <c r="K73" t="n">
-        <v>-102.71</v>
+        <v>-130.06</v>
       </c>
       <c r="L73" t="n">
-        <v>191.7</v>
+        <v>242.77</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>37.74</v>
+        <v>40.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-69.83</v>
+        <v>-75.42</v>
       </c>
       <c r="L74" t="n">
-        <v>79.38</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-23.64</v>
+        <v>-27.46</v>
       </c>
       <c r="K75" t="n">
-        <v>-50.2</v>
+        <v>-58.33</v>
       </c>
       <c r="L75" t="n">
-        <v>55.49</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-53.46</v>
+        <v>-62.93</v>
       </c>
       <c r="K76" t="n">
-        <v>9.73</v>
+        <v>11.45</v>
       </c>
       <c r="L76" t="n">
-        <v>54.34</v>
+        <v>63.96</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>56.31</v>
+        <v>70.12</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.26</v>
+        <v>-7.8</v>
       </c>
       <c r="L77" t="n">
-        <v>56.66</v>
+        <v>70.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-116.55</v>
+        <v>-118.38</v>
       </c>
       <c r="K78" t="n">
-        <v>75.78</v>
+        <v>76.97</v>
       </c>
       <c r="L78" t="n">
-        <v>139.02</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-95.14</v>
+        <v>-100.53</v>
       </c>
       <c r="K79" t="n">
-        <v>58.32</v>
+        <v>61.61</v>
       </c>
       <c r="L79" t="n">
-        <v>111.59</v>
+        <v>117.91</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>117.63</v>
+        <v>132.99</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.46</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>132.26</v>
+        <v>149.52</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-87.33</v>
+        <v>-104.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.43</v>
+        <v>-49.44</v>
       </c>
       <c r="L81" t="n">
-        <v>96.66</v>
+        <v>115.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-7.64</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-101.25</v>
+        <v>-123.1</v>
       </c>
       <c r="L82" t="n">
-        <v>101.54</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-18.02</v>
+        <v>-23.3</v>
       </c>
       <c r="K83" t="n">
-        <v>9.869999999999999</v>
+        <v>12.75</v>
       </c>
       <c r="L83" t="n">
-        <v>20.54</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-126.51</v>
+        <v>-152.16</v>
       </c>
       <c r="K84" t="n">
-        <v>-119.26</v>
+        <v>-143.44</v>
       </c>
       <c r="L84" t="n">
-        <v>173.86</v>
+        <v>209.12</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>-178.61</v>
+        <v>-195.71</v>
       </c>
       <c r="K85" t="n">
-        <v>134.11</v>
+        <v>146.94</v>
       </c>
       <c r="L85" t="n">
-        <v>223.35</v>
+        <v>244.73</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-214.2</v>
+        <v>-303.12</v>
       </c>
       <c r="K86" t="n">
-        <v>-183.12</v>
+        <v>-259.14</v>
       </c>
       <c r="L86" t="n">
-        <v>281.81</v>
+        <v>398.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-129.81</v>
+        <v>-162</v>
       </c>
       <c r="K87" t="n">
-        <v>216.94</v>
+        <v>270.74</v>
       </c>
       <c r="L87" t="n">
-        <v>252.81</v>
+        <v>315.51</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>161.34</v>
+        <v>209.91</v>
       </c>
       <c r="K88" t="n">
-        <v>-69.52</v>
+        <v>-90.44</v>
       </c>
       <c r="L88" t="n">
-        <v>175.68</v>
+        <v>228.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-06.xlsx
+++ b/output/2025-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>50.02</v>
+        <v>55.37</v>
       </c>
       <c r="K14" t="n">
-        <v>63.1</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>80.52</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="15">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-13.32</v>
+        <v>-13.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-92.40000000000001</v>
+        <v>-94.02</v>
       </c>
       <c r="L17" t="n">
-        <v>93.36</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.6</v>
+        <v>-9.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-96.94</v>
+        <v>-97.63</v>
       </c>
       <c r="L18" t="n">
-        <v>97.41</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>-45.15</v>
+        <v>-47.43</v>
       </c>
       <c r="K19" t="n">
-        <v>75.13</v>
+        <v>78.92</v>
       </c>
       <c r="L19" t="n">
-        <v>87.65000000000001</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-62.14</v>
+        <v>-63.66</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="L29" t="n">
-        <v>62.53</v>
+        <v>64.06999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-20.77</v>
+        <v>-20.94</v>
       </c>
       <c r="K30" t="n">
-        <v>62.88</v>
+        <v>63.41</v>
       </c>
       <c r="L30" t="n">
-        <v>66.22</v>
+        <v>66.78</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>77.28</v>
+        <v>79.72</v>
       </c>
       <c r="K31" t="n">
-        <v>-21.49</v>
+        <v>-22.17</v>
       </c>
       <c r="L31" t="n">
-        <v>80.20999999999999</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="32">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-85.44</v>
+        <v>-91.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-42.06</v>
+        <v>-45.15</v>
       </c>
       <c r="L33" t="n">
-        <v>95.23</v>
+        <v>102.21</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-30.08</v>
+        <v>-31.25</v>
       </c>
       <c r="K34" t="n">
-        <v>-96.33</v>
+        <v>-100.07</v>
       </c>
       <c r="L34" t="n">
-        <v>100.92</v>
+        <v>104.84</v>
       </c>
     </row>
     <row r="35">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-61.3</v>
+        <v>-62.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.63</v>
+        <v>-45.8</v>
       </c>
       <c r="L46" t="n">
-        <v>75.81999999999999</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2110,13 +2110,13 @@
         <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-31.38</v>
+        <v>-36</v>
       </c>
       <c r="K49" t="n">
-        <v>-80.81999999999999</v>
+        <v>-92.7</v>
       </c>
       <c r="L49" t="n">
-        <v>86.7</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-23.04</v>
+        <v>-23.27</v>
       </c>
       <c r="K59" t="n">
-        <v>-79.40000000000001</v>
+        <v>-80.19</v>
       </c>
       <c r="L59" t="n">
-        <v>82.68000000000001</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-73.09999999999999</v>
+        <v>-79.81</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.46</v>
+        <v>-23.43</v>
       </c>
       <c r="L60" t="n">
-        <v>76.19</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>14.62</v>
+        <v>15.59</v>
       </c>
       <c r="K61" t="n">
-        <v>-72.51000000000001</v>
+        <v>-77.33</v>
       </c>
       <c r="L61" t="n">
-        <v>73.95999999999999</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="62">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>22.11</v>
+        <v>23.77</v>
       </c>
       <c r="K63" t="n">
-        <v>-67.90000000000001</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>71.41</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>76.15000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>46.57</v>
+        <v>48.78</v>
       </c>
       <c r="L64" t="n">
-        <v>89.26000000000001</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>40.76</v>
+        <v>54.19</v>
       </c>
       <c r="K74" t="n">
-        <v>-75.42</v>
+        <v>-100.27</v>
       </c>
       <c r="L74" t="n">
-        <v>85.73</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-27.46</v>
+        <v>-34.22</v>
       </c>
       <c r="K75" t="n">
-        <v>-58.33</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>64.48</v>
+        <v>80.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-62.93</v>
+        <v>-78.89</v>
       </c>
       <c r="K76" t="n">
-        <v>11.45</v>
+        <v>14.36</v>
       </c>
       <c r="L76" t="n">
-        <v>63.96</v>
+        <v>80.18000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>70.12</v>
+        <v>73.66</v>
       </c>
       <c r="K77" t="n">
-        <v>-7.8</v>
+        <v>-8.19</v>
       </c>
       <c r="L77" t="n">
-        <v>70.55</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-118.38</v>
+        <v>-126.87</v>
       </c>
       <c r="K78" t="n">
-        <v>76.97</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>141.2</v>
+        <v>151.33</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-100.53</v>
+        <v>-126.11</v>
       </c>
       <c r="K79" t="n">
-        <v>61.61</v>
+        <v>77.3</v>
       </c>
       <c r="L79" t="n">
-        <v>117.91</v>
+        <v>147.92</v>
       </c>
     </row>
     <row r="80">
